--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1033,6 +1033,4480 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>126583702</v>
+      </c>
+      <c r="B5" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>712372</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6358494</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>126583676</v>
+      </c>
+      <c r="B6" t="n">
+        <v>98384</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>712373</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6358470</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI6" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
+        </is>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>126583718</v>
+      </c>
+      <c r="B7" t="n">
+        <v>107243</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>712205</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6358507</v>
+      </c>
+      <c r="S7" t="n">
+        <v>3</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, lite äldre skog.</t>
+        </is>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>126583805</v>
+      </c>
+      <c r="B8" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>712121</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6358401</v>
+      </c>
+      <c r="S8" t="n">
+        <v>5</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, glänta.</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>126583807</v>
+      </c>
+      <c r="B9" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>712230</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6358468</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI9" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, glänta.</t>
+        </is>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>126583720</v>
+      </c>
+      <c r="B10" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>712215</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6358579</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC10" t="inlineStr">
+        <is>
+          <t>Vid mindre sten (OL-kontroll).</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI10" t="inlineStr">
+        <is>
+          <t>Tallskog med yngre rakare tallar, enstaka grövre samt enstaka granar. Möjligen på f.d. odlingsområde (jfr Fornsök).</t>
+        </is>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>126583687</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>712386</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6358485</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI11" t="inlineStr">
+        <is>
+          <t>Sumpskog runt dike; träd på socklar.</t>
+        </is>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>126583700</v>
+      </c>
+      <c r="B12" t="n">
+        <v>98339</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>219798</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Skogsknipprot</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Epipactis helleborine</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>712372</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6358494</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI12" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
+        </is>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>126583708</v>
+      </c>
+      <c r="B13" t="n">
+        <v>107243</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>712342</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6358478</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; fuktigare skog mot O-NO.</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>126583701</v>
+      </c>
+      <c r="B14" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>712372</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6358494</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Varav 10 mot NO.</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>126583688</v>
+      </c>
+      <c r="B15" t="n">
+        <v>105956</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>712386</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6358485</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>Sumpskog runt dike; träd på socklar.</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>126583723</v>
+      </c>
+      <c r="B16" t="n">
+        <v>105956</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>712196</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6358593</v>
+      </c>
+      <c r="S16" t="n">
+        <v>5</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>Alvarskog med gläntor.</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>126583642</v>
+      </c>
+      <c r="B17" t="n">
+        <v>105956</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>712130</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6358376</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>126583726</v>
+      </c>
+      <c r="B18" t="n">
+        <v>103814</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>220164</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Solvända</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Helianthemum nummularium</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(L.) Mill.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>712183</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6358595</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>Alvarglänta.</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>126583639</v>
+      </c>
+      <c r="B19" t="n">
+        <v>105956</v>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>712121</v>
+      </c>
+      <c r="R19" t="n">
+        <v>6358401</v>
+      </c>
+      <c r="S19" t="n">
+        <v>5</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>126583703</v>
+      </c>
+      <c r="B20" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>712360</v>
+      </c>
+      <c r="R20" t="n">
+        <v>6358476</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; fuktigare skog.</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>126583698</v>
+      </c>
+      <c r="B21" t="n">
+        <v>105956</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>712372</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6358494</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>126583699</v>
+      </c>
+      <c r="B22" t="n">
+        <v>98384</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>712372</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6358494</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>126583672</v>
+      </c>
+      <c r="B23" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>712360</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6358451</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; fuktig.</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>126583862</v>
+      </c>
+      <c r="B24" t="n">
+        <v>95964</v>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>2180</v>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>Blåmossa</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Leucobryum glaucum</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J24" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>712369</v>
+      </c>
+      <c r="R24" t="n">
+        <v>6358414</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
+    </row>
+    <row r="25">
+      <c r="A25" t="n">
+        <v>126583644</v>
+      </c>
+      <c r="B25" t="n">
+        <v>105956</v>
+      </c>
+      <c r="D25" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E25" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H25" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
+      <c r="P25" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q25" t="n">
+        <v>712152</v>
+      </c>
+      <c r="R25" t="n">
+        <v>6358376</v>
+      </c>
+      <c r="S25" t="n">
+        <v>5</v>
+      </c>
+      <c r="T25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V25" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W25" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA25" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG25" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT25" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX25" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY25" t="inlineStr"/>
+    </row>
+    <row r="26">
+      <c r="A26" t="n">
+        <v>126583741</v>
+      </c>
+      <c r="B26" t="n">
+        <v>99036</v>
+      </c>
+      <c r="D26" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E26" t="n">
+        <v>222322</v>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>Ängsstarr</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>Carex hostiana</t>
+        </is>
+      </c>
+      <c r="H26" t="inlineStr">
+        <is>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="P26" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q26" t="n">
+        <v>712209</v>
+      </c>
+      <c r="R26" t="n">
+        <v>6358656</v>
+      </c>
+      <c r="S26" t="n">
+        <v>10</v>
+      </c>
+      <c r="T26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V26" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W26" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA26" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Märklig kombination av arter med ängsstarr, darrgräs, blåtåtel, ängshavre, blodnäva, färgmåra.</t>
+        </is>
+      </c>
+      <c r="AD26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG26" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Fuktmark vid stig, f.d. odlingsområde?</t>
+        </is>
+      </c>
+      <c r="AT26" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX26" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY26" t="inlineStr"/>
+    </row>
+    <row r="27">
+      <c r="A27" t="n">
+        <v>126583707</v>
+      </c>
+      <c r="B27" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E27" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q27" t="n">
+        <v>712342</v>
+      </c>
+      <c r="R27" t="n">
+        <v>6358478</v>
+      </c>
+      <c r="S27" t="n">
+        <v>10</v>
+      </c>
+      <c r="T27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V27" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W27" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y27" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA27" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG27" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI27" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; fuktigare skog mot O-NO.</t>
+        </is>
+      </c>
+      <c r="AT27" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX27" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="n">
+        <v>126583694</v>
+      </c>
+      <c r="B28" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E28" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q28" t="n">
+        <v>712382</v>
+      </c>
+      <c r="R28" t="n">
+        <v>6358499</v>
+      </c>
+      <c r="S28" t="n">
+        <v>10</v>
+      </c>
+      <c r="T28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V28" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W28" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y28" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA28" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG28" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI28" t="inlineStr">
+        <is>
+          <t>Sumpskog runt dike; träd på socklar.</t>
+        </is>
+      </c>
+      <c r="AT28" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX28" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="n">
+        <v>126583675</v>
+      </c>
+      <c r="B29" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E29" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q29" t="n">
+        <v>712351</v>
+      </c>
+      <c r="R29" t="n">
+        <v>6358459</v>
+      </c>
+      <c r="S29" t="n">
+        <v>10</v>
+      </c>
+      <c r="T29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V29" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W29" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y29" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA29" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG29" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI29" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; fuktig.</t>
+        </is>
+      </c>
+      <c r="AT29" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX29" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="n">
+        <v>126583677</v>
+      </c>
+      <c r="B30" t="n">
+        <v>98279</v>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E30" t="n">
+        <v>223591</v>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>Skogsnycklar</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q30" t="n">
+        <v>712373</v>
+      </c>
+      <c r="R30" t="n">
+        <v>6358470</v>
+      </c>
+      <c r="S30" t="n">
+        <v>10</v>
+      </c>
+      <c r="T30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V30" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W30" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y30" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA30" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG30" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI30" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
+        </is>
+      </c>
+      <c r="AT30" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX30" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="n">
+        <v>126583646</v>
+      </c>
+      <c r="B31" t="n">
+        <v>105956</v>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E31" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q31" t="n">
+        <v>712194</v>
+      </c>
+      <c r="R31" t="n">
+        <v>6358413</v>
+      </c>
+      <c r="S31" t="n">
+        <v>10</v>
+      </c>
+      <c r="T31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V31" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W31" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y31" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA31" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG31" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI31" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT31" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX31" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY31" t="inlineStr"/>
+    </row>
+    <row r="32">
+      <c r="A32" t="n">
+        <v>126583743</v>
+      </c>
+      <c r="B32" t="n">
+        <v>98384</v>
+      </c>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E32" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G32" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H32" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P32" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q32" t="n">
+        <v>712224</v>
+      </c>
+      <c r="R32" t="n">
+        <v>6358688</v>
+      </c>
+      <c r="S32" t="n">
+        <v>10</v>
+      </c>
+      <c r="T32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V32" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W32" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y32" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA32" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG32" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI32" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT32" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX32" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>126583808</v>
+      </c>
+      <c r="B33" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E33" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q33" t="n">
+        <v>712218</v>
+      </c>
+      <c r="R33" t="n">
+        <v>6358694</v>
+      </c>
+      <c r="S33" t="n">
+        <v>5</v>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W33" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y33" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA33" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG33" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI33" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, glänta.</t>
+        </is>
+      </c>
+      <c r="AT33" t="inlineStr"/>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX33" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY33" t="inlineStr"/>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>126583673</v>
+      </c>
+      <c r="B34" t="n">
+        <v>98384</v>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E34" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q34" t="n">
+        <v>712351</v>
+      </c>
+      <c r="R34" t="n">
+        <v>6358459</v>
+      </c>
+      <c r="S34" t="n">
+        <v>10</v>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W34" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y34" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA34" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG34" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI34" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; fuktig.</t>
+        </is>
+      </c>
+      <c r="AT34" t="inlineStr"/>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX34" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY34" t="inlineStr"/>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>126583650</v>
+      </c>
+      <c r="B35" t="n">
+        <v>107243</v>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E35" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q35" t="n">
+        <v>712214</v>
+      </c>
+      <c r="R35" t="n">
+        <v>6358424</v>
+      </c>
+      <c r="S35" t="n">
+        <v>10</v>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W35" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y35" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA35" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG35" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI35" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT35" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX35" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY35" t="inlineStr"/>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>126583641</v>
+      </c>
+      <c r="B36" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E36" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q36" t="n">
+        <v>712130</v>
+      </c>
+      <c r="R36" t="n">
+        <v>6358376</v>
+      </c>
+      <c r="S36" t="n">
+        <v>10</v>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W36" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y36" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA36" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG36" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI36" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT36" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX36" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY36" t="inlineStr"/>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>126583648</v>
+      </c>
+      <c r="B37" t="n">
+        <v>107243</v>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E37" t="n">
+        <v>220079</v>
+      </c>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>Jordtistel</t>
+        </is>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Cirsium acaule</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q37" t="n">
+        <v>712194</v>
+      </c>
+      <c r="R37" t="n">
+        <v>6358413</v>
+      </c>
+      <c r="S37" t="n">
+        <v>10</v>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W37" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y37" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA37" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG37" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI37" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
+      </c>
+      <c r="AT37" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX37" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY37" t="inlineStr"/>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>126583734</v>
+      </c>
+      <c r="B38" t="n">
+        <v>106654</v>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E38" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q38" t="n">
+        <v>712187</v>
+      </c>
+      <c r="R38" t="n">
+        <v>6358620</v>
+      </c>
+      <c r="S38" t="n">
+        <v>10</v>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W38" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y38" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA38" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG38" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI38" t="inlineStr">
+        <is>
+          <t>Alvartallskog, gles, med flera döda tallar.</t>
+        </is>
+      </c>
+      <c r="AT38" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX38" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY38" t="inlineStr"/>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>126583695</v>
+      </c>
+      <c r="B39" t="n">
+        <v>105956</v>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E39" t="n">
+        <v>220785</v>
+      </c>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>Ask</t>
+        </is>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Fraxinus excelsior</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q39" t="n">
+        <v>712382</v>
+      </c>
+      <c r="R39" t="n">
+        <v>6358499</v>
+      </c>
+      <c r="S39" t="n">
+        <v>10</v>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W39" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y39" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA39" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG39" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI39" t="inlineStr">
+        <is>
+          <t>Sumpskog runt dike; träd på socklar.</t>
+        </is>
+      </c>
+      <c r="AT39" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX39" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY39" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>126583670</v>
+      </c>
+      <c r="B40" t="n">
+        <v>98384</v>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E40" t="n">
+        <v>219847</v>
+      </c>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>Tvåblad</t>
+        </is>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Neottia ovata</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I40" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q40" t="n">
+        <v>712360</v>
+      </c>
+      <c r="R40" t="n">
+        <v>6358451</v>
+      </c>
+      <c r="S40" t="n">
+        <v>10</v>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W40" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y40" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA40" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG40" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI40" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; fuktig.</t>
+        </is>
+      </c>
+      <c r="AT40" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX40" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY40" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>126583806</v>
+      </c>
+      <c r="B41" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E41" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I41" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q41" t="n">
+        <v>712386</v>
+      </c>
+      <c r="R41" t="n">
+        <v>6358485</v>
+      </c>
+      <c r="S41" t="n">
+        <v>10</v>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W41" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y41" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA41" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Snabb observation.</t>
+        </is>
+      </c>
+      <c r="AD41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG41" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI41" t="inlineStr">
+        <is>
+          <t>Sumpskog runt dike; träd på socklar.</t>
+        </is>
+      </c>
+      <c r="AT41" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX41" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY41" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>126583714</v>
+      </c>
+      <c r="B42" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E42" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q42" t="n">
+        <v>712284</v>
+      </c>
+      <c r="R42" t="n">
+        <v>6358477</v>
+      </c>
+      <c r="S42" t="n">
+        <v>10</v>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W42" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y42" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA42" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG42" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI42" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, lite äldre skog.</t>
+        </is>
+      </c>
+      <c r="AT42" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX42" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY42" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>126583809</v>
+      </c>
+      <c r="B43" t="n">
+        <v>43228</v>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E43" t="n">
+        <v>101242</v>
+      </c>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>Dårgräsfjäril</t>
+        </is>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Lopinga achine</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I43" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q43" t="n">
+        <v>712214</v>
+      </c>
+      <c r="R43" t="n">
+        <v>6358733</v>
+      </c>
+      <c r="S43" t="n">
+        <v>5</v>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W43" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y43" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA43" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG43" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI43" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog, glänta, f.d. odlingsröse mot O.</t>
+        </is>
+      </c>
+      <c r="AT43" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX43" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY43" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>126583728</v>
+      </c>
+      <c r="B44" t="n">
+        <v>106654</v>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E44" t="n">
+        <v>221849</v>
+      </c>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>Backtimjan</t>
+        </is>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Thymus serpyllum</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q44" t="n">
+        <v>712183</v>
+      </c>
+      <c r="R44" t="n">
+        <v>6358595</v>
+      </c>
+      <c r="S44" t="n">
+        <v>10</v>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AD44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG44" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI44" t="inlineStr">
+        <is>
+          <t>Alvarglänta.</t>
+        </is>
+      </c>
+      <c r="AT44" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX44" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY44" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>126583678</v>
+      </c>
+      <c r="B45" t="n">
+        <v>109185</v>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E45" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Bjärges 1:20 (3), Gtl</t>
+        </is>
+      </c>
+      <c r="Q45" t="n">
+        <v>712373</v>
+      </c>
+      <c r="R45" t="n">
+        <v>6358470</v>
+      </c>
+      <c r="S45" t="n">
+        <v>10</v>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W45" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y45" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AA45" t="inlineStr">
+        <is>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
+      <c r="AD45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG45" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI45" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
+        </is>
+      </c>
+      <c r="AT45" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AX45" t="inlineStr">
+        <is>
+          <t>Jörgen Petersson</t>
+        </is>
+      </c>
+      <c r="AY45" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -3103,57 +3103,48 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126583862</v>
+        <v>126583644</v>
       </c>
       <c r="B24" t="n">
-        <v>95964</v>
+        <v>105956</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>220785</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I24" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J24" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>712369</v>
+        <v>712152</v>
       </c>
       <c r="R24" t="n">
-        <v>6358414</v>
+        <v>6358376</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3193,6 +3184,11 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3209,48 +3205,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126583644</v>
+        <v>126583741</v>
       </c>
       <c r="B25" t="n">
-        <v>105956</v>
+        <v>99036</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220785</v>
+        <v>222322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712152</v>
+        <v>712209</v>
       </c>
       <c r="R25" t="n">
-        <v>6358376</v>
+        <v>6358656</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3282,6 +3287,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Märklig kombination av arter med ängsstarr, darrgräs, blåtåtel, ängshavre, blodnäva, färgmåra.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3293,7 +3303,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Fuktmark vid stig, f.d. odlingsområde?</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3311,42 +3321,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126583741</v>
+        <v>126583862</v>
       </c>
       <c r="B26" t="n">
-        <v>99036</v>
+        <v>95964</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222322</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3355,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712209</v>
+        <v>712369</v>
       </c>
       <c r="R26" t="n">
-        <v>6358656</v>
+        <v>6358414</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3393,11 +3403,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Märklig kombination av arter med ängsstarr, darrgräs, blåtåtel, ängshavre, blodnäva, färgmåra.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3406,11 +3411,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Fuktmark vid stig, f.d. odlingsområde?</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -1035,10 +1035,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>126583702</v>
+        <v>126583807</v>
       </c>
       <c r="B5" t="n">
-        <v>109185</v>
+        <v>43228</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1046,34 +1046,53 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>712372</v>
+        <v>712230</v>
       </c>
       <c r="R5" t="n">
-        <v>6358494</v>
+        <v>6358468</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1108,11 +1127,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1124,7 +1138,7 @@
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
+          <t>Kalkbarrskog, glänta.</t>
         </is>
       </c>
       <c r="AT5" t="inlineStr"/>
@@ -1142,10 +1156,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>126583718</v>
+        <v>126583805</v>
       </c>
       <c r="B6" t="n">
-        <v>107243</v>
+        <v>43228</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1153,31 +1167,41 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220079</v>
+        <v>101242</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
@@ -1186,13 +1210,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>712205</v>
+        <v>712121</v>
       </c>
       <c r="R6" t="n">
-        <v>6358507</v>
+        <v>6358401</v>
       </c>
       <c r="S6" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1235,7 +1259,7 @@
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, lite äldre skog.</t>
+          <t>Kalkbarrskog, glänta.</t>
         </is>
       </c>
       <c r="AT6" t="inlineStr"/>
@@ -1253,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126583805</v>
+        <v>126583718</v>
       </c>
       <c r="B7" t="n">
-        <v>43228</v>
+        <v>107318</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1264,41 +1288,31 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>101242</v>
+        <v>220079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
@@ -1307,13 +1321,13 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712121</v>
+        <v>712205</v>
       </c>
       <c r="R7" t="n">
-        <v>6358401</v>
+        <v>6358507</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1356,7 +1370,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, glänta.</t>
+          <t>Kalkbarrskog, lite äldre skog.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1374,54 +1388,45 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126583676</v>
+        <v>126583702</v>
       </c>
       <c r="B8" t="n">
-        <v>98384</v>
+        <v>109260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>712373</v>
+        <v>712372</v>
       </c>
       <c r="R8" t="n">
-        <v>6358470</v>
+        <v>6358494</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1456,6 +1461,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1467,7 +1477,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
+          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1485,52 +1495,42 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>126583807</v>
+        <v>126583676</v>
       </c>
       <c r="B9" t="n">
-        <v>43228</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>101242</v>
+        <v>219847</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M9" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1539,10 +1539,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>712230</v>
+        <v>712373</v>
       </c>
       <c r="R9" t="n">
-        <v>6358468</v>
+        <v>6358470</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1588,7 +1588,7 @@
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, glänta.</t>
+          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
         </is>
       </c>
       <c r="AT9" t="inlineStr"/>
@@ -1609,7 +1609,7 @@
         <v>126583700</v>
       </c>
       <c r="B10" t="n">
-        <v>98339</v>
+        <v>98414</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>126583720</v>
       </c>
       <c r="B11" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>126583687</v>
       </c>
       <c r="B12" t="n">
-        <v>98279</v>
+        <v>98354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,45 +1944,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126583688</v>
+        <v>126583708</v>
       </c>
       <c r="B13" t="n">
-        <v>105956</v>
+        <v>107318</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220785</v>
+        <v>220079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712386</v>
+        <v>712342</v>
       </c>
       <c r="R13" t="n">
-        <v>6358485</v>
+        <v>6358478</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,7 +2037,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Sumpskog runt dike; träd på socklar.</t>
+          <t>Kalkbarrskog; fuktigare skog mot O-NO.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2046,54 +2055,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126583708</v>
+        <v>126583688</v>
       </c>
       <c r="B14" t="n">
-        <v>107243</v>
+        <v>106031</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220079</v>
+        <v>220785</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712342</v>
+        <v>712386</v>
       </c>
       <c r="R14" t="n">
-        <v>6358478</v>
+        <v>6358485</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2139,7 +2139,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktigare skog mot O-NO.</t>
+          <t>Sumpskog runt dike; träd på socklar.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2160,7 +2160,7 @@
         <v>126583701</v>
       </c>
       <c r="B15" t="n">
-        <v>98279</v>
+        <v>98354</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2276,7 +2276,7 @@
         <v>126583642</v>
       </c>
       <c r="B16" t="n">
-        <v>105956</v>
+        <v>106031</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>126583723</v>
       </c>
       <c r="B17" t="n">
-        <v>105956</v>
+        <v>106031</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2480,7 +2480,7 @@
         <v>126583639</v>
       </c>
       <c r="B18" t="n">
-        <v>105956</v>
+        <v>106031</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2579,27 +2579,27 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126583703</v>
+        <v>126583698</v>
       </c>
       <c r="B19" t="n">
-        <v>109185</v>
+        <v>106031</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712360</v>
+        <v>712372</v>
       </c>
       <c r="R19" t="n">
-        <v>6358476</v>
+        <v>6358494</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktigare skog.</t>
+          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2684,7 +2684,7 @@
         <v>126583726</v>
       </c>
       <c r="B20" t="n">
-        <v>103814</v>
+        <v>103889</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2783,27 +2783,27 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>126583698</v>
+        <v>126583703</v>
       </c>
       <c r="B21" t="n">
-        <v>105956</v>
+        <v>109260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E21" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
@@ -2818,10 +2818,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>712372</v>
+        <v>712360</v>
       </c>
       <c r="R21" t="n">
-        <v>6358494</v>
+        <v>6358476</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2867,7 +2867,7 @@
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
+          <t>Kalkbarrskog; fuktigare skog.</t>
         </is>
       </c>
       <c r="AT21" t="inlineStr"/>
@@ -2888,7 +2888,7 @@
         <v>126583672</v>
       </c>
       <c r="B22" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>126583699</v>
       </c>
       <c r="B23" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3106,7 +3106,7 @@
         <v>126583741</v>
       </c>
       <c r="B24" t="n">
-        <v>99036</v>
+        <v>99111</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3219,57 +3219,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126583862</v>
+        <v>126583644</v>
       </c>
       <c r="B25" t="n">
-        <v>95964</v>
+        <v>106031</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>2180</v>
+        <v>220785</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712369</v>
+        <v>712152</v>
       </c>
       <c r="R25" t="n">
-        <v>6358414</v>
+        <v>6358376</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3309,6 +3300,11 @@
       </c>
       <c r="AG25" t="b">
         <v>0</v>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
@@ -3325,48 +3321,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126583644</v>
+        <v>126583862</v>
       </c>
       <c r="B26" t="n">
-        <v>105956</v>
+        <v>96039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>dm²</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712152</v>
+        <v>712369</v>
       </c>
       <c r="R26" t="n">
-        <v>6358376</v>
+        <v>6358414</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3406,11 +3411,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3430,7 +3430,7 @@
         <v>126583707</v>
       </c>
       <c r="B27" t="n">
-        <v>109185</v>
+        <v>109260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>126583694</v>
       </c>
       <c r="B28" t="n">
-        <v>98279</v>
+        <v>98354</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,27 +3640,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126583675</v>
+        <v>126583646</v>
       </c>
       <c r="B29" t="n">
-        <v>109185</v>
+        <v>106031</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220299</v>
+        <v>220785</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>712351</v>
+        <v>712194</v>
       </c>
       <c r="R29" t="n">
-        <v>6358459</v>
+        <v>6358413</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3713,11 +3713,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3729,7 +3724,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3747,48 +3742,67 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126583646</v>
+        <v>126583808</v>
       </c>
       <c r="B30" t="n">
-        <v>105956</v>
+        <v>43228</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220785</v>
+        <v>101242</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>712194</v>
+        <v>712218</v>
       </c>
       <c r="R30" t="n">
-        <v>6358413</v>
+        <v>6358694</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3831,7 +3845,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, glänta.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3849,52 +3863,42 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126583808</v>
+        <v>126583743</v>
       </c>
       <c r="B31" t="n">
-        <v>43228</v>
+        <v>98459</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>101242</v>
+        <v>219847</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J31" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K31" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P31" t="inlineStr">
@@ -3903,13 +3907,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>712218</v>
+        <v>712224</v>
       </c>
       <c r="R31" t="n">
-        <v>6358694</v>
+        <v>6358688</v>
       </c>
       <c r="S31" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3952,7 +3956,7 @@
       </c>
       <c r="AI31" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, glänta.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT31" t="inlineStr"/>
@@ -3970,54 +3974,45 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126583743</v>
+        <v>126583675</v>
       </c>
       <c r="B32" t="n">
-        <v>98384</v>
+        <v>109260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>219847</v>
+        <v>220299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>712224</v>
+        <v>712351</v>
       </c>
       <c r="R32" t="n">
-        <v>6358688</v>
+        <v>6358459</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4052,6 +4047,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog; fuktig.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4084,7 +4084,7 @@
         <v>126583677</v>
       </c>
       <c r="B33" t="n">
-        <v>98279</v>
+        <v>98354</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>126583650</v>
       </c>
       <c r="B34" t="n">
-        <v>107243</v>
+        <v>107318</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>126583673</v>
       </c>
       <c r="B35" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4414,10 +4414,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126583734</v>
+        <v>126583648</v>
       </c>
       <c r="B36" t="n">
-        <v>106654</v>
+        <v>107318</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4425,34 +4425,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>221849</v>
+        <v>220079</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>712187</v>
+        <v>712194</v>
       </c>
       <c r="R36" t="n">
-        <v>6358620</v>
+        <v>6358413</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4498,7 +4507,7 @@
       </c>
       <c r="AI36" t="inlineStr">
         <is>
-          <t>Alvartallskog, gles, med flera döda tallar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT36" t="inlineStr"/>
@@ -4516,10 +4525,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126583648</v>
+        <v>126583641</v>
       </c>
       <c r="B37" t="n">
-        <v>107243</v>
+        <v>109260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4527,43 +4536,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I37" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J37" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>712194</v>
+        <v>712130</v>
       </c>
       <c r="R37" t="n">
-        <v>6358413</v>
+        <v>6358376</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4627,10 +4627,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126583641</v>
+        <v>126583734</v>
       </c>
       <c r="B38" t="n">
-        <v>109185</v>
+        <v>106729</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4638,16 +4638,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>712130</v>
+        <v>712187</v>
       </c>
       <c r="R38" t="n">
-        <v>6358376</v>
+        <v>6358620</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvartallskog, gles, med flera döda tallar.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4732,7 +4732,7 @@
         <v>126583695</v>
       </c>
       <c r="B39" t="n">
-        <v>105956</v>
+        <v>106031</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>126583670</v>
       </c>
       <c r="B41" t="n">
-        <v>98384</v>
+        <v>98459</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5068,10 +5068,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>126583714</v>
+        <v>126583809</v>
       </c>
       <c r="B42" t="n">
-        <v>109185</v>
+        <v>43228</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -5079,31 +5079,41 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>3</t>
         </is>
       </c>
       <c r="J42" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P42" t="inlineStr">
@@ -5112,13 +5122,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>712284</v>
+        <v>712214</v>
       </c>
       <c r="R42" t="n">
-        <v>6358477</v>
+        <v>6358733</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5161,7 +5171,7 @@
       </c>
       <c r="AI42" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, lite äldre skog.</t>
+          <t>Kalkbarrskog, glänta, f.d. odlingsröse mot O.</t>
         </is>
       </c>
       <c r="AT42" t="inlineStr"/>
@@ -5179,10 +5189,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>126583809</v>
+        <v>126583714</v>
       </c>
       <c r="B43" t="n">
-        <v>43228</v>
+        <v>109260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5190,41 +5200,31 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J43" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K43" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P43" t="inlineStr">
@@ -5233,13 +5233,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>712214</v>
+        <v>712284</v>
       </c>
       <c r="R43" t="n">
-        <v>6358733</v>
+        <v>6358477</v>
       </c>
       <c r="S43" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5282,7 +5282,7 @@
       </c>
       <c r="AI43" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, glänta, f.d. odlingsröse mot O.</t>
+          <t>Kalkbarrskog, lite äldre skog.</t>
         </is>
       </c>
       <c r="AT43" t="inlineStr"/>
@@ -5300,10 +5300,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126583728</v>
+        <v>126583678</v>
       </c>
       <c r="B44" t="n">
-        <v>106654</v>
+        <v>109260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5311,16 +5311,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>712183</v>
+        <v>712373</v>
       </c>
       <c r="R44" t="n">
-        <v>6358595</v>
+        <v>6358470</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5373,6 +5373,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5384,7 +5389,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5402,10 +5407,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126583678</v>
+        <v>126583728</v>
       </c>
       <c r="B45" t="n">
-        <v>109185</v>
+        <v>106729</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5413,16 +5418,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5437,10 +5442,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>712373</v>
+        <v>712183</v>
       </c>
       <c r="R45" t="n">
-        <v>6358470</v>
+        <v>6358595</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5475,11 +5480,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -1277,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126583718</v>
+        <v>126583702</v>
       </c>
       <c r="B7" t="n">
-        <v>107318</v>
+        <v>109266</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,46 +1288,37 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712205</v>
+        <v>712372</v>
       </c>
       <c r="R7" t="n">
-        <v>6358507</v>
+        <v>6358494</v>
       </c>
       <c r="S7" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1359,6 +1350,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1370,7 +1366,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, lite äldre skog.</t>
+          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1388,10 +1384,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126583702</v>
+        <v>126583718</v>
       </c>
       <c r="B8" t="n">
-        <v>109260</v>
+        <v>107324</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1399,37 +1395,46 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>712372</v>
+        <v>712205</v>
       </c>
       <c r="R8" t="n">
-        <v>6358494</v>
+        <v>6358507</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1461,11 +1466,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
+          <t>Kalkbarrskog, lite äldre skog.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1498,7 +1498,7 @@
         <v>126583676</v>
       </c>
       <c r="B9" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>126583700</v>
       </c>
       <c r="B10" t="n">
-        <v>98414</v>
+        <v>98420</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>126583720</v>
       </c>
       <c r="B11" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>126583687</v>
       </c>
       <c r="B12" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,37 +1944,37 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126583708</v>
+        <v>126583701</v>
       </c>
       <c r="B13" t="n">
-        <v>107318</v>
+        <v>98360</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220079</v>
+        <v>223591</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1988,10 +1988,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712342</v>
+        <v>712372</v>
       </c>
       <c r="R13" t="n">
-        <v>6358478</v>
+        <v>6358494</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,6 +2026,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC13" t="inlineStr">
+        <is>
+          <t>Varav 10 mot NO.</t>
+        </is>
+      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2037,7 +2042,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktigare skog mot O-NO.</t>
+          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2058,7 +2063,7 @@
         <v>126583688</v>
       </c>
       <c r="B14" t="n">
-        <v>106031</v>
+        <v>106037</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2157,37 +2162,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126583701</v>
+        <v>126583708</v>
       </c>
       <c r="B15" t="n">
-        <v>98354</v>
+        <v>107324</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>223591</v>
+        <v>220079</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>75</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2201,10 +2206,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712372</v>
+        <v>712342</v>
       </c>
       <c r="R15" t="n">
-        <v>6358494</v>
+        <v>6358478</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2239,11 +2244,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC15" t="inlineStr">
-        <is>
-          <t>Varav 10 mot NO.</t>
-        </is>
-      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
+          <t>Kalkbarrskog; fuktigare skog mot O-NO.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2276,7 +2276,7 @@
         <v>126583642</v>
       </c>
       <c r="B16" t="n">
-        <v>106031</v>
+        <v>106037</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2378,7 +2378,7 @@
         <v>126583723</v>
       </c>
       <c r="B17" t="n">
-        <v>106031</v>
+        <v>106037</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2477,10 +2477,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126583639</v>
+        <v>126583698</v>
       </c>
       <c r="B18" t="n">
-        <v>106031</v>
+        <v>106037</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2512,13 +2512,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712121</v>
+        <v>712372</v>
       </c>
       <c r="R18" t="n">
-        <v>6358401</v>
+        <v>6358494</v>
       </c>
       <c r="S18" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2579,32 +2579,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126583698</v>
+        <v>126583726</v>
       </c>
       <c r="B19" t="n">
-        <v>106031</v>
+        <v>103895</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220785</v>
+        <v>220164</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712372</v>
+        <v>712183</v>
       </c>
       <c r="R19" t="n">
-        <v>6358494</v>
+        <v>6358595</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2681,32 +2681,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126583726</v>
+        <v>126583639</v>
       </c>
       <c r="B20" t="n">
-        <v>103889</v>
+        <v>106037</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220164</v>
+        <v>220785</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2716,13 +2716,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712183</v>
+        <v>712121</v>
       </c>
       <c r="R20" t="n">
-        <v>6358595</v>
+        <v>6358401</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -2786,7 +2786,7 @@
         <v>126583703</v>
       </c>
       <c r="B21" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>126583672</v>
       </c>
       <c r="B22" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>126583699</v>
       </c>
       <c r="B23" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3103,42 +3103,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126583741</v>
+        <v>126583862</v>
       </c>
       <c r="B24" t="n">
-        <v>99111</v>
+        <v>96045</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>222322</v>
+        <v>2180</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3147,10 +3147,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>712209</v>
+        <v>712369</v>
       </c>
       <c r="R24" t="n">
-        <v>6358656</v>
+        <v>6358414</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3185,11 +3185,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC24" t="inlineStr">
-        <is>
-          <t>Märklig kombination av arter med ängsstarr, darrgräs, blåtåtel, ängshavre, blodnäva, färgmåra.</t>
-        </is>
-      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3198,11 +3193,6 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
-      </c>
-      <c r="AI24" t="inlineStr">
-        <is>
-          <t>Fuktmark vid stig, f.d. odlingsområde?</t>
-        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3219,48 +3209,57 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126583644</v>
+        <v>126583741</v>
       </c>
       <c r="B25" t="n">
-        <v>106031</v>
+        <v>99117</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220785</v>
+        <v>222322</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J25" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712152</v>
+        <v>712209</v>
       </c>
       <c r="R25" t="n">
-        <v>6358376</v>
+        <v>6358656</v>
       </c>
       <c r="S25" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3292,6 +3291,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Märklig kombination av arter med ängsstarr, darrgräs, blåtåtel, ängshavre, blodnäva, färgmåra.</t>
+        </is>
+      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3303,7 +3307,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Fuktmark vid stig, f.d. odlingsområde?</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3321,57 +3325,48 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126583862</v>
+        <v>126583644</v>
       </c>
       <c r="B26" t="n">
-        <v>96039</v>
+        <v>106037</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>2180</v>
+        <v>220785</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J26" t="inlineStr">
-        <is>
-          <t>dm²</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712369</v>
+        <v>712152</v>
       </c>
       <c r="R26" t="n">
-        <v>6358414</v>
+        <v>6358376</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3411,6 +3406,11 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
+      </c>
+      <c r="AI26" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3430,7 +3430,7 @@
         <v>126583707</v>
       </c>
       <c r="B27" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>126583694</v>
       </c>
       <c r="B28" t="n">
-        <v>98354</v>
+        <v>98360</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,27 +3640,27 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126583646</v>
+        <v>126583675</v>
       </c>
       <c r="B29" t="n">
-        <v>106031</v>
+        <v>109266</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
@@ -3675,10 +3675,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>712194</v>
+        <v>712351</v>
       </c>
       <c r="R29" t="n">
-        <v>6358413</v>
+        <v>6358459</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3713,6 +3713,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3724,7 +3729,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog; fuktig.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3742,67 +3747,48 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126583808</v>
+        <v>126583646</v>
       </c>
       <c r="B30" t="n">
-        <v>43228</v>
+        <v>106037</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>101242</v>
+        <v>220785</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J30" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K30" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>712218</v>
+        <v>712194</v>
       </c>
       <c r="R30" t="n">
-        <v>6358694</v>
+        <v>6358413</v>
       </c>
       <c r="S30" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3845,7 +3831,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, glänta.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3866,7 +3852,7 @@
         <v>126583743</v>
       </c>
       <c r="B31" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3974,45 +3960,54 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126583675</v>
+        <v>126583677</v>
       </c>
       <c r="B32" t="n">
-        <v>109260</v>
+        <v>98360</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220299</v>
+        <v>223591</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J32" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>712351</v>
+        <v>712373</v>
       </c>
       <c r="R32" t="n">
-        <v>6358459</v>
+        <v>6358470</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -4047,11 +4042,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4063,7 +4053,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig.</t>
+          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4081,42 +4071,52 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126583677</v>
+        <v>126583808</v>
       </c>
       <c r="B33" t="n">
-        <v>98354</v>
+        <v>43228</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>223591</v>
+        <v>101242</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4125,13 +4125,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>712373</v>
+        <v>712218</v>
       </c>
       <c r="R33" t="n">
-        <v>6358470</v>
+        <v>6358694</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
+          <t>Kalkbarrskog, glänta.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4195,7 +4195,7 @@
         <v>126583650</v>
       </c>
       <c r="B34" t="n">
-        <v>107318</v>
+        <v>107324</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>126583673</v>
       </c>
       <c r="B35" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4417,7 +4417,7 @@
         <v>126583648</v>
       </c>
       <c r="B36" t="n">
-        <v>107318</v>
+        <v>107324</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4525,10 +4525,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126583641</v>
+        <v>126583734</v>
       </c>
       <c r="B37" t="n">
-        <v>109260</v>
+        <v>106735</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4536,16 +4536,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4560,10 +4560,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>712130</v>
+        <v>712187</v>
       </c>
       <c r="R37" t="n">
-        <v>6358376</v>
+        <v>6358620</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4609,7 +4609,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvartallskog, gles, med flera döda tallar.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4627,10 +4627,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126583734</v>
+        <v>126583641</v>
       </c>
       <c r="B38" t="n">
-        <v>106729</v>
+        <v>109266</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4638,16 +4638,16 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
@@ -4662,10 +4662,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>712187</v>
+        <v>712130</v>
       </c>
       <c r="R38" t="n">
-        <v>6358620</v>
+        <v>6358376</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Alvartallskog, gles, med flera döda tallar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4732,7 +4732,7 @@
         <v>126583695</v>
       </c>
       <c r="B39" t="n">
-        <v>106031</v>
+        <v>106037</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>126583670</v>
       </c>
       <c r="B41" t="n">
-        <v>98459</v>
+        <v>98465</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>126583714</v>
       </c>
       <c r="B43" t="n">
-        <v>109260</v>
+        <v>109266</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5300,10 +5300,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126583678</v>
+        <v>126583728</v>
       </c>
       <c r="B44" t="n">
-        <v>109260</v>
+        <v>106735</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5311,16 +5311,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>712373</v>
+        <v>712183</v>
       </c>
       <c r="R44" t="n">
-        <v>6358470</v>
+        <v>6358595</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5373,11 +5373,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5389,7 +5384,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5407,10 +5402,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126583728</v>
+        <v>126583678</v>
       </c>
       <c r="B45" t="n">
-        <v>106729</v>
+        <v>109266</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5418,16 +5413,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5442,10 +5437,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>712183</v>
+        <v>712373</v>
       </c>
       <c r="R45" t="n">
-        <v>6358595</v>
+        <v>6358470</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5480,6 +5475,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -1944,54 +1944,45 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126583701</v>
+        <v>126583688</v>
       </c>
       <c r="B13" t="n">
-        <v>98360</v>
+        <v>106037</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712372</v>
+        <v>712386</v>
       </c>
       <c r="R13" t="n">
-        <v>6358494</v>
+        <v>6358485</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2026,11 +2017,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC13" t="inlineStr">
-        <is>
-          <t>Varav 10 mot NO.</t>
-        </is>
-      </c>
       <c r="AD13" t="b">
         <v>0</v>
       </c>
@@ -2042,7 +2028,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
+          <t>Sumpskog runt dike; träd på socklar.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2060,45 +2046,54 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126583688</v>
+        <v>126583701</v>
       </c>
       <c r="B14" t="n">
-        <v>106037</v>
+        <v>98360</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220785</v>
+        <v>223591</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712386</v>
+        <v>712372</v>
       </c>
       <c r="R14" t="n">
-        <v>6358485</v>
+        <v>6358494</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2133,6 +2128,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC14" t="inlineStr">
+        <is>
+          <t>Varav 10 mot NO.</t>
+        </is>
+      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2144,7 +2144,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Sumpskog runt dike; träd på socklar.</t>
+          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2273,7 +2273,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126583642</v>
+        <v>126583723</v>
       </c>
       <c r="B16" t="n">
         <v>106037</v>
@@ -2308,13 +2308,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>712130</v>
+        <v>712196</v>
       </c>
       <c r="R16" t="n">
-        <v>6358376</v>
+        <v>6358593</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvarskog med gläntor.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2375,7 +2375,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126583723</v>
+        <v>126583642</v>
       </c>
       <c r="B17" t="n">
         <v>106037</v>
@@ -2410,13 +2410,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712196</v>
+        <v>712130</v>
       </c>
       <c r="R17" t="n">
-        <v>6358593</v>
+        <v>6358376</v>
       </c>
       <c r="S17" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Alvarskog med gläntor.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2477,7 +2477,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>126583698</v>
+        <v>126583639</v>
       </c>
       <c r="B18" t="n">
         <v>106037</v>
@@ -2512,13 +2512,13 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>712372</v>
+        <v>712121</v>
       </c>
       <c r="R18" t="n">
-        <v>6358494</v>
+        <v>6358401</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2561,7 +2561,7 @@
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT18" t="inlineStr"/>
@@ -2579,32 +2579,32 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>126583726</v>
+        <v>126583698</v>
       </c>
       <c r="B19" t="n">
-        <v>103895</v>
+        <v>106037</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220164</v>
+        <v>220785</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
@@ -2614,10 +2614,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>712183</v>
+        <v>712372</v>
       </c>
       <c r="R19" t="n">
-        <v>6358595</v>
+        <v>6358494</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2663,7 +2663,7 @@
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
         </is>
       </c>
       <c r="AT19" t="inlineStr"/>
@@ -2681,32 +2681,32 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>126583639</v>
+        <v>126583726</v>
       </c>
       <c r="B20" t="n">
-        <v>106037</v>
+        <v>103895</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>220785</v>
+        <v>220164</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2716,13 +2716,13 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>712121</v>
+        <v>712183</v>
       </c>
       <c r="R20" t="n">
-        <v>6358401</v>
+        <v>6358595</v>
       </c>
       <c r="S20" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT20" t="inlineStr"/>
@@ -3209,57 +3209,48 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>126583741</v>
+        <v>126583644</v>
       </c>
       <c r="B25" t="n">
-        <v>99117</v>
+        <v>106037</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>222322</v>
+        <v>220785</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>DC.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="J25" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>712209</v>
+        <v>712152</v>
       </c>
       <c r="R25" t="n">
-        <v>6358656</v>
+        <v>6358376</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3291,11 +3282,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Märklig kombination av arter med ängsstarr, darrgräs, blåtåtel, ängshavre, blodnäva, färgmåra.</t>
-        </is>
-      </c>
       <c r="AD25" t="b">
         <v>0</v>
       </c>
@@ -3307,7 +3293,7 @@
       </c>
       <c r="AI25" t="inlineStr">
         <is>
-          <t>Fuktmark vid stig, f.d. odlingsområde?</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT25" t="inlineStr"/>
@@ -3325,48 +3311,57 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126583644</v>
+        <v>126583741</v>
       </c>
       <c r="B26" t="n">
-        <v>106037</v>
+        <v>99117</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220785</v>
+        <v>222322</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J26" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712152</v>
+        <v>712209</v>
       </c>
       <c r="R26" t="n">
-        <v>6358376</v>
+        <v>6358656</v>
       </c>
       <c r="S26" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3398,6 +3393,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC26" t="inlineStr">
+        <is>
+          <t>Märklig kombination av arter med ängsstarr, darrgräs, blåtåtel, ängshavre, blodnäva, färgmåra.</t>
+        </is>
+      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3409,7 +3409,7 @@
       </c>
       <c r="AI26" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Fuktmark vid stig, f.d. odlingsområde?</t>
         </is>
       </c>
       <c r="AT26" t="inlineStr"/>
@@ -3640,45 +3640,54 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126583675</v>
+        <v>126583743</v>
       </c>
       <c r="B29" t="n">
-        <v>109266</v>
+        <v>98465</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>712351</v>
+        <v>712224</v>
       </c>
       <c r="R29" t="n">
-        <v>6358459</v>
+        <v>6358688</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3713,11 +3722,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD29" t="b">
         <v>0</v>
       </c>
@@ -3729,7 +3733,7 @@
       </c>
       <c r="AI29" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT29" t="inlineStr"/>
@@ -3747,27 +3751,27 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126583646</v>
+        <v>126583675</v>
       </c>
       <c r="B30" t="n">
-        <v>106037</v>
+        <v>109266</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
@@ -3782,10 +3786,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>712194</v>
+        <v>712351</v>
       </c>
       <c r="R30" t="n">
-        <v>6358413</v>
+        <v>6358459</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3820,6 +3824,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3831,7 +3840,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog; fuktig.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3849,54 +3858,45 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126583743</v>
+        <v>126583646</v>
       </c>
       <c r="B31" t="n">
-        <v>98465</v>
+        <v>106037</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J31" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>712224</v>
+        <v>712194</v>
       </c>
       <c r="R31" t="n">
-        <v>6358688</v>
+        <v>6358413</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3960,42 +3960,52 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126583677</v>
+        <v>126583808</v>
       </c>
       <c r="B32" t="n">
-        <v>98360</v>
+        <v>43228</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>223591</v>
+        <v>101242</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J32" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K32" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M32" t="inlineStr">
+        <is>
+          <t>friflygande</t>
         </is>
       </c>
       <c r="P32" t="inlineStr">
@@ -4004,13 +4014,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>712373</v>
+        <v>712218</v>
       </c>
       <c r="R32" t="n">
-        <v>6358470</v>
+        <v>6358694</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4053,7 +4063,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
+          <t>Kalkbarrskog, glänta.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4071,52 +4081,42 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>126583808</v>
+        <v>126583677</v>
       </c>
       <c r="B33" t="n">
-        <v>43228</v>
+        <v>98360</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>101242</v>
+        <v>223591</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>66</t>
         </is>
       </c>
       <c r="J33" t="inlineStr">
         <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K33" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M33" t="inlineStr">
-        <is>
-          <t>friflygande</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P33" t="inlineStr">
@@ -4125,13 +4125,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>712218</v>
+        <v>712373</v>
       </c>
       <c r="R33" t="n">
-        <v>6358694</v>
+        <v>6358470</v>
       </c>
       <c r="S33" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4174,7 +4174,7 @@
       </c>
       <c r="AI33" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, glänta.</t>
+          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
         </is>
       </c>
       <c r="AT33" t="inlineStr"/>
@@ -4414,10 +4414,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126583648</v>
+        <v>126583641</v>
       </c>
       <c r="B36" t="n">
-        <v>107324</v>
+        <v>109266</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4425,43 +4425,34 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J36" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>712194</v>
+        <v>712130</v>
       </c>
       <c r="R36" t="n">
-        <v>6358413</v>
+        <v>6358376</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4627,10 +4618,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126583641</v>
+        <v>126583648</v>
       </c>
       <c r="B38" t="n">
-        <v>109266</v>
+        <v>107324</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4638,34 +4629,43 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>712130</v>
+        <v>712194</v>
       </c>
       <c r="R38" t="n">
-        <v>6358376</v>
+        <v>6358413</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -5300,10 +5300,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>126583728</v>
+        <v>126583678</v>
       </c>
       <c r="B44" t="n">
-        <v>106735</v>
+        <v>109266</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5311,16 +5311,16 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -5335,10 +5335,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>712183</v>
+        <v>712373</v>
       </c>
       <c r="R44" t="n">
-        <v>6358595</v>
+        <v>6358470</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5373,6 +5373,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD44" t="b">
         <v>0</v>
       </c>
@@ -5384,7 +5389,7 @@
       </c>
       <c r="AI44" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
         </is>
       </c>
       <c r="AT44" t="inlineStr"/>
@@ -5402,10 +5407,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>126583678</v>
+        <v>126583728</v>
       </c>
       <c r="B45" t="n">
-        <v>109266</v>
+        <v>106735</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -5413,16 +5418,16 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220299</v>
+        <v>221849</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
@@ -5437,10 +5442,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>712373</v>
+        <v>712183</v>
       </c>
       <c r="R45" t="n">
-        <v>6358470</v>
+        <v>6358595</v>
       </c>
       <c r="S45" t="n">
         <v>10</v>
@@ -5475,11 +5480,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD45" t="b">
         <v>0</v>
       </c>
@@ -5491,7 +5491,7 @@
       </c>
       <c r="AI45" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT45" t="inlineStr"/>

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY45"/>
+  <dimension ref="A1:AY72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5507,6 +5507,2651 @@
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>128947652</v>
+      </c>
+      <c r="B46" t="n">
+        <v>86806</v>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E46" t="n">
+        <v>424</v>
+      </c>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q46" t="n">
+        <v>712290</v>
+      </c>
+      <c r="R46" t="n">
+        <v>6358633</v>
+      </c>
+      <c r="S46" t="n">
+        <v>10</v>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W46" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y46" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA46" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG46" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT46" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX46" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY46" t="inlineStr"/>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>128947671</v>
+      </c>
+      <c r="B47" t="n">
+        <v>86784</v>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E47" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q47" t="n">
+        <v>712289</v>
+      </c>
+      <c r="R47" t="n">
+        <v>6358633</v>
+      </c>
+      <c r="S47" t="n">
+        <v>10</v>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W47" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y47" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA47" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG47" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT47" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX47" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY47" t="inlineStr"/>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>128947656</v>
+      </c>
+      <c r="B48" t="n">
+        <v>86959</v>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I48" t="inlineStr"/>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q48" t="n">
+        <v>712239</v>
+      </c>
+      <c r="R48" t="n">
+        <v>6358515</v>
+      </c>
+      <c r="S48" t="n">
+        <v>10</v>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W48" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y48" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA48" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF48" t="inlineStr"/>
+      <c r="AG48" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT48" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX48" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY48" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>128947660</v>
+      </c>
+      <c r="B49" t="n">
+        <v>86959</v>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q49" t="n">
+        <v>712054</v>
+      </c>
+      <c r="R49" t="n">
+        <v>6358300</v>
+      </c>
+      <c r="S49" t="n">
+        <v>10</v>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF49" t="inlineStr"/>
+      <c r="AG49" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT49" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX49" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY49" t="inlineStr"/>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>128947664</v>
+      </c>
+      <c r="B50" t="n">
+        <v>91923</v>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E50" t="n">
+        <v>5420</v>
+      </c>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>Grovticka</t>
+        </is>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Phaeolus schweinitzii</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q50" t="n">
+        <v>712272</v>
+      </c>
+      <c r="R50" t="n">
+        <v>6358461</v>
+      </c>
+      <c r="S50" t="n">
+        <v>10</v>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG50" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT50" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX50" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>128947675</v>
+      </c>
+      <c r="B51" t="n">
+        <v>86922</v>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E51" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q51" t="n">
+        <v>712229</v>
+      </c>
+      <c r="R51" t="n">
+        <v>6358510</v>
+      </c>
+      <c r="S51" t="n">
+        <v>10</v>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y51" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA51" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG51" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT51" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX51" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY51" t="inlineStr"/>
+    </row>
+    <row r="52">
+      <c r="A52" t="n">
+        <v>128947674</v>
+      </c>
+      <c r="B52" t="n">
+        <v>86784</v>
+      </c>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E52" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
+      <c r="P52" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q52" t="n">
+        <v>712125</v>
+      </c>
+      <c r="R52" t="n">
+        <v>6358399</v>
+      </c>
+      <c r="S52" t="n">
+        <v>10</v>
+      </c>
+      <c r="T52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V52" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W52" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y52" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA52" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG52" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT52" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX52" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>128947659</v>
+      </c>
+      <c r="B53" t="n">
+        <v>86959</v>
+      </c>
+      <c r="D53" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E53" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G53" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H53" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
+      <c r="P53" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q53" t="n">
+        <v>712053</v>
+      </c>
+      <c r="R53" t="n">
+        <v>6358298</v>
+      </c>
+      <c r="S53" t="n">
+        <v>10</v>
+      </c>
+      <c r="T53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V53" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W53" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y53" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA53" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF53" t="inlineStr"/>
+      <c r="AG53" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT53" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX53" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY53" t="inlineStr"/>
+    </row>
+    <row r="54">
+      <c r="A54" t="n">
+        <v>128947677</v>
+      </c>
+      <c r="B54" t="n">
+        <v>86922</v>
+      </c>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E54" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="P54" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q54" t="n">
+        <v>712057</v>
+      </c>
+      <c r="R54" t="n">
+        <v>6358299</v>
+      </c>
+      <c r="S54" t="n">
+        <v>10</v>
+      </c>
+      <c r="T54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V54" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W54" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y54" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA54" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG54" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT54" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX54" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>128947676</v>
+      </c>
+      <c r="B55" t="n">
+        <v>86922</v>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E55" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G55" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
+      <c r="P55" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q55" t="n">
+        <v>712154</v>
+      </c>
+      <c r="R55" t="n">
+        <v>6358428</v>
+      </c>
+      <c r="S55" t="n">
+        <v>10</v>
+      </c>
+      <c r="T55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V55" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W55" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y55" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA55" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG55" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT55" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX55" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY55" t="inlineStr"/>
+    </row>
+    <row r="56">
+      <c r="A56" t="n">
+        <v>128947667</v>
+      </c>
+      <c r="B56" t="n">
+        <v>92830</v>
+      </c>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E56" t="n">
+        <v>5964</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>Fjällig taggsvamp s.str.</t>
+        </is>
+      </c>
+      <c r="G56" t="inlineStr">
+        <is>
+          <t>Sarcodon imbricatus</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr">
+        <is>
+          <t>(L.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
+      <c r="P56" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q56" t="n">
+        <v>712163</v>
+      </c>
+      <c r="R56" t="n">
+        <v>6358380</v>
+      </c>
+      <c r="S56" t="n">
+        <v>10</v>
+      </c>
+      <c r="T56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V56" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W56" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y56" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA56" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF56" t="inlineStr"/>
+      <c r="AG56" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT56" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX56" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY56" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" t="n">
+        <v>128947669</v>
+      </c>
+      <c r="B57" t="n">
+        <v>86784</v>
+      </c>
+      <c r="D57" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E57" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G57" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H57" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="P57" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q57" t="n">
+        <v>712363</v>
+      </c>
+      <c r="R57" t="n">
+        <v>6358457</v>
+      </c>
+      <c r="S57" t="n">
+        <v>10</v>
+      </c>
+      <c r="T57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V57" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W57" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y57" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA57" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG57" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT57" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX57" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY57" t="inlineStr"/>
+    </row>
+    <row r="58">
+      <c r="A58" t="n">
+        <v>128947647</v>
+      </c>
+      <c r="B58" t="n">
+        <v>86982</v>
+      </c>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E58" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G58" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
+      <c r="P58" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q58" t="n">
+        <v>712175</v>
+      </c>
+      <c r="R58" t="n">
+        <v>6358413</v>
+      </c>
+      <c r="S58" t="n">
+        <v>10</v>
+      </c>
+      <c r="T58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V58" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W58" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y58" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA58" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG58" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT58" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX58" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY58" t="inlineStr"/>
+    </row>
+    <row r="59">
+      <c r="A59" t="n">
+        <v>128947648</v>
+      </c>
+      <c r="B59" t="n">
+        <v>86982</v>
+      </c>
+      <c r="D59" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E59" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G59" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
+      <c r="P59" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q59" t="n">
+        <v>712168</v>
+      </c>
+      <c r="R59" t="n">
+        <v>6358403</v>
+      </c>
+      <c r="S59" t="n">
+        <v>10</v>
+      </c>
+      <c r="T59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V59" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W59" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y59" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA59" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG59" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT59" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX59" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY59" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" t="n">
+        <v>128947655</v>
+      </c>
+      <c r="B60" t="n">
+        <v>86760</v>
+      </c>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E60" t="n">
+        <v>3762</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>Olivspindling</t>
+        </is>
+      </c>
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>Cortinarius venetus</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr">
+        <is>
+          <t>(Fr.:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
+      <c r="P60" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q60" t="n">
+        <v>712080</v>
+      </c>
+      <c r="R60" t="n">
+        <v>6358365</v>
+      </c>
+      <c r="S60" t="n">
+        <v>10</v>
+      </c>
+      <c r="T60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V60" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W60" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y60" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA60" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG60" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT60" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX60" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>128947649</v>
+      </c>
+      <c r="B61" t="n">
+        <v>86982</v>
+      </c>
+      <c r="D61" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E61" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
+      <c r="P61" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q61" t="n">
+        <v>712051</v>
+      </c>
+      <c r="R61" t="n">
+        <v>6358299</v>
+      </c>
+      <c r="S61" t="n">
+        <v>10</v>
+      </c>
+      <c r="T61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V61" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W61" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y61" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA61" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG61" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT61" t="inlineStr"/>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX61" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY61" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>128947654</v>
+      </c>
+      <c r="B62" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G62" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
+      <c r="P62" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q62" t="n">
+        <v>712106</v>
+      </c>
+      <c r="R62" t="n">
+        <v>6358348</v>
+      </c>
+      <c r="S62" t="n">
+        <v>10</v>
+      </c>
+      <c r="T62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V62" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W62" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y62" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA62" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG62" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT62" t="inlineStr"/>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX62" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>128947643</v>
+      </c>
+      <c r="B63" t="n">
+        <v>86902</v>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>473</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>Äggspindling</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>Cortinarius meinhardii</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>Bon</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
+      <c r="P63" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q63" t="n">
+        <v>712289</v>
+      </c>
+      <c r="R63" t="n">
+        <v>6358633</v>
+      </c>
+      <c r="S63" t="n">
+        <v>10</v>
+      </c>
+      <c r="T63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V63" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W63" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y63" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA63" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF63" t="inlineStr"/>
+      <c r="AG63" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT63" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX63" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>128947663</v>
+      </c>
+      <c r="B64" t="n">
+        <v>86875</v>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr"/>
+      <c r="P64" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q64" t="n">
+        <v>712176</v>
+      </c>
+      <c r="R64" t="n">
+        <v>6358409</v>
+      </c>
+      <c r="S64" t="n">
+        <v>10</v>
+      </c>
+      <c r="T64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V64" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W64" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y64" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA64" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF64" t="inlineStr"/>
+      <c r="AG64" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT64" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX64" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>128947666</v>
+      </c>
+      <c r="B65" t="n">
+        <v>86981</v>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E65" t="n">
+        <v>449</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr"/>
+      <c r="P65" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q65" t="n">
+        <v>712159</v>
+      </c>
+      <c r="R65" t="n">
+        <v>6358410</v>
+      </c>
+      <c r="S65" t="n">
+        <v>10</v>
+      </c>
+      <c r="T65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V65" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W65" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y65" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA65" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG65" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT65" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX65" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY65" t="inlineStr"/>
+    </row>
+    <row r="66">
+      <c r="A66" t="n">
+        <v>128947657</v>
+      </c>
+      <c r="B66" t="n">
+        <v>86959</v>
+      </c>
+      <c r="D66" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E66" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="P66" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q66" t="n">
+        <v>712164</v>
+      </c>
+      <c r="R66" t="n">
+        <v>6358415</v>
+      </c>
+      <c r="S66" t="n">
+        <v>10</v>
+      </c>
+      <c r="T66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V66" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W66" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y66" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA66" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF66" t="inlineStr"/>
+      <c r="AG66" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT66" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX66" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY66" t="inlineStr"/>
+    </row>
+    <row r="67">
+      <c r="A67" t="n">
+        <v>128947653</v>
+      </c>
+      <c r="B67" t="n">
+        <v>57713</v>
+      </c>
+      <c r="D67" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E67" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H67" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
+      <c r="P67" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q67" t="n">
+        <v>712303</v>
+      </c>
+      <c r="R67" t="n">
+        <v>6358650</v>
+      </c>
+      <c r="S67" t="n">
+        <v>10</v>
+      </c>
+      <c r="T67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V67" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W67" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y67" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA67" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG67" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT67" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX67" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY67" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" t="n">
+        <v>128947673</v>
+      </c>
+      <c r="B68" t="n">
+        <v>86784</v>
+      </c>
+      <c r="D68" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E68" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H68" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
+      <c r="P68" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q68" t="n">
+        <v>712157</v>
+      </c>
+      <c r="R68" t="n">
+        <v>6358456</v>
+      </c>
+      <c r="S68" t="n">
+        <v>10</v>
+      </c>
+      <c r="T68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V68" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W68" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y68" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA68" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG68" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT68" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX68" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY68" t="inlineStr"/>
+    </row>
+    <row r="69">
+      <c r="A69" t="n">
+        <v>128947645</v>
+      </c>
+      <c r="B69" t="n">
+        <v>87004</v>
+      </c>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E69" t="n">
+        <v>3767</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>Violettfläckig spindling</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H69" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
+      <c r="P69" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q69" t="n">
+        <v>712060</v>
+      </c>
+      <c r="R69" t="n">
+        <v>6358285</v>
+      </c>
+      <c r="S69" t="n">
+        <v>10</v>
+      </c>
+      <c r="T69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V69" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W69" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y69" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA69" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG69" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT69" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX69" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY69" t="inlineStr"/>
+    </row>
+    <row r="70">
+      <c r="A70" t="n">
+        <v>128947670</v>
+      </c>
+      <c r="B70" t="n">
+        <v>86784</v>
+      </c>
+      <c r="D70" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E70" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
+      <c r="P70" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q70" t="n">
+        <v>712289</v>
+      </c>
+      <c r="R70" t="n">
+        <v>6358623</v>
+      </c>
+      <c r="S70" t="n">
+        <v>10</v>
+      </c>
+      <c r="T70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V70" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W70" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y70" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA70" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG70" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT70" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX70" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY70" t="inlineStr"/>
+    </row>
+    <row r="71">
+      <c r="A71" t="n">
+        <v>128947644</v>
+      </c>
+      <c r="B71" t="n">
+        <v>86902</v>
+      </c>
+      <c r="D71" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E71" t="n">
+        <v>473</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>Äggspindling</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>Cortinarius meinhardii</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr">
+        <is>
+          <t>Bon</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
+      <c r="P71" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q71" t="n">
+        <v>712130</v>
+      </c>
+      <c r="R71" t="n">
+        <v>6358403</v>
+      </c>
+      <c r="S71" t="n">
+        <v>10</v>
+      </c>
+      <c r="T71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V71" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W71" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y71" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA71" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG71" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT71" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX71" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY71" t="inlineStr"/>
+    </row>
+    <row r="72">
+      <c r="A72" t="n">
+        <v>128947672</v>
+      </c>
+      <c r="B72" t="n">
+        <v>86784</v>
+      </c>
+      <c r="D72" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E72" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H72" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
+      <c r="P72" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q72" t="n">
+        <v>712269</v>
+      </c>
+      <c r="R72" t="n">
+        <v>6358619</v>
+      </c>
+      <c r="S72" t="n">
+        <v>10</v>
+      </c>
+      <c r="T72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V72" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W72" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y72" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA72" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG72" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT72" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX72" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY72" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY72"/>
+  <dimension ref="A1:AY73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5512,7 +5512,7 @@
         <v>128947652</v>
       </c>
       <c r="B46" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>128947671</v>
       </c>
       <c r="B47" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>128947656</v>
       </c>
       <c r="B48" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>128947660</v>
       </c>
       <c r="B49" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>128947664</v>
       </c>
       <c r="B50" t="n">
-        <v>91923</v>
+        <v>91927</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>128947675</v>
       </c>
       <c r="B51" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>128947674</v>
       </c>
       <c r="B52" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>128947659</v>
       </c>
       <c r="B53" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>128947677</v>
       </c>
       <c r="B54" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>128947676</v>
       </c>
       <c r="B55" t="n">
-        <v>86922</v>
+        <v>86926</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6482,10 +6482,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128947667</v>
+        <v>128947669</v>
       </c>
       <c r="B56" t="n">
-        <v>92830</v>
+        <v>86788</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6493,37 +6493,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5964</v>
+        <v>3712</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>712163</v>
+        <v>712363</v>
       </c>
       <c r="R56" t="n">
-        <v>6358380</v>
+        <v>6358457</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6564,7 +6561,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6583,10 +6579,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128947669</v>
+        <v>128947667</v>
       </c>
       <c r="B57" t="n">
-        <v>86784</v>
+        <v>92834</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6594,34 +6590,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3712</v>
+        <v>5964</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712363</v>
+        <v>712163</v>
       </c>
       <c r="R57" t="n">
-        <v>6358457</v>
+        <v>6358380</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6662,6 +6661,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6683,7 +6683,7 @@
         <v>128947647</v>
       </c>
       <c r="B58" t="n">
-        <v>86982</v>
+        <v>86986</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6777,32 +6777,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128947648</v>
+        <v>128947655</v>
       </c>
       <c r="B59" t="n">
-        <v>86982</v>
+        <v>86764</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>248947</v>
+        <v>3762</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712168</v>
+        <v>712080</v>
       </c>
       <c r="R59" t="n">
-        <v>6358403</v>
+        <v>6358365</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6874,45 +6874,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128947655</v>
+        <v>128947654</v>
       </c>
       <c r="B60" t="n">
-        <v>86760</v>
+        <v>57717</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3762</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712080</v>
+        <v>712106</v>
       </c>
       <c r="R60" t="n">
-        <v>6358365</v>
+        <v>6358348</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6971,10 +6979,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128947649</v>
+        <v>128947648</v>
       </c>
       <c r="B61" t="n">
-        <v>86982</v>
+        <v>86986</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7006,10 +7014,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712051</v>
+        <v>712168</v>
       </c>
       <c r="R61" t="n">
-        <v>6358299</v>
+        <v>6358403</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7068,53 +7076,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128947654</v>
+        <v>128947649</v>
       </c>
       <c r="B62" t="n">
-        <v>57713</v>
+        <v>86986</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>248947</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712106</v>
+        <v>712051</v>
       </c>
       <c r="R62" t="n">
-        <v>6358348</v>
+        <v>6358299</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7176,7 +7176,7 @@
         <v>128947643</v>
       </c>
       <c r="B63" t="n">
-        <v>86902</v>
+        <v>86906</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7271,10 +7271,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128947663</v>
+        <v>128947666</v>
       </c>
       <c r="B64" t="n">
-        <v>86875</v>
+        <v>86985</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7282,21 +7282,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712176</v>
+        <v>712159</v>
       </c>
       <c r="R64" t="n">
-        <v>6358409</v>
+        <v>6358410</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7350,7 +7350,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7369,10 +7368,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128947666</v>
+        <v>128947663</v>
       </c>
       <c r="B65" t="n">
-        <v>86981</v>
+        <v>86879</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7380,21 +7379,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7404,10 +7403,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>712159</v>
+        <v>712176</v>
       </c>
       <c r="R65" t="n">
-        <v>6358410</v>
+        <v>6358409</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7448,6 +7447,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7469,7 +7469,7 @@
         <v>128947657</v>
       </c>
       <c r="B66" t="n">
-        <v>86959</v>
+        <v>86963</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>128947653</v>
       </c>
       <c r="B67" t="n">
-        <v>57713</v>
+        <v>57717</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>128947673</v>
       </c>
       <c r="B68" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>128947645</v>
       </c>
       <c r="B69" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>128947670</v>
       </c>
       <c r="B70" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>128947644</v>
       </c>
       <c r="B71" t="n">
-        <v>86902</v>
+        <v>86906</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>128947672</v>
       </c>
       <c r="B72" t="n">
-        <v>86784</v>
+        <v>86788</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8151,6 +8151,104 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+    </row>
+    <row r="73">
+      <c r="A73" t="n">
+        <v>128947646</v>
+      </c>
+      <c r="B73" t="n">
+        <v>86950</v>
+      </c>
+      <c r="D73" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E73" t="n">
+        <v>3599</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>Narrspindling</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>Cortinarius pseudoarcuatorum</t>
+        </is>
+      </c>
+      <c r="H73" t="inlineStr">
+        <is>
+          <t>Rob.Henry</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
+      <c r="P73" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q73" t="n">
+        <v>712298</v>
+      </c>
+      <c r="R73" t="n">
+        <v>6358625</v>
+      </c>
+      <c r="S73" t="n">
+        <v>10</v>
+      </c>
+      <c r="T73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V73" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W73" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y73" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA73" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF73" t="inlineStr"/>
+      <c r="AG73" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT73" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX73" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY73" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -5703,7 +5703,7 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128947656</v>
+        <v>128947660</v>
       </c>
       <c r="B48" t="n">
         <v>86963</v>
@@ -5738,10 +5738,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>712239</v>
+        <v>712054</v>
       </c>
       <c r="R48" t="n">
-        <v>6358515</v>
+        <v>6358300</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5801,7 +5801,7 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128947660</v>
+        <v>128947656</v>
       </c>
       <c r="B49" t="n">
         <v>86963</v>
@@ -5836,10 +5836,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>712054</v>
+        <v>712239</v>
       </c>
       <c r="R49" t="n">
-        <v>6358300</v>
+        <v>6358515</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5996,10 +5996,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128947675</v>
+        <v>128947674</v>
       </c>
       <c r="B51" t="n">
-        <v>86926</v>
+        <v>86788</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6007,21 +6007,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712229</v>
+        <v>712125</v>
       </c>
       <c r="R51" t="n">
-        <v>6358510</v>
+        <v>6358399</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6093,10 +6093,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128947674</v>
+        <v>128947675</v>
       </c>
       <c r="B52" t="n">
-        <v>86788</v>
+        <v>86926</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6104,21 +6104,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6128,10 +6128,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712125</v>
+        <v>712229</v>
       </c>
       <c r="R52" t="n">
-        <v>6358399</v>
+        <v>6358510</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6482,10 +6482,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128947669</v>
+        <v>128947667</v>
       </c>
       <c r="B56" t="n">
-        <v>86788</v>
+        <v>92834</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6493,34 +6493,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3712</v>
+        <v>5964</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>712363</v>
+        <v>712163</v>
       </c>
       <c r="R56" t="n">
-        <v>6358457</v>
+        <v>6358380</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6561,6 +6564,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6579,10 +6583,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128947667</v>
+        <v>128947669</v>
       </c>
       <c r="B57" t="n">
-        <v>92834</v>
+        <v>86788</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6590,37 +6594,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5964</v>
+        <v>3712</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712163</v>
+        <v>712363</v>
       </c>
       <c r="R57" t="n">
-        <v>6358380</v>
+        <v>6358457</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6661,7 +6662,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7766,32 +7766,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128947645</v>
+        <v>128947670</v>
       </c>
       <c r="B69" t="n">
-        <v>87008</v>
+        <v>86788</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7801,10 +7801,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>712060</v>
+        <v>712289</v>
       </c>
       <c r="R69" t="n">
-        <v>6358285</v>
+        <v>6358623</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7863,32 +7863,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128947670</v>
+        <v>128947645</v>
       </c>
       <c r="B70" t="n">
-        <v>86788</v>
+        <v>87008</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7898,10 +7898,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>712289</v>
+        <v>712060</v>
       </c>
       <c r="R70" t="n">
-        <v>6358623</v>
+        <v>6358285</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY73"/>
+  <dimension ref="A1:AY99"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5899,10 +5899,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128947664</v>
+        <v>128947674</v>
       </c>
       <c r="B50" t="n">
-        <v>91927</v>
+        <v>86788</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5910,21 +5910,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5420</v>
+        <v>3712</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>712272</v>
+        <v>712125</v>
       </c>
       <c r="R50" t="n">
-        <v>6358461</v>
+        <v>6358399</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5996,10 +5996,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128947674</v>
+        <v>128947675</v>
       </c>
       <c r="B51" t="n">
-        <v>86788</v>
+        <v>86926</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6007,21 +6007,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712125</v>
+        <v>712229</v>
       </c>
       <c r="R51" t="n">
-        <v>6358399</v>
+        <v>6358510</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6093,10 +6093,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128947675</v>
+        <v>128947664</v>
       </c>
       <c r="B52" t="n">
-        <v>86926</v>
+        <v>91927</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6104,21 +6104,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3674</v>
+        <v>5420</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6128,10 +6128,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712229</v>
+        <v>712272</v>
       </c>
       <c r="R52" t="n">
-        <v>6358510</v>
+        <v>6358461</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6482,10 +6482,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128947667</v>
+        <v>128947669</v>
       </c>
       <c r="B56" t="n">
-        <v>92834</v>
+        <v>86788</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6493,37 +6493,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5964</v>
+        <v>3712</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>712163</v>
+        <v>712363</v>
       </c>
       <c r="R56" t="n">
-        <v>6358380</v>
+        <v>6358457</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6564,7 +6561,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6583,10 +6579,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128947669</v>
+        <v>128947667</v>
       </c>
       <c r="B57" t="n">
-        <v>86788</v>
+        <v>92834</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6594,34 +6590,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3712</v>
+        <v>5964</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712363</v>
+        <v>712163</v>
       </c>
       <c r="R57" t="n">
-        <v>6358457</v>
+        <v>6358380</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6662,6 +6661,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7564,53 +7564,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128947653</v>
+        <v>128947673</v>
       </c>
       <c r="B67" t="n">
-        <v>57717</v>
+        <v>86788</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>3712</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>712303</v>
+        <v>712157</v>
       </c>
       <c r="R67" t="n">
-        <v>6358650</v>
+        <v>6358456</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7669,45 +7661,53 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128947673</v>
+        <v>128947653</v>
       </c>
       <c r="B68" t="n">
-        <v>86788</v>
+        <v>57717</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3712</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>712157</v>
+        <v>712303</v>
       </c>
       <c r="R68" t="n">
-        <v>6358456</v>
+        <v>6358650</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8250,6 +8250,2799 @@
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>129004213</v>
+      </c>
+      <c r="B74" t="n">
+        <v>86810</v>
+      </c>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E74" t="n">
+        <v>424</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H74" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I74" t="inlineStr"/>
+      <c r="P74" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q74" t="n">
+        <v>712140</v>
+      </c>
+      <c r="R74" t="n">
+        <v>6358430</v>
+      </c>
+      <c r="S74" t="n">
+        <v>10</v>
+      </c>
+      <c r="T74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V74" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W74" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y74" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA74" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG74" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT74" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX74" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY74" t="inlineStr"/>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>129004190</v>
+      </c>
+      <c r="B75" t="n">
+        <v>86986</v>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
+      <c r="P75" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q75" t="n">
+        <v>712178</v>
+      </c>
+      <c r="R75" t="n">
+        <v>6358421</v>
+      </c>
+      <c r="S75" t="n">
+        <v>10</v>
+      </c>
+      <c r="T75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V75" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W75" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y75" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA75" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG75" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT75" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX75" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY75" t="inlineStr"/>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>129004186</v>
+      </c>
+      <c r="B76" t="n">
+        <v>86906</v>
+      </c>
+      <c r="D76" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E76" t="n">
+        <v>473</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>Äggspindling</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>Cortinarius meinhardii</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr">
+        <is>
+          <t>Bon</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="P76" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q76" t="n">
+        <v>712117</v>
+      </c>
+      <c r="R76" t="n">
+        <v>6358397</v>
+      </c>
+      <c r="S76" t="n">
+        <v>10</v>
+      </c>
+      <c r="T76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V76" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W76" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y76" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA76" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG76" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT76" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX76" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY76" t="inlineStr"/>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>129004199</v>
+      </c>
+      <c r="B77" t="n">
+        <v>86963</v>
+      </c>
+      <c r="D77" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E77" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H77" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="P77" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q77" t="n">
+        <v>712133</v>
+      </c>
+      <c r="R77" t="n">
+        <v>6358416</v>
+      </c>
+      <c r="S77" t="n">
+        <v>10</v>
+      </c>
+      <c r="T77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V77" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W77" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y77" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA77" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF77" t="inlineStr"/>
+      <c r="AG77" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT77" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX77" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY77" t="inlineStr"/>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>129004203</v>
+      </c>
+      <c r="B78" t="n">
+        <v>86879</v>
+      </c>
+      <c r="D78" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E78" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H78" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
+      <c r="P78" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q78" t="n">
+        <v>712263</v>
+      </c>
+      <c r="R78" t="n">
+        <v>6358461</v>
+      </c>
+      <c r="S78" t="n">
+        <v>10</v>
+      </c>
+      <c r="T78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V78" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W78" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y78" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA78" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG78" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT78" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX78" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY78" t="inlineStr"/>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>129004215</v>
+      </c>
+      <c r="B79" t="n">
+        <v>86810</v>
+      </c>
+      <c r="D79" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E79" t="n">
+        <v>424</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>Svartgrön spindling</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>Cortinarius atrovirens</t>
+        </is>
+      </c>
+      <c r="H79" t="inlineStr">
+        <is>
+          <t>Kalchbr.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="P79" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q79" t="n">
+        <v>712139</v>
+      </c>
+      <c r="R79" t="n">
+        <v>6358436</v>
+      </c>
+      <c r="S79" t="n">
+        <v>10</v>
+      </c>
+      <c r="T79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V79" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W79" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y79" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AA79" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>12:22</t>
+        </is>
+      </c>
+      <c r="AD79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG79" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT79" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX79" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY79" t="inlineStr"/>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>129004194</v>
+      </c>
+      <c r="B80" t="n">
+        <v>86788</v>
+      </c>
+      <c r="D80" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E80" t="n">
+        <v>3712</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>Blå slemspindling</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>Cortinarius salor</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>Fr.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
+      <c r="P80" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q80" t="n">
+        <v>712133</v>
+      </c>
+      <c r="R80" t="n">
+        <v>6358398</v>
+      </c>
+      <c r="S80" t="n">
+        <v>10</v>
+      </c>
+      <c r="T80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V80" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W80" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y80" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AA80" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>11:24</t>
+        </is>
+      </c>
+      <c r="AD80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG80" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT80" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX80" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY80" t="inlineStr"/>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>129004195</v>
+      </c>
+      <c r="B81" t="n">
+        <v>86940</v>
+      </c>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E81" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
+      <c r="P81" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q81" t="n">
+        <v>712179</v>
+      </c>
+      <c r="R81" t="n">
+        <v>6358417</v>
+      </c>
+      <c r="S81" t="n">
+        <v>10</v>
+      </c>
+      <c r="T81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V81" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W81" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y81" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA81" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF81" t="inlineStr"/>
+      <c r="AG81" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT81" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX81" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY81" t="inlineStr"/>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>129004211</v>
+      </c>
+      <c r="B82" t="n">
+        <v>86985</v>
+      </c>
+      <c r="D82" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E82" t="n">
+        <v>449</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H82" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
+      <c r="P82" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q82" t="n">
+        <v>712141</v>
+      </c>
+      <c r="R82" t="n">
+        <v>6358437</v>
+      </c>
+      <c r="S82" t="n">
+        <v>10</v>
+      </c>
+      <c r="T82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V82" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W82" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y82" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z82" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AA82" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB82" t="inlineStr">
+        <is>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>kollekt</t>
+        </is>
+      </c>
+      <c r="AD82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG82" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT82" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX82" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY82" t="inlineStr"/>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>129004208</v>
+      </c>
+      <c r="B83" t="n">
+        <v>86985</v>
+      </c>
+      <c r="D83" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E83" t="n">
+        <v>449</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H83" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr"/>
+      <c r="P83" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q83" t="n">
+        <v>712234</v>
+      </c>
+      <c r="R83" t="n">
+        <v>6358425</v>
+      </c>
+      <c r="S83" t="n">
+        <v>10</v>
+      </c>
+      <c r="T83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V83" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W83" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y83" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AA83" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>13:39</t>
+        </is>
+      </c>
+      <c r="AD83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG83" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT83" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX83" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY83" t="inlineStr"/>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>129004212</v>
+      </c>
+      <c r="B84" t="n">
+        <v>86985</v>
+      </c>
+      <c r="D84" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E84" t="n">
+        <v>449</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr"/>
+      <c r="P84" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q84" t="n">
+        <v>712167</v>
+      </c>
+      <c r="R84" t="n">
+        <v>6358439</v>
+      </c>
+      <c r="S84" t="n">
+        <v>10</v>
+      </c>
+      <c r="T84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V84" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W84" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y84" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AA84" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>12:42</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Kollekt Tre tydligt i myrstack. en äldre fk hade doft av Skuren rödbeta.</t>
+        </is>
+      </c>
+      <c r="AD84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF84" t="inlineStr"/>
+      <c r="AG84" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT84" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX84" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY84" t="inlineStr"/>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>129004207</v>
+      </c>
+      <c r="B85" t="n">
+        <v>86985</v>
+      </c>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E85" t="n">
+        <v>449</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H85" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
+      <c r="P85" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q85" t="n">
+        <v>712120</v>
+      </c>
+      <c r="R85" t="n">
+        <v>6358399</v>
+      </c>
+      <c r="S85" t="n">
+        <v>10</v>
+      </c>
+      <c r="T85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V85" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W85" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y85" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA85" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG85" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT85" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX85" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>129004210</v>
+      </c>
+      <c r="B86" t="n">
+        <v>86985</v>
+      </c>
+      <c r="D86" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E86" t="n">
+        <v>449</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I86" t="inlineStr"/>
+      <c r="P86" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q86" t="n">
+        <v>712140</v>
+      </c>
+      <c r="R86" t="n">
+        <v>6358434</v>
+      </c>
+      <c r="S86" t="n">
+        <v>10</v>
+      </c>
+      <c r="T86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V86" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W86" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y86" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AA86" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>12:07</t>
+        </is>
+      </c>
+      <c r="AD86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG86" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT86" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX86" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>129004192</v>
+      </c>
+      <c r="B87" t="n">
+        <v>110763</v>
+      </c>
+      <c r="D87" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E87" t="n">
+        <v>219711</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>Sårläka</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>Sanicula europaea</t>
+        </is>
+      </c>
+      <c r="H87" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
+      <c r="P87" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q87" t="n">
+        <v>712118</v>
+      </c>
+      <c r="R87" t="n">
+        <v>6358398</v>
+      </c>
+      <c r="S87" t="n">
+        <v>10</v>
+      </c>
+      <c r="T87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V87" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W87" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y87" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AA87" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>11:22</t>
+        </is>
+      </c>
+      <c r="AD87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG87" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT87" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX87" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>129004202</v>
+      </c>
+      <c r="B88" t="n">
+        <v>90924</v>
+      </c>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E88" t="n">
+        <v>1000938</v>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>Geastrum</t>
+        </is>
+      </c>
+      <c r="H88" t="inlineStr">
+        <is>
+          <t>Pers.:Pers.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
+      <c r="P88" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q88" t="n">
+        <v>712196</v>
+      </c>
+      <c r="R88" t="n">
+        <v>6358401</v>
+      </c>
+      <c r="S88" t="n">
+        <v>10</v>
+      </c>
+      <c r="T88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V88" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W88" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y88" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA88" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF88" t="inlineStr"/>
+      <c r="AG88" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT88" t="inlineStr"/>
+      <c r="AW88" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX88" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY88" t="inlineStr"/>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>129004200</v>
+      </c>
+      <c r="B89" t="n">
+        <v>86963</v>
+      </c>
+      <c r="D89" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E89" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr"/>
+      <c r="P89" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q89" t="n">
+        <v>712116</v>
+      </c>
+      <c r="R89" t="n">
+        <v>6358338</v>
+      </c>
+      <c r="S89" t="n">
+        <v>10</v>
+      </c>
+      <c r="T89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V89" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W89" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y89" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA89" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF89" t="inlineStr"/>
+      <c r="AG89" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT89" t="inlineStr"/>
+      <c r="AW89" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX89" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>129004204</v>
+      </c>
+      <c r="B90" t="n">
+        <v>86879</v>
+      </c>
+      <c r="D90" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E90" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
+      <c r="P90" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q90" t="n">
+        <v>712180</v>
+      </c>
+      <c r="R90" t="n">
+        <v>6358430</v>
+      </c>
+      <c r="S90" t="n">
+        <v>10</v>
+      </c>
+      <c r="T90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V90" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W90" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y90" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA90" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG90" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT90" t="inlineStr"/>
+      <c r="AW90" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX90" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>129004206</v>
+      </c>
+      <c r="B91" t="n">
+        <v>86985</v>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E91" t="n">
+        <v>449</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H91" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
+      <c r="P91" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q91" t="n">
+        <v>712178</v>
+      </c>
+      <c r="R91" t="n">
+        <v>6358418</v>
+      </c>
+      <c r="S91" t="n">
+        <v>10</v>
+      </c>
+      <c r="T91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V91" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W91" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y91" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AA91" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>13:00</t>
+        </is>
+      </c>
+      <c r="AD91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG91" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT91" t="inlineStr"/>
+      <c r="AW91" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX91" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY91" t="inlineStr"/>
+    </row>
+    <row r="92">
+      <c r="A92" t="n">
+        <v>129004193</v>
+      </c>
+      <c r="B92" t="n">
+        <v>90306</v>
+      </c>
+      <c r="D92" t="inlineStr">
+        <is>
+          <t>EN</t>
+        </is>
+      </c>
+      <c r="E92" t="n">
+        <v>2072</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>Sienamusseron</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>Tricholoma joachimii</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>Bon &amp; A.Riva</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
+      <c r="P92" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q92" t="n">
+        <v>712067</v>
+      </c>
+      <c r="R92" t="n">
+        <v>6358371</v>
+      </c>
+      <c r="S92" t="n">
+        <v>10</v>
+      </c>
+      <c r="T92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V92" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W92" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y92" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AA92" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>10:47</t>
+        </is>
+      </c>
+      <c r="AD92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF92" t="inlineStr"/>
+      <c r="AG92" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT92" t="inlineStr"/>
+      <c r="AW92" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX92" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY92" t="inlineStr"/>
+    </row>
+    <row r="93">
+      <c r="A93" t="n">
+        <v>129004209</v>
+      </c>
+      <c r="B93" t="n">
+        <v>86985</v>
+      </c>
+      <c r="D93" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E93" t="n">
+        <v>449</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I93" t="inlineStr"/>
+      <c r="P93" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q93" t="n">
+        <v>712185</v>
+      </c>
+      <c r="R93" t="n">
+        <v>6358414</v>
+      </c>
+      <c r="S93" t="n">
+        <v>10</v>
+      </c>
+      <c r="T93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V93" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W93" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y93" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AA93" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>13:17</t>
+        </is>
+      </c>
+      <c r="AD93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG93" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT93" t="inlineStr"/>
+      <c r="AW93" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX93" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY93" t="inlineStr"/>
+    </row>
+    <row r="94">
+      <c r="A94" t="n">
+        <v>129004191</v>
+      </c>
+      <c r="B94" t="n">
+        <v>86986</v>
+      </c>
+      <c r="D94" t="inlineStr">
+        <is>
+          <t>DD</t>
+        </is>
+      </c>
+      <c r="E94" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H94" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
+      <c r="P94" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q94" t="n">
+        <v>712118</v>
+      </c>
+      <c r="R94" t="n">
+        <v>6358397</v>
+      </c>
+      <c r="S94" t="n">
+        <v>10</v>
+      </c>
+      <c r="T94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V94" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W94" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y94" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA94" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG94" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT94" t="inlineStr"/>
+      <c r="AW94" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX94" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY94" t="inlineStr"/>
+    </row>
+    <row r="95">
+      <c r="A95" t="n">
+        <v>129004188</v>
+      </c>
+      <c r="B95" t="n">
+        <v>87008</v>
+      </c>
+      <c r="D95" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E95" t="n">
+        <v>3767</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>Violettfläckig spindling</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
+      <c r="P95" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q95" t="n">
+        <v>712181</v>
+      </c>
+      <c r="R95" t="n">
+        <v>6358403</v>
+      </c>
+      <c r="S95" t="n">
+        <v>10</v>
+      </c>
+      <c r="T95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V95" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W95" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y95" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AA95" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>13:31</t>
+        </is>
+      </c>
+      <c r="AD95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG95" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT95" t="inlineStr"/>
+      <c r="AW95" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX95" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY95" t="inlineStr"/>
+    </row>
+    <row r="96">
+      <c r="A96" t="n">
+        <v>129004214</v>
+      </c>
+      <c r="B96" t="n">
+        <v>86926</v>
+      </c>
+      <c r="D96" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E96" t="n">
+        <v>3674</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>Anisspindling</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>Cortinarius odorifer</t>
+        </is>
+      </c>
+      <c r="H96" t="inlineStr">
+        <is>
+          <t>Britzelm.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
+      <c r="P96" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q96" t="n">
+        <v>712132</v>
+      </c>
+      <c r="R96" t="n">
+        <v>6358416</v>
+      </c>
+      <c r="S96" t="n">
+        <v>10</v>
+      </c>
+      <c r="T96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V96" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W96" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y96" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA96" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG96" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT96" t="inlineStr"/>
+      <c r="AW96" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX96" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY96" t="inlineStr"/>
+    </row>
+    <row r="97">
+      <c r="A97" t="n">
+        <v>129004205</v>
+      </c>
+      <c r="B97" t="n">
+        <v>86985</v>
+      </c>
+      <c r="D97" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E97" t="n">
+        <v>449</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>Granrotspindling</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>Cortinarius subfraudulosus</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>Kytöv. &amp; al.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
+      <c r="P97" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q97" t="n">
+        <v>712139</v>
+      </c>
+      <c r="R97" t="n">
+        <v>6358437</v>
+      </c>
+      <c r="S97" t="n">
+        <v>10</v>
+      </c>
+      <c r="T97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V97" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W97" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y97" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AA97" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>11:33</t>
+        </is>
+      </c>
+      <c r="AD97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG97" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT97" t="inlineStr"/>
+      <c r="AW97" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX97" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY97" t="inlineStr"/>
+    </row>
+    <row r="98">
+      <c r="A98" t="n">
+        <v>129004201</v>
+      </c>
+      <c r="B98" t="n">
+        <v>86855</v>
+      </c>
+      <c r="D98" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E98" t="n">
+        <v>445</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>Kopparspindling</t>
+        </is>
+      </c>
+      <c r="G98" t="inlineStr">
+        <is>
+          <t>Cortinarius cupreorufus</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr"/>
+      <c r="P98" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q98" t="n">
+        <v>712185</v>
+      </c>
+      <c r="R98" t="n">
+        <v>6358418</v>
+      </c>
+      <c r="S98" t="n">
+        <v>10</v>
+      </c>
+      <c r="T98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V98" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W98" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y98" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AA98" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>13:22</t>
+        </is>
+      </c>
+      <c r="AD98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG98" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT98" t="inlineStr"/>
+      <c r="AW98" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX98" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY98" t="inlineStr"/>
+    </row>
+    <row r="99">
+      <c r="A99" t="n">
+        <v>129004187</v>
+      </c>
+      <c r="B99" t="n">
+        <v>87008</v>
+      </c>
+      <c r="D99" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E99" t="n">
+        <v>3767</v>
+      </c>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>Violettfläckig spindling</t>
+        </is>
+      </c>
+      <c r="G99" t="inlineStr">
+        <is>
+          <t>Cortinarius violaceomaculatus</t>
+        </is>
+      </c>
+      <c r="H99" t="inlineStr">
+        <is>
+          <t>Brandrud</t>
+        </is>
+      </c>
+      <c r="I99" t="inlineStr"/>
+      <c r="P99" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q99" t="n">
+        <v>712224</v>
+      </c>
+      <c r="R99" t="n">
+        <v>6358420</v>
+      </c>
+      <c r="S99" t="n">
+        <v>10</v>
+      </c>
+      <c r="T99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V99" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W99" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y99" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AA99" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>13:37</t>
+        </is>
+      </c>
+      <c r="AD99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG99" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT99" t="inlineStr"/>
+      <c r="AW99" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX99" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY99" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -5512,7 +5512,7 @@
         <v>128947652</v>
       </c>
       <c r="B46" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>128947671</v>
       </c>
       <c r="B47" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5703,10 +5703,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>128947660</v>
+        <v>128947656</v>
       </c>
       <c r="B48" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5738,10 +5738,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>712054</v>
+        <v>712239</v>
       </c>
       <c r="R48" t="n">
-        <v>6358300</v>
+        <v>6358515</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5801,10 +5801,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>128947656</v>
+        <v>128947660</v>
       </c>
       <c r="B49" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5836,10 +5836,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>712239</v>
+        <v>712054</v>
       </c>
       <c r="R49" t="n">
-        <v>6358515</v>
+        <v>6358300</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5902,7 +5902,7 @@
         <v>128947674</v>
       </c>
       <c r="B50" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>128947675</v>
       </c>
       <c r="B51" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>128947664</v>
       </c>
       <c r="B52" t="n">
-        <v>91927</v>
+        <v>91932</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>128947659</v>
       </c>
       <c r="B53" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>128947677</v>
       </c>
       <c r="B54" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>128947676</v>
       </c>
       <c r="B55" t="n">
-        <v>86926</v>
+        <v>86931</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>128947669</v>
       </c>
       <c r="B56" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>128947667</v>
       </c>
       <c r="B57" t="n">
-        <v>92834</v>
+        <v>92839</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>128947647</v>
       </c>
       <c r="B58" t="n">
-        <v>86986</v>
+        <v>86991</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>128947655</v>
       </c>
       <c r="B59" t="n">
-        <v>86764</v>
+        <v>86769</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>128947654</v>
       </c>
       <c r="B60" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>128947648</v>
       </c>
       <c r="B61" t="n">
-        <v>86986</v>
+        <v>86991</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>128947649</v>
       </c>
       <c r="B62" t="n">
-        <v>86986</v>
+        <v>86991</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>128947643</v>
       </c>
       <c r="B63" t="n">
-        <v>86906</v>
+        <v>86911</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7271,10 +7271,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128947666</v>
+        <v>128947663</v>
       </c>
       <c r="B64" t="n">
-        <v>86985</v>
+        <v>86884</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7282,21 +7282,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712159</v>
+        <v>712176</v>
       </c>
       <c r="R64" t="n">
-        <v>6358410</v>
+        <v>6358409</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7350,6 +7350,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7368,10 +7369,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128947663</v>
+        <v>128947666</v>
       </c>
       <c r="B65" t="n">
-        <v>86879</v>
+        <v>86990</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7379,21 +7380,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7403,10 +7404,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>712176</v>
+        <v>712159</v>
       </c>
       <c r="R65" t="n">
-        <v>6358409</v>
+        <v>6358410</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7447,7 +7448,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7469,7 +7469,7 @@
         <v>128947657</v>
       </c>
       <c r="B66" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>128947673</v>
       </c>
       <c r="B67" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>128947653</v>
       </c>
       <c r="B68" t="n">
-        <v>57717</v>
+        <v>57720</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7769,7 +7769,7 @@
         <v>128947670</v>
       </c>
       <c r="B69" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>128947645</v>
       </c>
       <c r="B70" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>128947644</v>
       </c>
       <c r="B71" t="n">
-        <v>86906</v>
+        <v>86911</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>128947672</v>
       </c>
       <c r="B72" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>128947646</v>
       </c>
       <c r="B73" t="n">
-        <v>86950</v>
+        <v>86955</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>129004213</v>
       </c>
       <c r="B74" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>129004190</v>
       </c>
       <c r="B75" t="n">
-        <v>86986</v>
+        <v>86991</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>129004186</v>
       </c>
       <c r="B76" t="n">
-        <v>86906</v>
+        <v>86911</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>129004199</v>
       </c>
       <c r="B77" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>129004203</v>
       </c>
       <c r="B78" t="n">
-        <v>86879</v>
+        <v>86884</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>129004215</v>
       </c>
       <c r="B79" t="n">
-        <v>86810</v>
+        <v>86815</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>129004194</v>
       </c>
       <c r="B80" t="n">
-        <v>86788</v>
+        <v>86793</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9002,32 +9002,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129004195</v>
+        <v>129004211</v>
       </c>
       <c r="B81" t="n">
-        <v>86940</v>
+        <v>86990</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>249228</v>
+        <v>449</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9037,10 +9037,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>712179</v>
+        <v>712141</v>
       </c>
       <c r="R81" t="n">
-        <v>6358417</v>
+        <v>6358437</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9082,7 +9082,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>kollekt</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9091,7 +9096,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9110,32 +9114,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129004211</v>
+        <v>129004195</v>
       </c>
       <c r="B82" t="n">
-        <v>86985</v>
+        <v>86945</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>449</v>
+        <v>249228</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9145,10 +9149,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>712141</v>
+        <v>712179</v>
       </c>
       <c r="R82" t="n">
-        <v>6358437</v>
+        <v>6358417</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9180,7 +9184,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9190,12 +9194,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>kollekt</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9204,6 +9203,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9225,7 +9225,7 @@
         <v>129004208</v>
       </c>
       <c r="B83" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>129004212</v>
       </c>
       <c r="B84" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>129004207</v>
       </c>
       <c r="B85" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>129004210</v>
       </c>
       <c r="B86" t="n">
-        <v>86985</v>
+        <v>86990</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>129004192</v>
       </c>
       <c r="B87" t="n">
-        <v>110763</v>
+        <v>110771</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>129004202</v>
       </c>
       <c r="B88" t="n">
-        <v>90924</v>
+        <v>90929</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>129004200</v>
       </c>
       <c r="B89" t="n">
-        <v>86963</v>
+        <v>86968</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9974,10 +9974,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129004204</v>
+        <v>129004206</v>
       </c>
       <c r="B90" t="n">
-        <v>86879</v>
+        <v>86990</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9985,21 +9985,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10009,10 +10009,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>712180</v>
+        <v>712178</v>
       </c>
       <c r="R90" t="n">
-        <v>6358430</v>
+        <v>6358418</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10081,10 +10081,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129004206</v>
+        <v>129004204</v>
       </c>
       <c r="B91" t="n">
-        <v>86985</v>
+        <v>86884</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10092,21 +10092,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10116,10 +10116,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>712178</v>
+        <v>712180</v>
       </c>
       <c r="R91" t="n">
-        <v>6358418</v>
+        <v>6358430</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10188,32 +10188,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129004193</v>
+        <v>129004209</v>
       </c>
       <c r="B92" t="n">
-        <v>90306</v>
+        <v>86990</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2072</v>
+        <v>449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>712067</v>
+        <v>712185</v>
       </c>
       <c r="R92" t="n">
-        <v>6358371</v>
+        <v>6358414</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10277,7 +10277,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10296,32 +10295,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129004209</v>
+        <v>129004193</v>
       </c>
       <c r="B93" t="n">
-        <v>86985</v>
+        <v>90311</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>449</v>
+        <v>2072</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10331,10 +10330,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>712185</v>
+        <v>712067</v>
       </c>
       <c r="R93" t="n">
-        <v>6358414</v>
+        <v>6358371</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10366,7 +10365,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10376,7 +10375,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10385,6 +10384,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10403,32 +10403,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129004191</v>
+        <v>129004188</v>
       </c>
       <c r="B94" t="n">
-        <v>86986</v>
+        <v>87013</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>248947</v>
+        <v>3767</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10438,10 +10438,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>712118</v>
+        <v>712181</v>
       </c>
       <c r="R94" t="n">
-        <v>6358397</v>
+        <v>6358403</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10510,32 +10510,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129004188</v>
+        <v>129004191</v>
       </c>
       <c r="B95" t="n">
-        <v>87008</v>
+        <v>86991</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3767</v>
+        <v>248947</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10545,10 +10545,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>712181</v>
+        <v>712118</v>
       </c>
       <c r="R95" t="n">
-        <v>6358403</v>
+        <v>6358397</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10617,32 +10617,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129004214</v>
+        <v>129004205</v>
       </c>
       <c r="B96" t="n">
-        <v>86926</v>
+        <v>86990</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10652,10 +10652,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>712132</v>
+        <v>712139</v>
       </c>
       <c r="R96" t="n">
-        <v>6358416</v>
+        <v>6358437</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10724,10 +10724,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129004205</v>
+        <v>129004201</v>
       </c>
       <c r="B97" t="n">
-        <v>86985</v>
+        <v>86860</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10735,21 +10735,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>449</v>
+        <v>445</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10759,10 +10759,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>712139</v>
+        <v>712185</v>
       </c>
       <c r="R97" t="n">
-        <v>6358437</v>
+        <v>6358418</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10831,32 +10831,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129004201</v>
+        <v>129004214</v>
       </c>
       <c r="B98" t="n">
-        <v>86855</v>
+        <v>86931</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>445</v>
+        <v>3674</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10866,10 +10866,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>712185</v>
+        <v>712132</v>
       </c>
       <c r="R98" t="n">
-        <v>6358418</v>
+        <v>6358416</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10941,7 +10941,7 @@
         <v>129004187</v>
       </c>
       <c r="B99" t="n">
-        <v>87008</v>
+        <v>87013</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -6874,53 +6874,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128947654</v>
+        <v>128947648</v>
       </c>
       <c r="B60" t="n">
-        <v>57720</v>
+        <v>86998</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>248947</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712106</v>
+        <v>712168</v>
       </c>
       <c r="R60" t="n">
-        <v>6358348</v>
+        <v>6358403</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6979,7 +6971,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128947648</v>
+        <v>128947649</v>
       </c>
       <c r="B61" t="n">
         <v>86998</v>
@@ -7014,10 +7006,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712168</v>
+        <v>712051</v>
       </c>
       <c r="R61" t="n">
-        <v>6358403</v>
+        <v>6358299</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7076,45 +7068,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128947649</v>
+        <v>128947654</v>
       </c>
       <c r="B62" t="n">
-        <v>86998</v>
+        <v>57720</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>248947</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712051</v>
+        <v>712106</v>
       </c>
       <c r="R62" t="n">
-        <v>6358299</v>
+        <v>6358348</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -8252,32 +8252,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129004213</v>
+        <v>129004190</v>
       </c>
       <c r="B74" t="n">
-        <v>86822</v>
+        <v>86998</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>424</v>
+        <v>248947</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>712140</v>
+        <v>712178</v>
       </c>
       <c r="R74" t="n">
-        <v>6358430</v>
+        <v>6358421</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8359,32 +8359,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129004190</v>
+        <v>129004213</v>
       </c>
       <c r="B75" t="n">
-        <v>86998</v>
+        <v>86822</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>248947</v>
+        <v>424</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8394,10 +8394,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>712178</v>
+        <v>712140</v>
       </c>
       <c r="R75" t="n">
-        <v>6358421</v>
+        <v>6358430</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8788,32 +8788,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129004215</v>
+        <v>129004194</v>
       </c>
       <c r="B79" t="n">
-        <v>86822</v>
+        <v>86800</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>712139</v>
+        <v>712133</v>
       </c>
       <c r="R79" t="n">
-        <v>6358436</v>
+        <v>6358398</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8895,32 +8895,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129004194</v>
+        <v>129004215</v>
       </c>
       <c r="B80" t="n">
-        <v>86800</v>
+        <v>86822</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>712133</v>
+        <v>712139</v>
       </c>
       <c r="R80" t="n">
-        <v>6358398</v>
+        <v>6358436</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD80" t="b">

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -5512,7 +5512,7 @@
         <v>128947652</v>
       </c>
       <c r="B46" t="n">
-        <v>86822</v>
+        <v>86825</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>128947671</v>
       </c>
       <c r="B47" t="n">
-        <v>86800</v>
+        <v>86803</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>128947656</v>
       </c>
       <c r="B48" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>128947660</v>
       </c>
       <c r="B49" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>128947675</v>
       </c>
       <c r="B50" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>128947674</v>
       </c>
       <c r="B51" t="n">
-        <v>86800</v>
+        <v>86803</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>128947664</v>
       </c>
       <c r="B52" t="n">
-        <v>91940</v>
+        <v>91943</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>128947659</v>
       </c>
       <c r="B53" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>128947677</v>
       </c>
       <c r="B54" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>128947676</v>
       </c>
       <c r="B55" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6482,10 +6482,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128947667</v>
+        <v>128947669</v>
       </c>
       <c r="B56" t="n">
-        <v>92847</v>
+        <v>86803</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6493,37 +6493,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5964</v>
+        <v>3712</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>712163</v>
+        <v>712363</v>
       </c>
       <c r="R56" t="n">
-        <v>6358380</v>
+        <v>6358457</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6564,7 +6561,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6583,10 +6579,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128947669</v>
+        <v>128947667</v>
       </c>
       <c r="B57" t="n">
-        <v>86800</v>
+        <v>92852</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6594,34 +6590,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3712</v>
+        <v>5964</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712363</v>
+        <v>712163</v>
       </c>
       <c r="R57" t="n">
-        <v>6358457</v>
+        <v>6358380</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6662,6 +6661,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6683,7 +6683,7 @@
         <v>128947647</v>
       </c>
       <c r="B58" t="n">
-        <v>86998</v>
+        <v>87001</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>128947655</v>
       </c>
       <c r="B59" t="n">
-        <v>86776</v>
+        <v>86779</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6874,45 +6874,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128947648</v>
+        <v>128947654</v>
       </c>
       <c r="B60" t="n">
-        <v>86998</v>
+        <v>57720</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>248947</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712168</v>
+        <v>712106</v>
       </c>
       <c r="R60" t="n">
-        <v>6358403</v>
+        <v>6358348</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6971,10 +6979,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128947649</v>
+        <v>128947648</v>
       </c>
       <c r="B61" t="n">
-        <v>86998</v>
+        <v>87001</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7006,10 +7014,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712051</v>
+        <v>712168</v>
       </c>
       <c r="R61" t="n">
-        <v>6358299</v>
+        <v>6358403</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7068,53 +7076,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128947654</v>
+        <v>128947649</v>
       </c>
       <c r="B62" t="n">
-        <v>57720</v>
+        <v>87001</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>248947</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712106</v>
+        <v>712051</v>
       </c>
       <c r="R62" t="n">
-        <v>6358348</v>
+        <v>6358299</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7176,7 +7176,7 @@
         <v>128947643</v>
       </c>
       <c r="B63" t="n">
-        <v>86918</v>
+        <v>86921</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>128947666</v>
       </c>
       <c r="B64" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>128947663</v>
       </c>
       <c r="B65" t="n">
-        <v>86891</v>
+        <v>86894</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>128947657</v>
       </c>
       <c r="B66" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7564,45 +7564,53 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128947673</v>
+        <v>128947653</v>
       </c>
       <c r="B67" t="n">
-        <v>86800</v>
+        <v>57720</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3712</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>712157</v>
+        <v>712303</v>
       </c>
       <c r="R67" t="n">
-        <v>6358456</v>
+        <v>6358650</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7661,53 +7669,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128947653</v>
+        <v>128947673</v>
       </c>
       <c r="B68" t="n">
-        <v>57720</v>
+        <v>86803</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>3712</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>712303</v>
+        <v>712157</v>
       </c>
       <c r="R68" t="n">
-        <v>6358650</v>
+        <v>6358456</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7766,32 +7766,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128947645</v>
+        <v>128947670</v>
       </c>
       <c r="B69" t="n">
-        <v>87020</v>
+        <v>86803</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7801,10 +7801,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>712060</v>
+        <v>712289</v>
       </c>
       <c r="R69" t="n">
-        <v>6358285</v>
+        <v>6358623</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7863,32 +7863,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128947670</v>
+        <v>128947645</v>
       </c>
       <c r="B70" t="n">
-        <v>86800</v>
+        <v>87023</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7898,10 +7898,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>712289</v>
+        <v>712060</v>
       </c>
       <c r="R70" t="n">
-        <v>6358623</v>
+        <v>6358285</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7963,7 +7963,7 @@
         <v>128947644</v>
       </c>
       <c r="B71" t="n">
-        <v>86918</v>
+        <v>86921</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>128947672</v>
       </c>
       <c r="B72" t="n">
-        <v>86800</v>
+        <v>86803</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>128947646</v>
       </c>
       <c r="B73" t="n">
-        <v>86962</v>
+        <v>86965</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8252,32 +8252,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129004190</v>
+        <v>129004213</v>
       </c>
       <c r="B74" t="n">
-        <v>86998</v>
+        <v>86825</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>248947</v>
+        <v>424</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>712178</v>
+        <v>712140</v>
       </c>
       <c r="R74" t="n">
-        <v>6358421</v>
+        <v>6358430</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8359,32 +8359,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129004213</v>
+        <v>129004190</v>
       </c>
       <c r="B75" t="n">
-        <v>86822</v>
+        <v>87001</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>424</v>
+        <v>248947</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8394,10 +8394,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>712140</v>
+        <v>712178</v>
       </c>
       <c r="R75" t="n">
-        <v>6358430</v>
+        <v>6358421</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8469,7 +8469,7 @@
         <v>129004186</v>
       </c>
       <c r="B76" t="n">
-        <v>86918</v>
+        <v>86921</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>129004199</v>
       </c>
       <c r="B77" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>129004203</v>
       </c>
       <c r="B78" t="n">
-        <v>86891</v>
+        <v>86894</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8788,32 +8788,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129004194</v>
+        <v>129004215</v>
       </c>
       <c r="B79" t="n">
-        <v>86800</v>
+        <v>86825</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>712133</v>
+        <v>712139</v>
       </c>
       <c r="R79" t="n">
-        <v>6358398</v>
+        <v>6358436</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8895,32 +8895,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129004215</v>
+        <v>129004194</v>
       </c>
       <c r="B80" t="n">
-        <v>86822</v>
+        <v>86803</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>712139</v>
+        <v>712133</v>
       </c>
       <c r="R80" t="n">
-        <v>6358436</v>
+        <v>6358398</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9005,7 +9005,7 @@
         <v>129004211</v>
       </c>
       <c r="B81" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>129004195</v>
       </c>
       <c r="B82" t="n">
-        <v>86952</v>
+        <v>86955</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>129004208</v>
       </c>
       <c r="B83" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>129004212</v>
       </c>
       <c r="B84" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>129004207</v>
       </c>
       <c r="B85" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>129004210</v>
       </c>
       <c r="B86" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>129004192</v>
       </c>
       <c r="B87" t="n">
-        <v>110779</v>
+        <v>110784</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>129004202</v>
       </c>
       <c r="B88" t="n">
-        <v>90936</v>
+        <v>90939</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>129004200</v>
       </c>
       <c r="B89" t="n">
-        <v>86975</v>
+        <v>86978</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>129004206</v>
       </c>
       <c r="B90" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>129004204</v>
       </c>
       <c r="B91" t="n">
-        <v>86891</v>
+        <v>86894</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>129004209</v>
       </c>
       <c r="B92" t="n">
-        <v>86997</v>
+        <v>87000</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>129004193</v>
       </c>
       <c r="B93" t="n">
-        <v>90318</v>
+        <v>90321</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>129004188</v>
       </c>
       <c r="B94" t="n">
-        <v>87020</v>
+        <v>87023</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>129004191</v>
       </c>
       <c r="B95" t="n">
-        <v>86998</v>
+        <v>87001</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10617,32 +10617,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129004214</v>
+        <v>129004205</v>
       </c>
       <c r="B96" t="n">
-        <v>86938</v>
+        <v>87000</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10652,10 +10652,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>712132</v>
+        <v>712139</v>
       </c>
       <c r="R96" t="n">
-        <v>6358416</v>
+        <v>6358437</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10724,10 +10724,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129004187</v>
+        <v>129004201</v>
       </c>
       <c r="B97" t="n">
-        <v>87020</v>
+        <v>86870</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10735,16 +10735,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3767</v>
+        <v>445</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10759,10 +10759,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>712224</v>
+        <v>712185</v>
       </c>
       <c r="R97" t="n">
-        <v>6358420</v>
+        <v>6358418</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10831,32 +10831,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129004201</v>
+        <v>129004214</v>
       </c>
       <c r="B98" t="n">
-        <v>86867</v>
+        <v>86941</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>445</v>
+        <v>3674</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10866,10 +10866,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>712185</v>
+        <v>712132</v>
       </c>
       <c r="R98" t="n">
-        <v>6358418</v>
+        <v>6358416</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10938,10 +10938,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129004205</v>
+        <v>129004187</v>
       </c>
       <c r="B99" t="n">
-        <v>86997</v>
+        <v>87023</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10949,21 +10949,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10973,10 +10973,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>712139</v>
+        <v>712224</v>
       </c>
       <c r="R99" t="n">
-        <v>6358437</v>
+        <v>6358420</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD99" t="b">

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -5509,32 +5509,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128947652</v>
+        <v>128947671</v>
       </c>
       <c r="B46" t="n">
-        <v>86825</v>
+        <v>86806</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>712290</v>
+        <v>712289</v>
       </c>
       <c r="R46" t="n">
         <v>6358633</v>
@@ -5606,32 +5606,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128947671</v>
+        <v>128947652</v>
       </c>
       <c r="B47" t="n">
-        <v>86803</v>
+        <v>86828</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>712289</v>
+        <v>712290</v>
       </c>
       <c r="R47" t="n">
         <v>6358633</v>
@@ -5706,7 +5706,7 @@
         <v>128947656</v>
       </c>
       <c r="B48" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>128947660</v>
       </c>
       <c r="B49" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5899,10 +5899,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128947675</v>
+        <v>128947664</v>
       </c>
       <c r="B50" t="n">
-        <v>86941</v>
+        <v>91946</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5910,21 +5910,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3674</v>
+        <v>5420</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>712229</v>
+        <v>712272</v>
       </c>
       <c r="R50" t="n">
-        <v>6358510</v>
+        <v>6358461</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5996,10 +5996,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128947674</v>
+        <v>128947675</v>
       </c>
       <c r="B51" t="n">
-        <v>86803</v>
+        <v>86944</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6007,21 +6007,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712125</v>
+        <v>712229</v>
       </c>
       <c r="R51" t="n">
-        <v>6358399</v>
+        <v>6358510</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6093,10 +6093,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128947664</v>
+        <v>128947674</v>
       </c>
       <c r="B52" t="n">
-        <v>91943</v>
+        <v>86806</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6104,21 +6104,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5420</v>
+        <v>3712</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6128,10 +6128,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712272</v>
+        <v>712125</v>
       </c>
       <c r="R52" t="n">
-        <v>6358461</v>
+        <v>6358399</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6193,7 +6193,7 @@
         <v>128947659</v>
       </c>
       <c r="B53" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>128947677</v>
       </c>
       <c r="B54" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>128947676</v>
       </c>
       <c r="B55" t="n">
-        <v>86941</v>
+        <v>86944</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6482,10 +6482,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128947669</v>
+        <v>128947667</v>
       </c>
       <c r="B56" t="n">
-        <v>86803</v>
+        <v>92855</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6493,34 +6493,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3712</v>
+        <v>5964</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>712363</v>
+        <v>712163</v>
       </c>
       <c r="R56" t="n">
-        <v>6358457</v>
+        <v>6358380</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6561,6 +6564,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6579,10 +6583,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128947667</v>
+        <v>128947669</v>
       </c>
       <c r="B57" t="n">
-        <v>92852</v>
+        <v>86806</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6590,37 +6594,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5964</v>
+        <v>3712</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712163</v>
+        <v>712363</v>
       </c>
       <c r="R57" t="n">
-        <v>6358380</v>
+        <v>6358457</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6661,7 +6662,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6683,7 +6683,7 @@
         <v>128947647</v>
       </c>
       <c r="B58" t="n">
-        <v>87001</v>
+        <v>87004</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>128947655</v>
       </c>
       <c r="B59" t="n">
-        <v>86779</v>
+        <v>86782</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6874,53 +6874,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128947654</v>
+        <v>128947648</v>
       </c>
       <c r="B60" t="n">
-        <v>57720</v>
+        <v>87004</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>248947</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712106</v>
+        <v>712168</v>
       </c>
       <c r="R60" t="n">
-        <v>6358348</v>
+        <v>6358403</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6979,10 +6971,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128947648</v>
+        <v>128947649</v>
       </c>
       <c r="B61" t="n">
-        <v>87001</v>
+        <v>87004</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7014,10 +7006,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712168</v>
+        <v>712051</v>
       </c>
       <c r="R61" t="n">
-        <v>6358403</v>
+        <v>6358299</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7076,45 +7068,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128947649</v>
+        <v>128947654</v>
       </c>
       <c r="B62" t="n">
-        <v>87001</v>
+        <v>57720</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>248947</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712051</v>
+        <v>712106</v>
       </c>
       <c r="R62" t="n">
-        <v>6358299</v>
+        <v>6358348</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7176,7 +7176,7 @@
         <v>128947643</v>
       </c>
       <c r="B63" t="n">
-        <v>86921</v>
+        <v>86924</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>128947666</v>
       </c>
       <c r="B64" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>128947663</v>
       </c>
       <c r="B65" t="n">
-        <v>86894</v>
+        <v>86897</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>128947657</v>
       </c>
       <c r="B66" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7564,53 +7564,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128947653</v>
+        <v>128947673</v>
       </c>
       <c r="B67" t="n">
-        <v>57720</v>
+        <v>86806</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>3712</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>712303</v>
+        <v>712157</v>
       </c>
       <c r="R67" t="n">
-        <v>6358650</v>
+        <v>6358456</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7669,45 +7661,53 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128947673</v>
+        <v>128947653</v>
       </c>
       <c r="B68" t="n">
-        <v>86803</v>
+        <v>57720</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3712</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>712157</v>
+        <v>712303</v>
       </c>
       <c r="R68" t="n">
-        <v>6358456</v>
+        <v>6358650</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7766,32 +7766,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128947670</v>
+        <v>128947645</v>
       </c>
       <c r="B69" t="n">
-        <v>86803</v>
+        <v>87026</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7801,10 +7801,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>712289</v>
+        <v>712060</v>
       </c>
       <c r="R69" t="n">
-        <v>6358623</v>
+        <v>6358285</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7863,32 +7863,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128947645</v>
+        <v>128947670</v>
       </c>
       <c r="B70" t="n">
-        <v>87023</v>
+        <v>86806</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7898,10 +7898,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>712060</v>
+        <v>712289</v>
       </c>
       <c r="R70" t="n">
-        <v>6358285</v>
+        <v>6358623</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7963,7 +7963,7 @@
         <v>128947644</v>
       </c>
       <c r="B71" t="n">
-        <v>86921</v>
+        <v>86924</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>128947672</v>
       </c>
       <c r="B72" t="n">
-        <v>86803</v>
+        <v>86806</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>128947646</v>
       </c>
       <c r="B73" t="n">
-        <v>86965</v>
+        <v>86968</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8252,32 +8252,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129004213</v>
+        <v>129004190</v>
       </c>
       <c r="B74" t="n">
-        <v>86825</v>
+        <v>87004</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>424</v>
+        <v>248947</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>712140</v>
+        <v>712178</v>
       </c>
       <c r="R74" t="n">
-        <v>6358430</v>
+        <v>6358421</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8359,32 +8359,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129004190</v>
+        <v>129004213</v>
       </c>
       <c r="B75" t="n">
-        <v>87001</v>
+        <v>86828</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>248947</v>
+        <v>424</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8394,10 +8394,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>712178</v>
+        <v>712140</v>
       </c>
       <c r="R75" t="n">
-        <v>6358421</v>
+        <v>6358430</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8469,7 +8469,7 @@
         <v>129004186</v>
       </c>
       <c r="B76" t="n">
-        <v>86921</v>
+        <v>86924</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>129004199</v>
       </c>
       <c r="B77" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>129004203</v>
       </c>
       <c r="B78" t="n">
-        <v>86894</v>
+        <v>86897</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>129004215</v>
       </c>
       <c r="B79" t="n">
-        <v>86825</v>
+        <v>86828</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>129004194</v>
       </c>
       <c r="B80" t="n">
-        <v>86803</v>
+        <v>86806</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>129004211</v>
       </c>
       <c r="B81" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>129004195</v>
       </c>
       <c r="B82" t="n">
-        <v>86955</v>
+        <v>86958</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>129004208</v>
       </c>
       <c r="B83" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>129004212</v>
       </c>
       <c r="B84" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>129004207</v>
       </c>
       <c r="B85" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9549,32 +9549,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129004210</v>
+        <v>129004192</v>
       </c>
       <c r="B86" t="n">
-        <v>87000</v>
+        <v>110787</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>449</v>
+        <v>219711</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9584,10 +9584,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>712140</v>
+        <v>712118</v>
       </c>
       <c r="R86" t="n">
-        <v>6358434</v>
+        <v>6358398</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9656,32 +9656,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129004192</v>
+        <v>129004210</v>
       </c>
       <c r="B87" t="n">
-        <v>110784</v>
+        <v>87003</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219711</v>
+        <v>449</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9691,10 +9691,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>712118</v>
+        <v>712140</v>
       </c>
       <c r="R87" t="n">
-        <v>6358398</v>
+        <v>6358434</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9766,7 +9766,7 @@
         <v>129004202</v>
       </c>
       <c r="B88" t="n">
-        <v>90939</v>
+        <v>90942</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>129004200</v>
       </c>
       <c r="B89" t="n">
-        <v>86978</v>
+        <v>86981</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>129004206</v>
       </c>
       <c r="B90" t="n">
-        <v>87000</v>
+        <v>87003</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>129004204</v>
       </c>
       <c r="B91" t="n">
-        <v>86894</v>
+        <v>86897</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10188,32 +10188,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129004209</v>
+        <v>129004193</v>
       </c>
       <c r="B92" t="n">
-        <v>87000</v>
+        <v>90324</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>449</v>
+        <v>2072</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>712185</v>
+        <v>712067</v>
       </c>
       <c r="R92" t="n">
-        <v>6358414</v>
+        <v>6358371</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10277,6 +10277,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10295,32 +10296,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129004193</v>
+        <v>129004209</v>
       </c>
       <c r="B93" t="n">
-        <v>90321</v>
+        <v>87003</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2072</v>
+        <v>449</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10330,10 +10331,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>712067</v>
+        <v>712185</v>
       </c>
       <c r="R93" t="n">
-        <v>6358371</v>
+        <v>6358414</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10365,7 +10366,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10375,7 +10376,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10384,7 +10385,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10406,7 +10406,7 @@
         <v>129004188</v>
       </c>
       <c r="B94" t="n">
-        <v>87023</v>
+        <v>87026</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>129004191</v>
       </c>
       <c r="B95" t="n">
-        <v>87001</v>
+        <v>87004</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10617,10 +10617,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129004205</v>
+        <v>129004187</v>
       </c>
       <c r="B96" t="n">
-        <v>87000</v>
+        <v>87026</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10628,21 +10628,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10652,10 +10652,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>712139</v>
+        <v>712224</v>
       </c>
       <c r="R96" t="n">
-        <v>6358437</v>
+        <v>6358420</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10724,32 +10724,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129004201</v>
+        <v>129004214</v>
       </c>
       <c r="B97" t="n">
-        <v>86870</v>
+        <v>86944</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>445</v>
+        <v>3674</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10759,10 +10759,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>712185</v>
+        <v>712132</v>
       </c>
       <c r="R97" t="n">
-        <v>6358418</v>
+        <v>6358416</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10831,32 +10831,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129004214</v>
+        <v>129004205</v>
       </c>
       <c r="B98" t="n">
-        <v>86941</v>
+        <v>87003</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10866,10 +10866,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>712132</v>
+        <v>712139</v>
       </c>
       <c r="R98" t="n">
-        <v>6358416</v>
+        <v>6358437</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10938,10 +10938,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129004187</v>
+        <v>129004201</v>
       </c>
       <c r="B99" t="n">
-        <v>87023</v>
+        <v>86873</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10949,16 +10949,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3767</v>
+        <v>445</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10973,10 +10973,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>712224</v>
+        <v>712185</v>
       </c>
       <c r="R99" t="n">
-        <v>6358420</v>
+        <v>6358418</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD99" t="b">

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -5899,10 +5899,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128947664</v>
+        <v>128947675</v>
       </c>
       <c r="B50" t="n">
-        <v>91946</v>
+        <v>86944</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5910,21 +5910,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5420</v>
+        <v>3674</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>712272</v>
+        <v>712229</v>
       </c>
       <c r="R50" t="n">
-        <v>6358461</v>
+        <v>6358510</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5996,10 +5996,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128947675</v>
+        <v>128947674</v>
       </c>
       <c r="B51" t="n">
-        <v>86944</v>
+        <v>86806</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6007,21 +6007,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712229</v>
+        <v>712125</v>
       </c>
       <c r="R51" t="n">
-        <v>6358510</v>
+        <v>6358399</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6093,10 +6093,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128947674</v>
+        <v>128947664</v>
       </c>
       <c r="B52" t="n">
-        <v>86806</v>
+        <v>91946</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6104,21 +6104,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3712</v>
+        <v>5420</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6128,10 +6128,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712125</v>
+        <v>712272</v>
       </c>
       <c r="R52" t="n">
-        <v>6358399</v>
+        <v>6358461</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6482,10 +6482,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128947667</v>
+        <v>128947669</v>
       </c>
       <c r="B56" t="n">
-        <v>92855</v>
+        <v>86806</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6493,37 +6493,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5964</v>
+        <v>3712</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>712163</v>
+        <v>712363</v>
       </c>
       <c r="R56" t="n">
-        <v>6358380</v>
+        <v>6358457</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6564,7 +6561,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6583,10 +6579,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128947669</v>
+        <v>128947667</v>
       </c>
       <c r="B57" t="n">
-        <v>86806</v>
+        <v>92855</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6594,34 +6590,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3712</v>
+        <v>5964</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712363</v>
+        <v>712163</v>
       </c>
       <c r="R57" t="n">
-        <v>6358457</v>
+        <v>6358380</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6662,6 +6661,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6777,45 +6777,53 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128947655</v>
+        <v>128947654</v>
       </c>
       <c r="B59" t="n">
-        <v>86782</v>
+        <v>57720</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3762</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712080</v>
+        <v>712106</v>
       </c>
       <c r="R59" t="n">
-        <v>6358365</v>
+        <v>6358348</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6874,32 +6882,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128947648</v>
+        <v>128947655</v>
       </c>
       <c r="B60" t="n">
-        <v>87004</v>
+        <v>86782</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>248947</v>
+        <v>3762</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6909,10 +6917,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712168</v>
+        <v>712080</v>
       </c>
       <c r="R60" t="n">
-        <v>6358403</v>
+        <v>6358365</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6971,7 +6979,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128947649</v>
+        <v>128947648</v>
       </c>
       <c r="B61" t="n">
         <v>87004</v>
@@ -7006,10 +7014,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712051</v>
+        <v>712168</v>
       </c>
       <c r="R61" t="n">
-        <v>6358299</v>
+        <v>6358403</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7068,53 +7076,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128947654</v>
+        <v>128947649</v>
       </c>
       <c r="B62" t="n">
-        <v>57720</v>
+        <v>87004</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>248947</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712106</v>
+        <v>712051</v>
       </c>
       <c r="R62" t="n">
-        <v>6358348</v>
+        <v>6358299</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7766,32 +7766,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128947645</v>
+        <v>128947670</v>
       </c>
       <c r="B69" t="n">
-        <v>87026</v>
+        <v>86806</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7801,10 +7801,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>712060</v>
+        <v>712289</v>
       </c>
       <c r="R69" t="n">
-        <v>6358285</v>
+        <v>6358623</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7863,32 +7863,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128947670</v>
+        <v>128947645</v>
       </c>
       <c r="B70" t="n">
-        <v>86806</v>
+        <v>87026</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7898,10 +7898,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>712289</v>
+        <v>712060</v>
       </c>
       <c r="R70" t="n">
-        <v>6358623</v>
+        <v>6358285</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8252,32 +8252,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129004190</v>
+        <v>129004213</v>
       </c>
       <c r="B74" t="n">
-        <v>87004</v>
+        <v>86828</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>248947</v>
+        <v>424</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>712178</v>
+        <v>712140</v>
       </c>
       <c r="R74" t="n">
-        <v>6358421</v>
+        <v>6358430</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8359,32 +8359,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129004213</v>
+        <v>129004190</v>
       </c>
       <c r="B75" t="n">
-        <v>86828</v>
+        <v>87004</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>424</v>
+        <v>248947</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8394,10 +8394,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>712140</v>
+        <v>712178</v>
       </c>
       <c r="R75" t="n">
-        <v>6358430</v>
+        <v>6358421</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8788,32 +8788,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129004215</v>
+        <v>129004194</v>
       </c>
       <c r="B79" t="n">
-        <v>86828</v>
+        <v>86806</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>712139</v>
+        <v>712133</v>
       </c>
       <c r="R79" t="n">
-        <v>6358436</v>
+        <v>6358398</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8895,32 +8895,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129004194</v>
+        <v>129004215</v>
       </c>
       <c r="B80" t="n">
-        <v>86806</v>
+        <v>86828</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>712133</v>
+        <v>712139</v>
       </c>
       <c r="R80" t="n">
-        <v>6358398</v>
+        <v>6358436</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9549,32 +9549,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129004192</v>
+        <v>129004210</v>
       </c>
       <c r="B86" t="n">
-        <v>110787</v>
+        <v>87003</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219711</v>
+        <v>449</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9584,10 +9584,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>712118</v>
+        <v>712140</v>
       </c>
       <c r="R86" t="n">
-        <v>6358398</v>
+        <v>6358434</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9656,32 +9656,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129004210</v>
+        <v>129004192</v>
       </c>
       <c r="B87" t="n">
-        <v>87003</v>
+        <v>110787</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>449</v>
+        <v>219711</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9691,10 +9691,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>712140</v>
+        <v>712118</v>
       </c>
       <c r="R87" t="n">
-        <v>6358434</v>
+        <v>6358398</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10617,10 +10617,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129004187</v>
+        <v>129004205</v>
       </c>
       <c r="B96" t="n">
-        <v>87026</v>
+        <v>87003</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10628,21 +10628,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3767</v>
+        <v>449</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10652,10 +10652,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>712224</v>
+        <v>712139</v>
       </c>
       <c r="R96" t="n">
-        <v>6358420</v>
+        <v>6358437</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10724,32 +10724,32 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129004214</v>
+        <v>129004201</v>
       </c>
       <c r="B97" t="n">
-        <v>86944</v>
+        <v>86873</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3674</v>
+        <v>445</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10759,10 +10759,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>712132</v>
+        <v>712185</v>
       </c>
       <c r="R97" t="n">
-        <v>6358416</v>
+        <v>6358418</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10831,32 +10831,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129004205</v>
+        <v>129004214</v>
       </c>
       <c r="B98" t="n">
-        <v>87003</v>
+        <v>86944</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10866,10 +10866,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>712139</v>
+        <v>712132</v>
       </c>
       <c r="R98" t="n">
-        <v>6358437</v>
+        <v>6358416</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10938,10 +10938,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129004201</v>
+        <v>129004187</v>
       </c>
       <c r="B99" t="n">
-        <v>86873</v>
+        <v>87026</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10949,16 +10949,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>445</v>
+        <v>3767</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10973,10 +10973,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>712185</v>
+        <v>712224</v>
       </c>
       <c r="R99" t="n">
-        <v>6358418</v>
+        <v>6358420</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD99" t="b">

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -10831,32 +10831,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129004214</v>
+        <v>129004187</v>
       </c>
       <c r="B98" t="n">
-        <v>86944</v>
+        <v>87026</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10866,10 +10866,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>712132</v>
+        <v>712224</v>
       </c>
       <c r="R98" t="n">
-        <v>6358416</v>
+        <v>6358420</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10938,32 +10938,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129004187</v>
+        <v>129004214</v>
       </c>
       <c r="B99" t="n">
-        <v>87026</v>
+        <v>86944</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10973,10 +10973,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>712224</v>
+        <v>712132</v>
       </c>
       <c r="R99" t="n">
-        <v>6358420</v>
+        <v>6358416</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD99" t="b">

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -6777,53 +6777,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128947654</v>
+        <v>128947655</v>
       </c>
       <c r="B59" t="n">
-        <v>57720</v>
+        <v>86782</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>3762</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712106</v>
+        <v>712080</v>
       </c>
       <c r="R59" t="n">
-        <v>6358348</v>
+        <v>6358365</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6882,45 +6874,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128947655</v>
+        <v>128947654</v>
       </c>
       <c r="B60" t="n">
-        <v>86782</v>
+        <v>57720</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3762</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712080</v>
+        <v>712106</v>
       </c>
       <c r="R60" t="n">
-        <v>6358365</v>
+        <v>6358348</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7271,10 +7271,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128947666</v>
+        <v>128947663</v>
       </c>
       <c r="B64" t="n">
-        <v>87003</v>
+        <v>86897</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7282,21 +7282,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712159</v>
+        <v>712176</v>
       </c>
       <c r="R64" t="n">
-        <v>6358410</v>
+        <v>6358409</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7350,6 +7350,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7368,10 +7369,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128947663</v>
+        <v>128947666</v>
       </c>
       <c r="B65" t="n">
-        <v>86897</v>
+        <v>87003</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7379,21 +7380,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7403,10 +7404,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>712176</v>
+        <v>712159</v>
       </c>
       <c r="R65" t="n">
-        <v>6358409</v>
+        <v>6358410</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7447,7 +7448,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7564,45 +7564,53 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128947673</v>
+        <v>128947653</v>
       </c>
       <c r="B67" t="n">
-        <v>86806</v>
+        <v>57720</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3712</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>712157</v>
+        <v>712303</v>
       </c>
       <c r="R67" t="n">
-        <v>6358456</v>
+        <v>6358650</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7661,53 +7669,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128947653</v>
+        <v>128947673</v>
       </c>
       <c r="B68" t="n">
-        <v>57720</v>
+        <v>86806</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>3712</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>712303</v>
+        <v>712157</v>
       </c>
       <c r="R68" t="n">
-        <v>6358650</v>
+        <v>6358456</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7766,32 +7766,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128947670</v>
+        <v>128947645</v>
       </c>
       <c r="B69" t="n">
-        <v>86806</v>
+        <v>87026</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7801,10 +7801,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>712289</v>
+        <v>712060</v>
       </c>
       <c r="R69" t="n">
-        <v>6358623</v>
+        <v>6358285</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7863,32 +7863,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128947645</v>
+        <v>128947670</v>
       </c>
       <c r="B70" t="n">
-        <v>87026</v>
+        <v>86806</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7898,10 +7898,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>712060</v>
+        <v>712289</v>
       </c>
       <c r="R70" t="n">
-        <v>6358285</v>
+        <v>6358623</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8252,32 +8252,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129004213</v>
+        <v>129004190</v>
       </c>
       <c r="B74" t="n">
-        <v>86828</v>
+        <v>87004</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>424</v>
+        <v>248947</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>712140</v>
+        <v>712178</v>
       </c>
       <c r="R74" t="n">
-        <v>6358430</v>
+        <v>6358421</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8359,32 +8359,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129004190</v>
+        <v>129004213</v>
       </c>
       <c r="B75" t="n">
-        <v>87004</v>
+        <v>86828</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>248947</v>
+        <v>424</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8394,10 +8394,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>712178</v>
+        <v>712140</v>
       </c>
       <c r="R75" t="n">
-        <v>6358421</v>
+        <v>6358430</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8788,32 +8788,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129004194</v>
+        <v>129004215</v>
       </c>
       <c r="B79" t="n">
-        <v>86806</v>
+        <v>86828</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>712133</v>
+        <v>712139</v>
       </c>
       <c r="R79" t="n">
-        <v>6358398</v>
+        <v>6358436</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8895,32 +8895,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129004215</v>
+        <v>129004194</v>
       </c>
       <c r="B80" t="n">
-        <v>86828</v>
+        <v>86806</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>712139</v>
+        <v>712133</v>
       </c>
       <c r="R80" t="n">
-        <v>6358436</v>
+        <v>6358398</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9974,10 +9974,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129004206</v>
+        <v>129004204</v>
       </c>
       <c r="B90" t="n">
-        <v>87003</v>
+        <v>86897</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9985,21 +9985,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10009,10 +10009,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>712178</v>
+        <v>712180</v>
       </c>
       <c r="R90" t="n">
-        <v>6358418</v>
+        <v>6358430</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10081,10 +10081,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129004204</v>
+        <v>129004206</v>
       </c>
       <c r="B91" t="n">
-        <v>86897</v>
+        <v>87003</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10092,21 +10092,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10116,10 +10116,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>712180</v>
+        <v>712178</v>
       </c>
       <c r="R91" t="n">
-        <v>6358430</v>
+        <v>6358418</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10188,32 +10188,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129004193</v>
+        <v>129004209</v>
       </c>
       <c r="B92" t="n">
-        <v>90324</v>
+        <v>87003</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2072</v>
+        <v>449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>712067</v>
+        <v>712185</v>
       </c>
       <c r="R92" t="n">
-        <v>6358371</v>
+        <v>6358414</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10277,7 +10277,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10296,32 +10295,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129004209</v>
+        <v>129004193</v>
       </c>
       <c r="B93" t="n">
-        <v>87003</v>
+        <v>90324</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>449</v>
+        <v>2072</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10331,10 +10330,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>712185</v>
+        <v>712067</v>
       </c>
       <c r="R93" t="n">
-        <v>6358414</v>
+        <v>6358371</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10366,7 +10365,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10376,7 +10375,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10385,6 +10384,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10617,32 +10617,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129004205</v>
+        <v>129004214</v>
       </c>
       <c r="B96" t="n">
-        <v>87003</v>
+        <v>86944</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10652,10 +10652,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>712139</v>
+        <v>712132</v>
       </c>
       <c r="R96" t="n">
-        <v>6358437</v>
+        <v>6358416</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10724,10 +10724,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129004201</v>
+        <v>129004187</v>
       </c>
       <c r="B97" t="n">
-        <v>86873</v>
+        <v>87026</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10735,16 +10735,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>445</v>
+        <v>3767</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10759,10 +10759,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>712185</v>
+        <v>712224</v>
       </c>
       <c r="R97" t="n">
-        <v>6358418</v>
+        <v>6358420</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10831,10 +10831,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129004187</v>
+        <v>129004201</v>
       </c>
       <c r="B98" t="n">
-        <v>87026</v>
+        <v>86873</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10842,16 +10842,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3767</v>
+        <v>445</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -10866,10 +10866,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>712224</v>
+        <v>712185</v>
       </c>
       <c r="R98" t="n">
-        <v>6358420</v>
+        <v>6358418</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10938,32 +10938,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129004214</v>
+        <v>129004205</v>
       </c>
       <c r="B99" t="n">
-        <v>86944</v>
+        <v>87003</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10973,10 +10973,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>712132</v>
+        <v>712139</v>
       </c>
       <c r="R99" t="n">
-        <v>6358416</v>
+        <v>6358437</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD99" t="b">

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -5512,7 +5512,7 @@
         <v>128947671</v>
       </c>
       <c r="B46" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>128947652</v>
       </c>
       <c r="B47" t="n">
-        <v>86828</v>
+        <v>86832</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>128947656</v>
       </c>
       <c r="B48" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>128947660</v>
       </c>
       <c r="B49" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>128947675</v>
       </c>
       <c r="B50" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>128947674</v>
       </c>
       <c r="B51" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>128947664</v>
       </c>
       <c r="B52" t="n">
-        <v>91946</v>
+        <v>91953</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>128947659</v>
       </c>
       <c r="B53" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>128947677</v>
       </c>
       <c r="B54" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>128947676</v>
       </c>
       <c r="B55" t="n">
-        <v>86944</v>
+        <v>86948</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>128947669</v>
       </c>
       <c r="B56" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6582,7 +6582,7 @@
         <v>128947667</v>
       </c>
       <c r="B57" t="n">
-        <v>92855</v>
+        <v>92862</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>128947647</v>
       </c>
       <c r="B58" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6777,32 +6777,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128947655</v>
+        <v>128947648</v>
       </c>
       <c r="B59" t="n">
-        <v>86782</v>
+        <v>87008</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3762</v>
+        <v>248947</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712080</v>
+        <v>712168</v>
       </c>
       <c r="R59" t="n">
-        <v>6358365</v>
+        <v>6358403</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6874,53 +6874,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128947654</v>
+        <v>128947649</v>
       </c>
       <c r="B60" t="n">
-        <v>57720</v>
+        <v>87008</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>248947</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712106</v>
+        <v>712051</v>
       </c>
       <c r="R60" t="n">
-        <v>6358348</v>
+        <v>6358299</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6979,45 +6971,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128947648</v>
+        <v>128947654</v>
       </c>
       <c r="B61" t="n">
-        <v>87004</v>
+        <v>57722</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>248947</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712168</v>
+        <v>712106</v>
       </c>
       <c r="R61" t="n">
-        <v>6358403</v>
+        <v>6358348</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7076,32 +7076,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128947649</v>
+        <v>128947655</v>
       </c>
       <c r="B62" t="n">
-        <v>87004</v>
+        <v>86786</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>248947</v>
+        <v>3762</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7111,10 +7111,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712051</v>
+        <v>712080</v>
       </c>
       <c r="R62" t="n">
-        <v>6358299</v>
+        <v>6358365</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7176,7 +7176,7 @@
         <v>128947643</v>
       </c>
       <c r="B63" t="n">
-        <v>86924</v>
+        <v>86928</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>128947663</v>
       </c>
       <c r="B64" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7372,7 +7372,7 @@
         <v>128947666</v>
       </c>
       <c r="B65" t="n">
-        <v>87003</v>
+        <v>87007</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>128947657</v>
       </c>
       <c r="B66" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>128947653</v>
       </c>
       <c r="B67" t="n">
-        <v>57720</v>
+        <v>57722</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>128947673</v>
       </c>
       <c r="B68" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7766,32 +7766,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128947645</v>
+        <v>128947670</v>
       </c>
       <c r="B69" t="n">
-        <v>87026</v>
+        <v>86810</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7801,10 +7801,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>712060</v>
+        <v>712289</v>
       </c>
       <c r="R69" t="n">
-        <v>6358285</v>
+        <v>6358623</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7863,32 +7863,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128947670</v>
+        <v>128947645</v>
       </c>
       <c r="B70" t="n">
-        <v>86806</v>
+        <v>87030</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7898,10 +7898,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>712289</v>
+        <v>712060</v>
       </c>
       <c r="R70" t="n">
-        <v>6358623</v>
+        <v>6358285</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7963,7 +7963,7 @@
         <v>128947644</v>
       </c>
       <c r="B71" t="n">
-        <v>86924</v>
+        <v>86928</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>128947672</v>
       </c>
       <c r="B72" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>128947646</v>
       </c>
       <c r="B73" t="n">
-        <v>86968</v>
+        <v>86972</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8252,32 +8252,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129004190</v>
+        <v>129004213</v>
       </c>
       <c r="B74" t="n">
-        <v>87004</v>
+        <v>86832</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>248947</v>
+        <v>424</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>712178</v>
+        <v>712140</v>
       </c>
       <c r="R74" t="n">
-        <v>6358421</v>
+        <v>6358430</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8359,32 +8359,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129004213</v>
+        <v>129004190</v>
       </c>
       <c r="B75" t="n">
-        <v>86828</v>
+        <v>87008</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>424</v>
+        <v>248947</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8394,10 +8394,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>712140</v>
+        <v>712178</v>
       </c>
       <c r="R75" t="n">
-        <v>6358430</v>
+        <v>6358421</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8469,7 +8469,7 @@
         <v>129004186</v>
       </c>
       <c r="B76" t="n">
-        <v>86924</v>
+        <v>86928</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>129004199</v>
       </c>
       <c r="B77" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>129004203</v>
       </c>
       <c r="B78" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>129004215</v>
       </c>
       <c r="B79" t="n">
-        <v>86828</v>
+        <v>86832</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>129004194</v>
       </c>
       <c r="B80" t="n">
-        <v>86806</v>
+        <v>86810</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>129004211</v>
       </c>
       <c r="B81" t="n">
-        <v>87003</v>
+        <v>87007</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>129004195</v>
       </c>
       <c r="B82" t="n">
-        <v>86958</v>
+        <v>86962</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>129004208</v>
       </c>
       <c r="B83" t="n">
-        <v>87003</v>
+        <v>87007</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>129004212</v>
       </c>
       <c r="B84" t="n">
-        <v>87003</v>
+        <v>87007</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>129004207</v>
       </c>
       <c r="B85" t="n">
-        <v>87003</v>
+        <v>87007</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9549,32 +9549,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129004210</v>
+        <v>129004192</v>
       </c>
       <c r="B86" t="n">
-        <v>87003</v>
+        <v>110797</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>449</v>
+        <v>219711</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9584,10 +9584,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>712140</v>
+        <v>712118</v>
       </c>
       <c r="R86" t="n">
-        <v>6358434</v>
+        <v>6358398</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9656,32 +9656,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129004192</v>
+        <v>129004210</v>
       </c>
       <c r="B87" t="n">
-        <v>110787</v>
+        <v>87007</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219711</v>
+        <v>449</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9691,10 +9691,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>712118</v>
+        <v>712140</v>
       </c>
       <c r="R87" t="n">
-        <v>6358398</v>
+        <v>6358434</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9766,7 +9766,7 @@
         <v>129004202</v>
       </c>
       <c r="B88" t="n">
-        <v>90942</v>
+        <v>90946</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>129004200</v>
       </c>
       <c r="B89" t="n">
-        <v>86981</v>
+        <v>86985</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>129004204</v>
       </c>
       <c r="B90" t="n">
-        <v>86897</v>
+        <v>86901</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>129004206</v>
       </c>
       <c r="B91" t="n">
-        <v>87003</v>
+        <v>87007</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>129004209</v>
       </c>
       <c r="B92" t="n">
-        <v>87003</v>
+        <v>87007</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>129004193</v>
       </c>
       <c r="B93" t="n">
-        <v>90324</v>
+        <v>90328</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>129004188</v>
       </c>
       <c r="B94" t="n">
-        <v>87026</v>
+        <v>87030</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>129004191</v>
       </c>
       <c r="B95" t="n">
-        <v>87004</v>
+        <v>87008</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10617,32 +10617,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129004214</v>
+        <v>129004205</v>
       </c>
       <c r="B96" t="n">
-        <v>86944</v>
+        <v>87007</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10652,10 +10652,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>712132</v>
+        <v>712139</v>
       </c>
       <c r="R96" t="n">
-        <v>6358416</v>
+        <v>6358437</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10724,10 +10724,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129004187</v>
+        <v>129004201</v>
       </c>
       <c r="B97" t="n">
-        <v>87026</v>
+        <v>86877</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10735,16 +10735,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3767</v>
+        <v>445</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10759,10 +10759,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>712224</v>
+        <v>712185</v>
       </c>
       <c r="R97" t="n">
-        <v>6358420</v>
+        <v>6358418</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10831,32 +10831,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129004201</v>
+        <v>129004214</v>
       </c>
       <c r="B98" t="n">
-        <v>86873</v>
+        <v>86948</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>445</v>
+        <v>3674</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10866,10 +10866,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>712185</v>
+        <v>712132</v>
       </c>
       <c r="R98" t="n">
-        <v>6358418</v>
+        <v>6358416</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10938,10 +10938,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129004205</v>
+        <v>129004187</v>
       </c>
       <c r="B99" t="n">
-        <v>87003</v>
+        <v>87030</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10949,21 +10949,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10973,10 +10973,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>712139</v>
+        <v>712224</v>
       </c>
       <c r="R99" t="n">
-        <v>6358437</v>
+        <v>6358420</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD99" t="b">

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -6482,10 +6482,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128947669</v>
+        <v>128947667</v>
       </c>
       <c r="B56" t="n">
-        <v>86810</v>
+        <v>92862</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6493,34 +6493,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3712</v>
+        <v>5964</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>712363</v>
+        <v>712163</v>
       </c>
       <c r="R56" t="n">
-        <v>6358457</v>
+        <v>6358380</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6561,6 +6564,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6579,10 +6583,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128947667</v>
+        <v>128947669</v>
       </c>
       <c r="B57" t="n">
-        <v>92862</v>
+        <v>86810</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6590,37 +6594,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5964</v>
+        <v>3712</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712163</v>
+        <v>712363</v>
       </c>
       <c r="R57" t="n">
-        <v>6358380</v>
+        <v>6358457</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6661,7 +6662,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6777,45 +6777,53 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128947648</v>
+        <v>128947654</v>
       </c>
       <c r="B59" t="n">
-        <v>87008</v>
+        <v>57722</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>248947</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712168</v>
+        <v>712106</v>
       </c>
       <c r="R59" t="n">
-        <v>6358403</v>
+        <v>6358348</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6874,7 +6882,7 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128947649</v>
+        <v>128947648</v>
       </c>
       <c r="B60" t="n">
         <v>87008</v>
@@ -6909,10 +6917,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712051</v>
+        <v>712168</v>
       </c>
       <c r="R60" t="n">
-        <v>6358299</v>
+        <v>6358403</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6971,53 +6979,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128947654</v>
+        <v>128947649</v>
       </c>
       <c r="B61" t="n">
-        <v>57722</v>
+        <v>87008</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>248947</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712106</v>
+        <v>712051</v>
       </c>
       <c r="R61" t="n">
-        <v>6358348</v>
+        <v>6358299</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -9974,10 +9974,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129004204</v>
+        <v>129004206</v>
       </c>
       <c r="B90" t="n">
-        <v>86901</v>
+        <v>87007</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9985,21 +9985,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10009,10 +10009,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>712180</v>
+        <v>712178</v>
       </c>
       <c r="R90" t="n">
-        <v>6358430</v>
+        <v>6358418</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10081,10 +10081,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129004206</v>
+        <v>129004204</v>
       </c>
       <c r="B91" t="n">
-        <v>87007</v>
+        <v>86901</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10092,21 +10092,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10116,10 +10116,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>712178</v>
+        <v>712180</v>
       </c>
       <c r="R91" t="n">
-        <v>6358418</v>
+        <v>6358430</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -5509,32 +5509,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128947671</v>
+        <v>128947652</v>
       </c>
       <c r="B46" t="n">
-        <v>86810</v>
+        <v>86839</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>712289</v>
+        <v>712290</v>
       </c>
       <c r="R46" t="n">
         <v>6358633</v>
@@ -5606,32 +5606,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128947652</v>
+        <v>128947671</v>
       </c>
       <c r="B47" t="n">
-        <v>86832</v>
+        <v>86817</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>712290</v>
+        <v>712289</v>
       </c>
       <c r="R47" t="n">
         <v>6358633</v>
@@ -5706,7 +5706,7 @@
         <v>128947656</v>
       </c>
       <c r="B48" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>128947660</v>
       </c>
       <c r="B49" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>128947675</v>
       </c>
       <c r="B50" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>128947674</v>
       </c>
       <c r="B51" t="n">
-        <v>86810</v>
+        <v>86817</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>128947664</v>
       </c>
       <c r="B52" t="n">
-        <v>91953</v>
+        <v>91960</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>128947659</v>
       </c>
       <c r="B53" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>128947677</v>
       </c>
       <c r="B54" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>128947676</v>
       </c>
       <c r="B55" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>128947667</v>
       </c>
       <c r="B56" t="n">
-        <v>92862</v>
+        <v>92869</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>128947669</v>
       </c>
       <c r="B57" t="n">
-        <v>86810</v>
+        <v>86817</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>128947647</v>
       </c>
       <c r="B58" t="n">
-        <v>87008</v>
+        <v>87015</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6777,53 +6777,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128947654</v>
+        <v>128947655</v>
       </c>
       <c r="B59" t="n">
-        <v>57722</v>
+        <v>86793</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>3762</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712106</v>
+        <v>712080</v>
       </c>
       <c r="R59" t="n">
-        <v>6358348</v>
+        <v>6358365</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6882,45 +6874,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128947648</v>
+        <v>128947654</v>
       </c>
       <c r="B60" t="n">
-        <v>87008</v>
+        <v>57722</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>248947</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712168</v>
+        <v>712106</v>
       </c>
       <c r="R60" t="n">
-        <v>6358403</v>
+        <v>6358348</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6979,10 +6979,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128947649</v>
+        <v>128947648</v>
       </c>
       <c r="B61" t="n">
-        <v>87008</v>
+        <v>87015</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7014,10 +7014,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712051</v>
+        <v>712168</v>
       </c>
       <c r="R61" t="n">
-        <v>6358299</v>
+        <v>6358403</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7076,32 +7076,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128947655</v>
+        <v>128947649</v>
       </c>
       <c r="B62" t="n">
-        <v>86786</v>
+        <v>87015</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3762</v>
+        <v>248947</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7111,10 +7111,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712080</v>
+        <v>712051</v>
       </c>
       <c r="R62" t="n">
-        <v>6358365</v>
+        <v>6358299</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7176,7 +7176,7 @@
         <v>128947643</v>
       </c>
       <c r="B63" t="n">
-        <v>86928</v>
+        <v>86935</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7271,10 +7271,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128947663</v>
+        <v>128947666</v>
       </c>
       <c r="B64" t="n">
-        <v>86901</v>
+        <v>87014</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7282,21 +7282,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712176</v>
+        <v>712159</v>
       </c>
       <c r="R64" t="n">
-        <v>6358409</v>
+        <v>6358410</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7350,7 +7350,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7369,10 +7368,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128947666</v>
+        <v>128947663</v>
       </c>
       <c r="B65" t="n">
-        <v>87007</v>
+        <v>86908</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7380,21 +7379,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7404,10 +7403,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>712159</v>
+        <v>712176</v>
       </c>
       <c r="R65" t="n">
-        <v>6358410</v>
+        <v>6358409</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7448,6 +7447,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7469,7 +7469,7 @@
         <v>128947657</v>
       </c>
       <c r="B66" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7564,53 +7564,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128947653</v>
+        <v>128947673</v>
       </c>
       <c r="B67" t="n">
-        <v>57722</v>
+        <v>86817</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>3712</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>712303</v>
+        <v>712157</v>
       </c>
       <c r="R67" t="n">
-        <v>6358650</v>
+        <v>6358456</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7669,45 +7661,53 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128947673</v>
+        <v>128947653</v>
       </c>
       <c r="B68" t="n">
-        <v>86810</v>
+        <v>57722</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3712</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>712157</v>
+        <v>712303</v>
       </c>
       <c r="R68" t="n">
-        <v>6358456</v>
+        <v>6358650</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7766,32 +7766,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128947670</v>
+        <v>128947645</v>
       </c>
       <c r="B69" t="n">
-        <v>86810</v>
+        <v>87037</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7801,10 +7801,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>712289</v>
+        <v>712060</v>
       </c>
       <c r="R69" t="n">
-        <v>6358623</v>
+        <v>6358285</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7863,32 +7863,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128947645</v>
+        <v>128947670</v>
       </c>
       <c r="B70" t="n">
-        <v>87030</v>
+        <v>86817</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7898,10 +7898,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>712060</v>
+        <v>712289</v>
       </c>
       <c r="R70" t="n">
-        <v>6358285</v>
+        <v>6358623</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7963,7 +7963,7 @@
         <v>128947644</v>
       </c>
       <c r="B71" t="n">
-        <v>86928</v>
+        <v>86935</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>128947672</v>
       </c>
       <c r="B72" t="n">
-        <v>86810</v>
+        <v>86817</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>128947646</v>
       </c>
       <c r="B73" t="n">
-        <v>86972</v>
+        <v>86979</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>129004213</v>
       </c>
       <c r="B74" t="n">
-        <v>86832</v>
+        <v>86839</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>129004190</v>
       </c>
       <c r="B75" t="n">
-        <v>87008</v>
+        <v>87015</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>129004186</v>
       </c>
       <c r="B76" t="n">
-        <v>86928</v>
+        <v>86935</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>129004199</v>
       </c>
       <c r="B77" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>129004203</v>
       </c>
       <c r="B78" t="n">
-        <v>86901</v>
+        <v>86908</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8788,32 +8788,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129004215</v>
+        <v>129004194</v>
       </c>
       <c r="B79" t="n">
-        <v>86832</v>
+        <v>86817</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>712139</v>
+        <v>712133</v>
       </c>
       <c r="R79" t="n">
-        <v>6358436</v>
+        <v>6358398</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8895,32 +8895,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129004194</v>
+        <v>129004215</v>
       </c>
       <c r="B80" t="n">
-        <v>86810</v>
+        <v>86839</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>712133</v>
+        <v>712139</v>
       </c>
       <c r="R80" t="n">
-        <v>6358398</v>
+        <v>6358436</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9002,32 +9002,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129004211</v>
+        <v>129004195</v>
       </c>
       <c r="B81" t="n">
-        <v>87007</v>
+        <v>86969</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>449</v>
+        <v>249228</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9037,10 +9037,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>712141</v>
+        <v>712179</v>
       </c>
       <c r="R81" t="n">
-        <v>6358437</v>
+        <v>6358417</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9082,12 +9082,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>kollekt</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9096,6 +9091,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9114,32 +9110,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129004195</v>
+        <v>129004211</v>
       </c>
       <c r="B82" t="n">
-        <v>86962</v>
+        <v>87014</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>249228</v>
+        <v>449</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9149,10 +9145,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>712179</v>
+        <v>712141</v>
       </c>
       <c r="R82" t="n">
-        <v>6358417</v>
+        <v>6358437</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9184,7 +9180,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9194,7 +9190,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>kollekt</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9203,7 +9204,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9225,7 +9225,7 @@
         <v>129004208</v>
       </c>
       <c r="B83" t="n">
-        <v>87007</v>
+        <v>87014</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>129004212</v>
       </c>
       <c r="B84" t="n">
-        <v>87007</v>
+        <v>87014</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>129004207</v>
       </c>
       <c r="B85" t="n">
-        <v>87007</v>
+        <v>87014</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>129004192</v>
       </c>
       <c r="B86" t="n">
-        <v>110797</v>
+        <v>110804</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>129004210</v>
       </c>
       <c r="B87" t="n">
-        <v>87007</v>
+        <v>87014</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>129004202</v>
       </c>
       <c r="B88" t="n">
-        <v>90946</v>
+        <v>90953</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>129004200</v>
       </c>
       <c r="B89" t="n">
-        <v>86985</v>
+        <v>86992</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>129004206</v>
       </c>
       <c r="B90" t="n">
-        <v>87007</v>
+        <v>87014</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>129004204</v>
       </c>
       <c r="B91" t="n">
-        <v>86901</v>
+        <v>86908</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>129004209</v>
       </c>
       <c r="B92" t="n">
-        <v>87007</v>
+        <v>87014</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10298,7 +10298,7 @@
         <v>129004193</v>
       </c>
       <c r="B93" t="n">
-        <v>90328</v>
+        <v>90335</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>129004188</v>
       </c>
       <c r="B94" t="n">
-        <v>87030</v>
+        <v>87037</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>129004191</v>
       </c>
       <c r="B95" t="n">
-        <v>87008</v>
+        <v>87015</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>129004205</v>
       </c>
       <c r="B96" t="n">
-        <v>87007</v>
+        <v>87014</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>129004201</v>
       </c>
       <c r="B97" t="n">
-        <v>86877</v>
+        <v>86884</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>129004214</v>
       </c>
       <c r="B98" t="n">
-        <v>86948</v>
+        <v>86955</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>129004187</v>
       </c>
       <c r="B99" t="n">
-        <v>87030</v>
+        <v>87037</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -5509,32 +5509,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128947652</v>
+        <v>128947671</v>
       </c>
       <c r="B46" t="n">
-        <v>86839</v>
+        <v>86819</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>712290</v>
+        <v>712289</v>
       </c>
       <c r="R46" t="n">
         <v>6358633</v>
@@ -5606,32 +5606,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128947671</v>
+        <v>128947652</v>
       </c>
       <c r="B47" t="n">
-        <v>86817</v>
+        <v>86841</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>712289</v>
+        <v>712290</v>
       </c>
       <c r="R47" t="n">
         <v>6358633</v>
@@ -5706,7 +5706,7 @@
         <v>128947656</v>
       </c>
       <c r="B48" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>128947660</v>
       </c>
       <c r="B49" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5899,10 +5899,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128947675</v>
+        <v>128947664</v>
       </c>
       <c r="B50" t="n">
-        <v>86955</v>
+        <v>91962</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5910,21 +5910,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3674</v>
+        <v>5420</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>712229</v>
+        <v>712272</v>
       </c>
       <c r="R50" t="n">
-        <v>6358510</v>
+        <v>6358461</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5999,7 +5999,7 @@
         <v>128947674</v>
       </c>
       <c r="B51" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6093,10 +6093,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128947664</v>
+        <v>128947675</v>
       </c>
       <c r="B52" t="n">
-        <v>91960</v>
+        <v>86957</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6104,21 +6104,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5420</v>
+        <v>3674</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6128,10 +6128,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712272</v>
+        <v>712229</v>
       </c>
       <c r="R52" t="n">
-        <v>6358461</v>
+        <v>6358510</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6193,7 +6193,7 @@
         <v>128947659</v>
       </c>
       <c r="B53" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>128947677</v>
       </c>
       <c r="B54" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>128947676</v>
       </c>
       <c r="B55" t="n">
-        <v>86955</v>
+        <v>86957</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>128947667</v>
       </c>
       <c r="B56" t="n">
-        <v>92869</v>
+        <v>92871</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>128947669</v>
       </c>
       <c r="B57" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>128947647</v>
       </c>
       <c r="B58" t="n">
-        <v>87015</v>
+        <v>87017</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>128947655</v>
       </c>
       <c r="B59" t="n">
-        <v>86793</v>
+        <v>86795</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6877,7 +6877,7 @@
         <v>128947654</v>
       </c>
       <c r="B60" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>128947648</v>
       </c>
       <c r="B61" t="n">
-        <v>87015</v>
+        <v>87017</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>128947649</v>
       </c>
       <c r="B62" t="n">
-        <v>87015</v>
+        <v>87017</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>128947643</v>
       </c>
       <c r="B63" t="n">
-        <v>86935</v>
+        <v>86937</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7271,10 +7271,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128947666</v>
+        <v>128947663</v>
       </c>
       <c r="B64" t="n">
-        <v>87014</v>
+        <v>86910</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7282,21 +7282,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712159</v>
+        <v>712176</v>
       </c>
       <c r="R64" t="n">
-        <v>6358410</v>
+        <v>6358409</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7350,6 +7350,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7368,10 +7369,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128947663</v>
+        <v>128947666</v>
       </c>
       <c r="B65" t="n">
-        <v>86908</v>
+        <v>87016</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7379,21 +7380,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7403,10 +7404,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>712176</v>
+        <v>712159</v>
       </c>
       <c r="R65" t="n">
-        <v>6358409</v>
+        <v>6358410</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7447,7 +7448,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7469,7 +7469,7 @@
         <v>128947657</v>
       </c>
       <c r="B66" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>128947673</v>
       </c>
       <c r="B67" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7664,7 +7664,7 @@
         <v>128947653</v>
       </c>
       <c r="B68" t="n">
-        <v>57722</v>
+        <v>57724</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7766,32 +7766,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128947645</v>
+        <v>128947670</v>
       </c>
       <c r="B69" t="n">
-        <v>87037</v>
+        <v>86819</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7801,10 +7801,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>712060</v>
+        <v>712289</v>
       </c>
       <c r="R69" t="n">
-        <v>6358285</v>
+        <v>6358623</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7863,32 +7863,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128947670</v>
+        <v>128947645</v>
       </c>
       <c r="B70" t="n">
-        <v>86817</v>
+        <v>87039</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7898,10 +7898,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>712289</v>
+        <v>712060</v>
       </c>
       <c r="R70" t="n">
-        <v>6358623</v>
+        <v>6358285</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7963,7 +7963,7 @@
         <v>128947644</v>
       </c>
       <c r="B71" t="n">
-        <v>86935</v>
+        <v>86937</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>128947672</v>
       </c>
       <c r="B72" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>128947646</v>
       </c>
       <c r="B73" t="n">
-        <v>86979</v>
+        <v>86981</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>129004213</v>
       </c>
       <c r="B74" t="n">
-        <v>86839</v>
+        <v>86841</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>129004190</v>
       </c>
       <c r="B75" t="n">
-        <v>87015</v>
+        <v>87017</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>129004186</v>
       </c>
       <c r="B76" t="n">
-        <v>86935</v>
+        <v>86937</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>129004199</v>
       </c>
       <c r="B77" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>129004203</v>
       </c>
       <c r="B78" t="n">
-        <v>86908</v>
+        <v>86910</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>129004194</v>
       </c>
       <c r="B79" t="n">
-        <v>86817</v>
+        <v>86819</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>129004215</v>
       </c>
       <c r="B80" t="n">
-        <v>86839</v>
+        <v>86841</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9002,32 +9002,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129004195</v>
+        <v>129004211</v>
       </c>
       <c r="B81" t="n">
-        <v>86969</v>
+        <v>87016</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>249228</v>
+        <v>449</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9037,10 +9037,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>712179</v>
+        <v>712141</v>
       </c>
       <c r="R81" t="n">
-        <v>6358417</v>
+        <v>6358437</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9082,7 +9082,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>kollekt</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9091,7 +9096,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9110,32 +9114,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129004211</v>
+        <v>129004195</v>
       </c>
       <c r="B82" t="n">
-        <v>87014</v>
+        <v>86971</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>449</v>
+        <v>249228</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9145,10 +9149,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>712141</v>
+        <v>712179</v>
       </c>
       <c r="R82" t="n">
-        <v>6358437</v>
+        <v>6358417</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9180,7 +9184,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9190,12 +9194,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>kollekt</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9204,6 +9203,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9225,7 +9225,7 @@
         <v>129004208</v>
       </c>
       <c r="B83" t="n">
-        <v>87014</v>
+        <v>87016</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>129004212</v>
       </c>
       <c r="B84" t="n">
-        <v>87014</v>
+        <v>87016</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>129004207</v>
       </c>
       <c r="B85" t="n">
-        <v>87014</v>
+        <v>87016</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9549,32 +9549,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129004192</v>
+        <v>129004210</v>
       </c>
       <c r="B86" t="n">
-        <v>110804</v>
+        <v>87016</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219711</v>
+        <v>449</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9584,10 +9584,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>712118</v>
+        <v>712140</v>
       </c>
       <c r="R86" t="n">
-        <v>6358398</v>
+        <v>6358434</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9656,32 +9656,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129004210</v>
+        <v>129004192</v>
       </c>
       <c r="B87" t="n">
-        <v>87014</v>
+        <v>110806</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>449</v>
+        <v>219711</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9691,10 +9691,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>712140</v>
+        <v>712118</v>
       </c>
       <c r="R87" t="n">
-        <v>6358434</v>
+        <v>6358398</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9766,7 +9766,7 @@
         <v>129004202</v>
       </c>
       <c r="B88" t="n">
-        <v>90953</v>
+        <v>90955</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>129004200</v>
       </c>
       <c r="B89" t="n">
-        <v>86992</v>
+        <v>86994</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>129004206</v>
       </c>
       <c r="B90" t="n">
-        <v>87014</v>
+        <v>87016</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>129004204</v>
       </c>
       <c r="B91" t="n">
-        <v>86908</v>
+        <v>86910</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10188,32 +10188,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129004209</v>
+        <v>129004193</v>
       </c>
       <c r="B92" t="n">
-        <v>87014</v>
+        <v>90337</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>449</v>
+        <v>2072</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>712185</v>
+        <v>712067</v>
       </c>
       <c r="R92" t="n">
-        <v>6358414</v>
+        <v>6358371</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10277,6 +10277,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10295,32 +10296,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129004193</v>
+        <v>129004209</v>
       </c>
       <c r="B93" t="n">
-        <v>90335</v>
+        <v>87016</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2072</v>
+        <v>449</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10330,10 +10331,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>712067</v>
+        <v>712185</v>
       </c>
       <c r="R93" t="n">
-        <v>6358371</v>
+        <v>6358414</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10365,7 +10366,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10375,7 +10376,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10384,7 +10385,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10406,7 +10406,7 @@
         <v>129004188</v>
       </c>
       <c r="B94" t="n">
-        <v>87037</v>
+        <v>87039</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>129004191</v>
       </c>
       <c r="B95" t="n">
-        <v>87015</v>
+        <v>87017</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10617,32 +10617,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129004205</v>
+        <v>129004214</v>
       </c>
       <c r="B96" t="n">
-        <v>87014</v>
+        <v>86957</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10652,10 +10652,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>712139</v>
+        <v>712132</v>
       </c>
       <c r="R96" t="n">
-        <v>6358437</v>
+        <v>6358416</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10724,10 +10724,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129004201</v>
+        <v>129004187</v>
       </c>
       <c r="B97" t="n">
-        <v>86884</v>
+        <v>87039</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10735,16 +10735,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>445</v>
+        <v>3767</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10759,10 +10759,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>712185</v>
+        <v>712224</v>
       </c>
       <c r="R97" t="n">
-        <v>6358418</v>
+        <v>6358420</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10831,32 +10831,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129004214</v>
+        <v>129004205</v>
       </c>
       <c r="B98" t="n">
-        <v>86955</v>
+        <v>87016</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10866,10 +10866,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>712132</v>
+        <v>712139</v>
       </c>
       <c r="R98" t="n">
-        <v>6358416</v>
+        <v>6358437</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10938,10 +10938,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129004187</v>
+        <v>129004201</v>
       </c>
       <c r="B99" t="n">
-        <v>87037</v>
+        <v>86886</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10949,16 +10949,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3767</v>
+        <v>445</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10973,10 +10973,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>712224</v>
+        <v>712185</v>
       </c>
       <c r="R99" t="n">
-        <v>6358420</v>
+        <v>6358418</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD99" t="b">

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -5509,32 +5509,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128947671</v>
+        <v>128947652</v>
       </c>
       <c r="B46" t="n">
-        <v>86819</v>
+        <v>86841</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>712289</v>
+        <v>712290</v>
       </c>
       <c r="R46" t="n">
         <v>6358633</v>
@@ -5606,32 +5606,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128947652</v>
+        <v>128947671</v>
       </c>
       <c r="B47" t="n">
-        <v>86841</v>
+        <v>86819</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>712290</v>
+        <v>712289</v>
       </c>
       <c r="R47" t="n">
         <v>6358633</v>
@@ -5899,10 +5899,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128947664</v>
+        <v>128947675</v>
       </c>
       <c r="B50" t="n">
-        <v>91962</v>
+        <v>86957</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5910,21 +5910,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5420</v>
+        <v>3674</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>712272</v>
+        <v>712229</v>
       </c>
       <c r="R50" t="n">
-        <v>6358461</v>
+        <v>6358510</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -6093,10 +6093,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128947675</v>
+        <v>128947664</v>
       </c>
       <c r="B52" t="n">
-        <v>86957</v>
+        <v>91962</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6104,21 +6104,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3674</v>
+        <v>5420</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6128,10 +6128,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712229</v>
+        <v>712272</v>
       </c>
       <c r="R52" t="n">
-        <v>6358510</v>
+        <v>6358461</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6482,10 +6482,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128947667</v>
+        <v>128947669</v>
       </c>
       <c r="B56" t="n">
-        <v>92871</v>
+        <v>86819</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6493,37 +6493,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5964</v>
+        <v>3712</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>712163</v>
+        <v>712363</v>
       </c>
       <c r="R56" t="n">
-        <v>6358380</v>
+        <v>6358457</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6564,7 +6561,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6583,10 +6579,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128947669</v>
+        <v>128947667</v>
       </c>
       <c r="B57" t="n">
-        <v>86819</v>
+        <v>92871</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6594,34 +6590,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3712</v>
+        <v>5964</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712363</v>
+        <v>712163</v>
       </c>
       <c r="R57" t="n">
-        <v>6358457</v>
+        <v>6358380</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6662,6 +6661,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -7271,10 +7271,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128947663</v>
+        <v>128947666</v>
       </c>
       <c r="B64" t="n">
-        <v>86910</v>
+        <v>87016</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7282,21 +7282,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712176</v>
+        <v>712159</v>
       </c>
       <c r="R64" t="n">
-        <v>6358409</v>
+        <v>6358410</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7350,7 +7350,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7369,10 +7368,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128947666</v>
+        <v>128947663</v>
       </c>
       <c r="B65" t="n">
-        <v>87016</v>
+        <v>86910</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7380,21 +7379,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7404,10 +7403,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>712159</v>
+        <v>712176</v>
       </c>
       <c r="R65" t="n">
-        <v>6358410</v>
+        <v>6358409</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7448,6 +7447,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7766,32 +7766,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128947670</v>
+        <v>128947645</v>
       </c>
       <c r="B69" t="n">
-        <v>86819</v>
+        <v>87039</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7801,10 +7801,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>712289</v>
+        <v>712060</v>
       </c>
       <c r="R69" t="n">
-        <v>6358623</v>
+        <v>6358285</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7863,32 +7863,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128947645</v>
+        <v>128947670</v>
       </c>
       <c r="B70" t="n">
-        <v>87039</v>
+        <v>86819</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7898,10 +7898,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>712060</v>
+        <v>712289</v>
       </c>
       <c r="R70" t="n">
-        <v>6358285</v>
+        <v>6358623</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -10188,32 +10188,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129004193</v>
+        <v>129004209</v>
       </c>
       <c r="B92" t="n">
-        <v>90337</v>
+        <v>87016</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2072</v>
+        <v>449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>712067</v>
+        <v>712185</v>
       </c>
       <c r="R92" t="n">
-        <v>6358371</v>
+        <v>6358414</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10277,7 +10277,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10296,32 +10295,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129004209</v>
+        <v>129004193</v>
       </c>
       <c r="B93" t="n">
-        <v>87016</v>
+        <v>90337</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>449</v>
+        <v>2072</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10331,10 +10330,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>712185</v>
+        <v>712067</v>
       </c>
       <c r="R93" t="n">
-        <v>6358414</v>
+        <v>6358371</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10366,7 +10365,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10376,7 +10375,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10385,6 +10384,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -5899,10 +5899,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128947675</v>
+        <v>128947664</v>
       </c>
       <c r="B50" t="n">
-        <v>86957</v>
+        <v>91962</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5910,21 +5910,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3674</v>
+        <v>5420</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>712229</v>
+        <v>712272</v>
       </c>
       <c r="R50" t="n">
-        <v>6358510</v>
+        <v>6358461</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5996,10 +5996,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128947674</v>
+        <v>128947675</v>
       </c>
       <c r="B51" t="n">
-        <v>86819</v>
+        <v>86957</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6007,21 +6007,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712125</v>
+        <v>712229</v>
       </c>
       <c r="R51" t="n">
-        <v>6358399</v>
+        <v>6358510</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6093,10 +6093,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128947664</v>
+        <v>128947674</v>
       </c>
       <c r="B52" t="n">
-        <v>91962</v>
+        <v>86819</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6104,21 +6104,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5420</v>
+        <v>3712</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6128,10 +6128,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712272</v>
+        <v>712125</v>
       </c>
       <c r="R52" t="n">
-        <v>6358461</v>
+        <v>6358399</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7271,10 +7271,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128947666</v>
+        <v>128947663</v>
       </c>
       <c r="B64" t="n">
-        <v>87016</v>
+        <v>86910</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7282,21 +7282,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712159</v>
+        <v>712176</v>
       </c>
       <c r="R64" t="n">
-        <v>6358410</v>
+        <v>6358409</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7350,6 +7350,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7368,10 +7369,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128947663</v>
+        <v>128947666</v>
       </c>
       <c r="B65" t="n">
-        <v>86910</v>
+        <v>87016</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7379,21 +7380,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7403,10 +7404,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>712176</v>
+        <v>712159</v>
       </c>
       <c r="R65" t="n">
-        <v>6358409</v>
+        <v>6358410</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7447,7 +7448,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8252,32 +8252,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129004213</v>
+        <v>129004190</v>
       </c>
       <c r="B74" t="n">
-        <v>86841</v>
+        <v>87017</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>424</v>
+        <v>248947</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>712140</v>
+        <v>712178</v>
       </c>
       <c r="R74" t="n">
-        <v>6358430</v>
+        <v>6358421</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8359,32 +8359,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129004190</v>
+        <v>129004213</v>
       </c>
       <c r="B75" t="n">
-        <v>87017</v>
+        <v>86841</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>248947</v>
+        <v>424</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8394,10 +8394,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>712178</v>
+        <v>712140</v>
       </c>
       <c r="R75" t="n">
-        <v>6358421</v>
+        <v>6358430</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD75" t="b">

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -5509,32 +5509,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128947652</v>
+        <v>128947671</v>
       </c>
       <c r="B46" t="n">
-        <v>86841</v>
+        <v>86820</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>712290</v>
+        <v>712289</v>
       </c>
       <c r="R46" t="n">
         <v>6358633</v>
@@ -5606,32 +5606,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128947671</v>
+        <v>128947652</v>
       </c>
       <c r="B47" t="n">
-        <v>86819</v>
+        <v>86842</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>712289</v>
+        <v>712290</v>
       </c>
       <c r="R47" t="n">
         <v>6358633</v>
@@ -5706,7 +5706,7 @@
         <v>128947656</v>
       </c>
       <c r="B48" t="n">
-        <v>86994</v>
+        <v>86995</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>128947660</v>
       </c>
       <c r="B49" t="n">
-        <v>86994</v>
+        <v>86995</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>128947664</v>
       </c>
       <c r="B50" t="n">
-        <v>91962</v>
+        <v>91971</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5996,10 +5996,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128947675</v>
+        <v>128947674</v>
       </c>
       <c r="B51" t="n">
-        <v>86957</v>
+        <v>86820</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6007,21 +6007,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712229</v>
+        <v>712125</v>
       </c>
       <c r="R51" t="n">
-        <v>6358510</v>
+        <v>6358399</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6093,10 +6093,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128947674</v>
+        <v>128947675</v>
       </c>
       <c r="B52" t="n">
-        <v>86819</v>
+        <v>86958</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6104,21 +6104,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6128,10 +6128,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712125</v>
+        <v>712229</v>
       </c>
       <c r="R52" t="n">
-        <v>6358399</v>
+        <v>6358510</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6193,7 +6193,7 @@
         <v>128947659</v>
       </c>
       <c r="B53" t="n">
-        <v>86994</v>
+        <v>86995</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>128947677</v>
       </c>
       <c r="B54" t="n">
-        <v>86957</v>
+        <v>86958</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>128947676</v>
       </c>
       <c r="B55" t="n">
-        <v>86957</v>
+        <v>86958</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6482,10 +6482,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128947669</v>
+        <v>128947667</v>
       </c>
       <c r="B56" t="n">
-        <v>86819</v>
+        <v>92857</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6493,34 +6493,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3712</v>
+        <v>5964</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>712363</v>
+        <v>712163</v>
       </c>
       <c r="R56" t="n">
-        <v>6358457</v>
+        <v>6358380</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6561,6 +6564,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6579,10 +6583,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128947667</v>
+        <v>128947669</v>
       </c>
       <c r="B57" t="n">
-        <v>92871</v>
+        <v>86820</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6590,37 +6594,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5964</v>
+        <v>3712</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712163</v>
+        <v>712363</v>
       </c>
       <c r="R57" t="n">
-        <v>6358380</v>
+        <v>6358457</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6661,7 +6662,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6683,7 +6683,7 @@
         <v>128947647</v>
       </c>
       <c r="B58" t="n">
-        <v>87017</v>
+        <v>87018</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6777,32 +6777,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128947655</v>
+        <v>128947648</v>
       </c>
       <c r="B59" t="n">
-        <v>86795</v>
+        <v>87018</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3762</v>
+        <v>248947</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712080</v>
+        <v>712168</v>
       </c>
       <c r="R59" t="n">
-        <v>6358365</v>
+        <v>6358403</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6874,53 +6874,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128947654</v>
+        <v>128947649</v>
       </c>
       <c r="B60" t="n">
-        <v>57724</v>
+        <v>87018</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>248947</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712106</v>
+        <v>712051</v>
       </c>
       <c r="R60" t="n">
-        <v>6358348</v>
+        <v>6358299</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6979,45 +6971,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128947648</v>
+        <v>128947654</v>
       </c>
       <c r="B61" t="n">
-        <v>87017</v>
+        <v>57724</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>248947</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712168</v>
+        <v>712106</v>
       </c>
       <c r="R61" t="n">
-        <v>6358403</v>
+        <v>6358348</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7076,32 +7076,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128947649</v>
+        <v>128947655</v>
       </c>
       <c r="B62" t="n">
-        <v>87017</v>
+        <v>86796</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>248947</v>
+        <v>3762</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7111,10 +7111,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712051</v>
+        <v>712080</v>
       </c>
       <c r="R62" t="n">
-        <v>6358299</v>
+        <v>6358365</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7176,7 +7176,7 @@
         <v>128947643</v>
       </c>
       <c r="B63" t="n">
-        <v>86937</v>
+        <v>86938</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7271,10 +7271,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128947663</v>
+        <v>128947666</v>
       </c>
       <c r="B64" t="n">
-        <v>86910</v>
+        <v>87017</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7282,21 +7282,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712176</v>
+        <v>712159</v>
       </c>
       <c r="R64" t="n">
-        <v>6358409</v>
+        <v>6358410</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7350,7 +7350,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7369,10 +7368,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128947666</v>
+        <v>128947663</v>
       </c>
       <c r="B65" t="n">
-        <v>87016</v>
+        <v>86911</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7380,21 +7379,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7404,10 +7403,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>712159</v>
+        <v>712176</v>
       </c>
       <c r="R65" t="n">
-        <v>6358410</v>
+        <v>6358409</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7448,6 +7447,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7469,7 +7469,7 @@
         <v>128947657</v>
       </c>
       <c r="B66" t="n">
-        <v>86994</v>
+        <v>86995</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>128947673</v>
       </c>
       <c r="B67" t="n">
-        <v>86819</v>
+        <v>86820</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7766,32 +7766,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128947645</v>
+        <v>128947670</v>
       </c>
       <c r="B69" t="n">
-        <v>87039</v>
+        <v>86820</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7801,10 +7801,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>712060</v>
+        <v>712289</v>
       </c>
       <c r="R69" t="n">
-        <v>6358285</v>
+        <v>6358623</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7863,32 +7863,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128947670</v>
+        <v>128947645</v>
       </c>
       <c r="B70" t="n">
-        <v>86819</v>
+        <v>87040</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7898,10 +7898,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>712289</v>
+        <v>712060</v>
       </c>
       <c r="R70" t="n">
-        <v>6358623</v>
+        <v>6358285</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7963,7 +7963,7 @@
         <v>128947644</v>
       </c>
       <c r="B71" t="n">
-        <v>86937</v>
+        <v>86938</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>128947672</v>
       </c>
       <c r="B72" t="n">
-        <v>86819</v>
+        <v>86820</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>128947646</v>
       </c>
       <c r="B73" t="n">
-        <v>86981</v>
+        <v>86982</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>129004190</v>
       </c>
       <c r="B74" t="n">
-        <v>87017</v>
+        <v>87018</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>129004213</v>
       </c>
       <c r="B75" t="n">
-        <v>86841</v>
+        <v>86842</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>129004186</v>
       </c>
       <c r="B76" t="n">
-        <v>86937</v>
+        <v>86938</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>129004199</v>
       </c>
       <c r="B77" t="n">
-        <v>86994</v>
+        <v>86995</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>129004203</v>
       </c>
       <c r="B78" t="n">
-        <v>86910</v>
+        <v>86911</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8788,32 +8788,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129004194</v>
+        <v>129004215</v>
       </c>
       <c r="B79" t="n">
-        <v>86819</v>
+        <v>86842</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>712133</v>
+        <v>712139</v>
       </c>
       <c r="R79" t="n">
-        <v>6358398</v>
+        <v>6358436</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8895,32 +8895,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129004215</v>
+        <v>129004194</v>
       </c>
       <c r="B80" t="n">
-        <v>86841</v>
+        <v>86820</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>712139</v>
+        <v>712133</v>
       </c>
       <c r="R80" t="n">
-        <v>6358436</v>
+        <v>6358398</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9002,32 +9002,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129004211</v>
+        <v>129004195</v>
       </c>
       <c r="B81" t="n">
-        <v>87016</v>
+        <v>86972</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>449</v>
+        <v>249228</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9037,10 +9037,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>712141</v>
+        <v>712179</v>
       </c>
       <c r="R81" t="n">
-        <v>6358437</v>
+        <v>6358417</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9082,12 +9082,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>kollekt</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9096,6 +9091,7 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
+      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9114,32 +9110,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129004195</v>
+        <v>129004211</v>
       </c>
       <c r="B82" t="n">
-        <v>86971</v>
+        <v>87017</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>249228</v>
+        <v>449</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9149,10 +9145,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>712179</v>
+        <v>712141</v>
       </c>
       <c r="R82" t="n">
-        <v>6358417</v>
+        <v>6358437</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9184,7 +9180,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9194,7 +9190,12 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>kollekt</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9203,7 +9204,6 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
-      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9225,7 +9225,7 @@
         <v>129004208</v>
       </c>
       <c r="B83" t="n">
-        <v>87016</v>
+        <v>87017</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>129004212</v>
       </c>
       <c r="B84" t="n">
-        <v>87016</v>
+        <v>87017</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>129004207</v>
       </c>
       <c r="B85" t="n">
-        <v>87016</v>
+        <v>87017</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>129004210</v>
       </c>
       <c r="B86" t="n">
-        <v>87016</v>
+        <v>87017</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>129004192</v>
       </c>
       <c r="B87" t="n">
-        <v>110806</v>
+        <v>110832</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>129004202</v>
       </c>
       <c r="B88" t="n">
-        <v>90955</v>
+        <v>90956</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>129004200</v>
       </c>
       <c r="B89" t="n">
-        <v>86994</v>
+        <v>86995</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>129004206</v>
       </c>
       <c r="B90" t="n">
-        <v>87016</v>
+        <v>87017</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>129004204</v>
       </c>
       <c r="B91" t="n">
-        <v>86910</v>
+        <v>86911</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10188,32 +10188,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129004209</v>
+        <v>129004193</v>
       </c>
       <c r="B92" t="n">
-        <v>87016</v>
+        <v>90338</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>449</v>
+        <v>2072</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>712185</v>
+        <v>712067</v>
       </c>
       <c r="R92" t="n">
-        <v>6358414</v>
+        <v>6358371</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10277,6 +10277,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10295,32 +10296,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129004193</v>
+        <v>129004209</v>
       </c>
       <c r="B93" t="n">
-        <v>90337</v>
+        <v>87017</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2072</v>
+        <v>449</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10330,10 +10331,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>712067</v>
+        <v>712185</v>
       </c>
       <c r="R93" t="n">
-        <v>6358371</v>
+        <v>6358414</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10365,7 +10366,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10375,7 +10376,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10384,7 +10385,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10406,7 +10406,7 @@
         <v>129004188</v>
       </c>
       <c r="B94" t="n">
-        <v>87039</v>
+        <v>87040</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>129004191</v>
       </c>
       <c r="B95" t="n">
-        <v>87017</v>
+        <v>87018</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10617,32 +10617,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129004214</v>
+        <v>129004205</v>
       </c>
       <c r="B96" t="n">
-        <v>86957</v>
+        <v>87017</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10652,10 +10652,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>712132</v>
+        <v>712139</v>
       </c>
       <c r="R96" t="n">
-        <v>6358416</v>
+        <v>6358437</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10724,10 +10724,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129004187</v>
+        <v>129004201</v>
       </c>
       <c r="B97" t="n">
-        <v>87039</v>
+        <v>86887</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10735,16 +10735,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3767</v>
+        <v>445</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10759,10 +10759,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>712224</v>
+        <v>712185</v>
       </c>
       <c r="R97" t="n">
-        <v>6358420</v>
+        <v>6358418</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10831,10 +10831,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129004205</v>
+        <v>129004187</v>
       </c>
       <c r="B98" t="n">
-        <v>87016</v>
+        <v>87040</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10842,21 +10842,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>449</v>
+        <v>3767</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10866,10 +10866,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>712139</v>
+        <v>712224</v>
       </c>
       <c r="R98" t="n">
-        <v>6358437</v>
+        <v>6358420</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10938,32 +10938,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129004201</v>
+        <v>129004214</v>
       </c>
       <c r="B99" t="n">
-        <v>86886</v>
+        <v>86958</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>445</v>
+        <v>3674</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10973,10 +10973,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>712185</v>
+        <v>712132</v>
       </c>
       <c r="R99" t="n">
-        <v>6358418</v>
+        <v>6358416</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD99" t="b">

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -5899,10 +5899,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128947664</v>
+        <v>128947674</v>
       </c>
       <c r="B50" t="n">
-        <v>91971</v>
+        <v>86820</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5910,21 +5910,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5420</v>
+        <v>3712</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>712272</v>
+        <v>712125</v>
       </c>
       <c r="R50" t="n">
-        <v>6358461</v>
+        <v>6358399</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5996,10 +5996,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128947674</v>
+        <v>128947675</v>
       </c>
       <c r="B51" t="n">
-        <v>86820</v>
+        <v>86958</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6007,21 +6007,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712125</v>
+        <v>712229</v>
       </c>
       <c r="R51" t="n">
-        <v>6358399</v>
+        <v>6358510</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6093,10 +6093,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128947675</v>
+        <v>128947664</v>
       </c>
       <c r="B52" t="n">
-        <v>86958</v>
+        <v>91972</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6104,21 +6104,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3674</v>
+        <v>5420</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6128,10 +6128,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712229</v>
+        <v>712272</v>
       </c>
       <c r="R52" t="n">
-        <v>6358510</v>
+        <v>6358461</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6485,7 +6485,7 @@
         <v>128947667</v>
       </c>
       <c r="B56" t="n">
-        <v>92857</v>
+        <v>92858</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6777,32 +6777,32 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128947648</v>
+        <v>128947655</v>
       </c>
       <c r="B59" t="n">
-        <v>87018</v>
+        <v>86796</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>248947</v>
+        <v>3762</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6812,10 +6812,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712168</v>
+        <v>712080</v>
       </c>
       <c r="R59" t="n">
-        <v>6358403</v>
+        <v>6358365</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6874,45 +6874,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128947649</v>
+        <v>128947654</v>
       </c>
       <c r="B60" t="n">
-        <v>87018</v>
+        <v>57724</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>248947</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712051</v>
+        <v>712106</v>
       </c>
       <c r="R60" t="n">
-        <v>6358299</v>
+        <v>6358348</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6971,53 +6979,45 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128947654</v>
+        <v>128947648</v>
       </c>
       <c r="B61" t="n">
-        <v>57724</v>
+        <v>87018</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100049</v>
+        <v>248947</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712106</v>
+        <v>712168</v>
       </c>
       <c r="R61" t="n">
-        <v>6358348</v>
+        <v>6358403</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7076,32 +7076,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128947655</v>
+        <v>128947649</v>
       </c>
       <c r="B62" t="n">
-        <v>86796</v>
+        <v>87018</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>3762</v>
+        <v>248947</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7111,10 +7111,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712080</v>
+        <v>712051</v>
       </c>
       <c r="R62" t="n">
-        <v>6358365</v>
+        <v>6358299</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7564,45 +7564,53 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128947673</v>
+        <v>128947653</v>
       </c>
       <c r="B67" t="n">
-        <v>86820</v>
+        <v>57724</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3712</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>712157</v>
+        <v>712303</v>
       </c>
       <c r="R67" t="n">
-        <v>6358456</v>
+        <v>6358650</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7661,53 +7669,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128947653</v>
+        <v>128947673</v>
       </c>
       <c r="B68" t="n">
-        <v>57724</v>
+        <v>86820</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>3712</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>712303</v>
+        <v>712157</v>
       </c>
       <c r="R68" t="n">
-        <v>6358650</v>
+        <v>6358456</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -9002,32 +9002,32 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>129004195</v>
+        <v>129004211</v>
       </c>
       <c r="B81" t="n">
-        <v>86972</v>
+        <v>87017</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>249228</v>
+        <v>449</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9037,10 +9037,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>712179</v>
+        <v>712141</v>
       </c>
       <c r="R81" t="n">
-        <v>6358417</v>
+        <v>6358437</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9072,7 +9072,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:19</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9082,7 +9082,12 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>13:15</t>
+          <t>12:19</t>
+        </is>
+      </c>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>kollekt</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9091,7 +9096,6 @@
       <c r="AE81" t="b">
         <v>0</v>
       </c>
-      <c r="AF81" t="inlineStr"/>
       <c r="AG81" t="b">
         <v>0</v>
       </c>
@@ -9110,32 +9114,32 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>129004211</v>
+        <v>129004195</v>
       </c>
       <c r="B82" t="n">
-        <v>87017</v>
+        <v>86972</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>449</v>
+        <v>249228</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9145,10 +9149,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>712141</v>
+        <v>712179</v>
       </c>
       <c r="R82" t="n">
-        <v>6358437</v>
+        <v>6358417</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9180,7 +9184,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>12:19</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -9190,12 +9194,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>12:19</t>
-        </is>
-      </c>
-      <c r="AC82" t="inlineStr">
-        <is>
-          <t>kollekt</t>
+          <t>13:15</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9204,6 +9203,7 @@
       <c r="AE82" t="b">
         <v>0</v>
       </c>
+      <c r="AF82" t="inlineStr"/>
       <c r="AG82" t="b">
         <v>0</v>
       </c>
@@ -9549,32 +9549,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129004210</v>
+        <v>129004192</v>
       </c>
       <c r="B86" t="n">
-        <v>87017</v>
+        <v>110834</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>449</v>
+        <v>219711</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9584,10 +9584,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>712140</v>
+        <v>712118</v>
       </c>
       <c r="R86" t="n">
-        <v>6358434</v>
+        <v>6358398</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9656,32 +9656,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129004192</v>
+        <v>129004210</v>
       </c>
       <c r="B87" t="n">
-        <v>110832</v>
+        <v>87017</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219711</v>
+        <v>449</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9691,10 +9691,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>712118</v>
+        <v>712140</v>
       </c>
       <c r="R87" t="n">
-        <v>6358398</v>
+        <v>6358434</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10188,32 +10188,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129004193</v>
+        <v>129004209</v>
       </c>
       <c r="B92" t="n">
-        <v>90338</v>
+        <v>87017</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2072</v>
+        <v>449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>712067</v>
+        <v>712185</v>
       </c>
       <c r="R92" t="n">
-        <v>6358371</v>
+        <v>6358414</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10277,7 +10277,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10296,32 +10295,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129004209</v>
+        <v>129004193</v>
       </c>
       <c r="B93" t="n">
-        <v>87017</v>
+        <v>90338</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>449</v>
+        <v>2072</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10331,10 +10330,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>712185</v>
+        <v>712067</v>
       </c>
       <c r="R93" t="n">
-        <v>6358414</v>
+        <v>6358371</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10366,7 +10365,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10376,7 +10375,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10385,6 +10384,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10831,32 +10831,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129004187</v>
+        <v>129004214</v>
       </c>
       <c r="B98" t="n">
-        <v>87040</v>
+        <v>86958</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3767</v>
+        <v>3674</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10866,10 +10866,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>712224</v>
+        <v>712132</v>
       </c>
       <c r="R98" t="n">
-        <v>6358420</v>
+        <v>6358416</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10938,32 +10938,32 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129004214</v>
+        <v>129004187</v>
       </c>
       <c r="B99" t="n">
-        <v>86958</v>
+        <v>87040</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3674</v>
+        <v>3767</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -10973,10 +10973,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>712132</v>
+        <v>712224</v>
       </c>
       <c r="R99" t="n">
-        <v>6358416</v>
+        <v>6358420</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD99" t="b">

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -5509,32 +5509,32 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>128947671</v>
+        <v>128947652</v>
       </c>
       <c r="B46" t="n">
-        <v>86820</v>
+        <v>86842</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5544,7 +5544,7 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>712289</v>
+        <v>712290</v>
       </c>
       <c r="R46" t="n">
         <v>6358633</v>
@@ -5606,32 +5606,32 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>128947652</v>
+        <v>128947671</v>
       </c>
       <c r="B47" t="n">
-        <v>86842</v>
+        <v>86820</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5641,7 +5641,7 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>712290</v>
+        <v>712289</v>
       </c>
       <c r="R47" t="n">
         <v>6358633</v>
@@ -5899,10 +5899,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128947674</v>
+        <v>128947675</v>
       </c>
       <c r="B50" t="n">
-        <v>86820</v>
+        <v>86958</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5910,21 +5910,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>712125</v>
+        <v>712229</v>
       </c>
       <c r="R50" t="n">
-        <v>6358399</v>
+        <v>6358510</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5996,10 +5996,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128947675</v>
+        <v>128947674</v>
       </c>
       <c r="B51" t="n">
-        <v>86958</v>
+        <v>86820</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6007,21 +6007,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712229</v>
+        <v>712125</v>
       </c>
       <c r="R51" t="n">
-        <v>6358510</v>
+        <v>6358399</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6874,53 +6874,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128947654</v>
+        <v>128947648</v>
       </c>
       <c r="B60" t="n">
-        <v>57724</v>
+        <v>87018</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>248947</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712106</v>
+        <v>712168</v>
       </c>
       <c r="R60" t="n">
-        <v>6358348</v>
+        <v>6358403</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6979,7 +6971,7 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128947648</v>
+        <v>128947649</v>
       </c>
       <c r="B61" t="n">
         <v>87018</v>
@@ -7014,10 +7006,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712168</v>
+        <v>712051</v>
       </c>
       <c r="R61" t="n">
-        <v>6358403</v>
+        <v>6358299</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7076,45 +7068,53 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128947649</v>
+        <v>128947654</v>
       </c>
       <c r="B62" t="n">
-        <v>87018</v>
+        <v>57724</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>248947</v>
+        <v>100049</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712051</v>
+        <v>712106</v>
       </c>
       <c r="R62" t="n">
-        <v>6358299</v>
+        <v>6358348</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7564,53 +7564,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128947653</v>
+        <v>128947673</v>
       </c>
       <c r="B67" t="n">
-        <v>57724</v>
+        <v>86820</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>3712</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>712303</v>
+        <v>712157</v>
       </c>
       <c r="R67" t="n">
-        <v>6358650</v>
+        <v>6358456</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7669,45 +7661,53 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128947673</v>
+        <v>128947653</v>
       </c>
       <c r="B68" t="n">
-        <v>86820</v>
+        <v>57724</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3712</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>712157</v>
+        <v>712303</v>
       </c>
       <c r="R68" t="n">
-        <v>6358456</v>
+        <v>6358650</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7766,32 +7766,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128947670</v>
+        <v>128947645</v>
       </c>
       <c r="B69" t="n">
-        <v>86820</v>
+        <v>87040</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7801,10 +7801,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>712289</v>
+        <v>712060</v>
       </c>
       <c r="R69" t="n">
-        <v>6358623</v>
+        <v>6358285</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7863,32 +7863,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128947645</v>
+        <v>128947670</v>
       </c>
       <c r="B70" t="n">
-        <v>87040</v>
+        <v>86820</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7898,10 +7898,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>712060</v>
+        <v>712289</v>
       </c>
       <c r="R70" t="n">
-        <v>6358285</v>
+        <v>6358623</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8252,32 +8252,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129004190</v>
+        <v>129004213</v>
       </c>
       <c r="B74" t="n">
-        <v>87018</v>
+        <v>86842</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>248947</v>
+        <v>424</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>712178</v>
+        <v>712140</v>
       </c>
       <c r="R74" t="n">
-        <v>6358421</v>
+        <v>6358430</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8359,32 +8359,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129004213</v>
+        <v>129004190</v>
       </c>
       <c r="B75" t="n">
-        <v>86842</v>
+        <v>87018</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>424</v>
+        <v>248947</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8394,10 +8394,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>712140</v>
+        <v>712178</v>
       </c>
       <c r="R75" t="n">
-        <v>6358430</v>
+        <v>6358421</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9549,32 +9549,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129004192</v>
+        <v>129004210</v>
       </c>
       <c r="B86" t="n">
-        <v>110834</v>
+        <v>87017</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219711</v>
+        <v>449</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9584,10 +9584,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>712118</v>
+        <v>712140</v>
       </c>
       <c r="R86" t="n">
-        <v>6358398</v>
+        <v>6358434</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9656,32 +9656,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129004210</v>
+        <v>129004192</v>
       </c>
       <c r="B87" t="n">
-        <v>87017</v>
+        <v>110835</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>449</v>
+        <v>219711</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9691,10 +9691,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>712140</v>
+        <v>712118</v>
       </c>
       <c r="R87" t="n">
-        <v>6358434</v>
+        <v>6358398</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9974,10 +9974,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129004206</v>
+        <v>129004204</v>
       </c>
       <c r="B90" t="n">
-        <v>87017</v>
+        <v>86911</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9985,21 +9985,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10009,10 +10009,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>712178</v>
+        <v>712180</v>
       </c>
       <c r="R90" t="n">
-        <v>6358418</v>
+        <v>6358430</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10081,10 +10081,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129004204</v>
+        <v>129004206</v>
       </c>
       <c r="B91" t="n">
-        <v>86911</v>
+        <v>87017</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10092,21 +10092,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10116,10 +10116,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>712180</v>
+        <v>712178</v>
       </c>
       <c r="R91" t="n">
-        <v>6358430</v>
+        <v>6358418</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10403,32 +10403,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129004188</v>
+        <v>129004191</v>
       </c>
       <c r="B94" t="n">
-        <v>87040</v>
+        <v>87018</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3767</v>
+        <v>248947</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10438,10 +10438,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>712181</v>
+        <v>712118</v>
       </c>
       <c r="R94" t="n">
-        <v>6358403</v>
+        <v>6358397</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10510,32 +10510,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129004191</v>
+        <v>129004188</v>
       </c>
       <c r="B95" t="n">
-        <v>87018</v>
+        <v>87040</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>248947</v>
+        <v>3767</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10545,10 +10545,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>712118</v>
+        <v>712181</v>
       </c>
       <c r="R95" t="n">
-        <v>6358397</v>
+        <v>6358403</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD95" t="b">

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -5512,7 +5512,7 @@
         <v>128947652</v>
       </c>
       <c r="B46" t="n">
-        <v>86842</v>
+        <v>86845</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>128947671</v>
       </c>
       <c r="B47" t="n">
-        <v>86820</v>
+        <v>86823</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>128947656</v>
       </c>
       <c r="B48" t="n">
-        <v>86995</v>
+        <v>86998</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>128947660</v>
       </c>
       <c r="B49" t="n">
-        <v>86995</v>
+        <v>86998</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>128947675</v>
       </c>
       <c r="B50" t="n">
-        <v>86958</v>
+        <v>86961</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5999,7 +5999,7 @@
         <v>128947674</v>
       </c>
       <c r="B51" t="n">
-        <v>86820</v>
+        <v>86823</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6096,7 +6096,7 @@
         <v>128947664</v>
       </c>
       <c r="B52" t="n">
-        <v>91972</v>
+        <v>91975</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6193,7 +6193,7 @@
         <v>128947659</v>
       </c>
       <c r="B53" t="n">
-        <v>86995</v>
+        <v>86998</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>128947677</v>
       </c>
       <c r="B54" t="n">
-        <v>86958</v>
+        <v>86961</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>128947676</v>
       </c>
       <c r="B55" t="n">
-        <v>86958</v>
+        <v>86961</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>128947667</v>
       </c>
       <c r="B56" t="n">
-        <v>92858</v>
+        <v>92861</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>128947669</v>
       </c>
       <c r="B57" t="n">
-        <v>86820</v>
+        <v>86823</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>128947647</v>
       </c>
       <c r="B58" t="n">
-        <v>87018</v>
+        <v>87021</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>128947655</v>
       </c>
       <c r="B59" t="n">
-        <v>86796</v>
+        <v>86799</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6874,45 +6874,53 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128947648</v>
+        <v>128947654</v>
       </c>
       <c r="B60" t="n">
-        <v>87018</v>
+        <v>57724</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>248947</v>
+        <v>100049</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712168</v>
+        <v>712106</v>
       </c>
       <c r="R60" t="n">
-        <v>6358403</v>
+        <v>6358348</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6971,10 +6979,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128947649</v>
+        <v>128947648</v>
       </c>
       <c r="B61" t="n">
-        <v>87018</v>
+        <v>87021</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7006,10 +7014,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712051</v>
+        <v>712168</v>
       </c>
       <c r="R61" t="n">
-        <v>6358299</v>
+        <v>6358403</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7068,53 +7076,45 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128947654</v>
+        <v>128947649</v>
       </c>
       <c r="B62" t="n">
-        <v>57724</v>
+        <v>87021</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100049</v>
+        <v>248947</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712106</v>
+        <v>712051</v>
       </c>
       <c r="R62" t="n">
-        <v>6358348</v>
+        <v>6358299</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7176,7 +7176,7 @@
         <v>128947643</v>
       </c>
       <c r="B63" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7274,7 +7274,7 @@
         <v>128947666</v>
       </c>
       <c r="B64" t="n">
-        <v>87017</v>
+        <v>87020</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7371,7 +7371,7 @@
         <v>128947663</v>
       </c>
       <c r="B65" t="n">
-        <v>86911</v>
+        <v>86914</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7469,7 +7469,7 @@
         <v>128947657</v>
       </c>
       <c r="B66" t="n">
-        <v>86995</v>
+        <v>86998</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7564,45 +7564,53 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128947673</v>
+        <v>128947653</v>
       </c>
       <c r="B67" t="n">
-        <v>86820</v>
+        <v>57724</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>3712</v>
+        <v>100049</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
+      <c r="K67" t="inlineStr"/>
+      <c r="L67" t="inlineStr"/>
+      <c r="M67" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>712157</v>
+        <v>712303</v>
       </c>
       <c r="R67" t="n">
-        <v>6358456</v>
+        <v>6358650</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7661,53 +7669,45 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128947653</v>
+        <v>128947673</v>
       </c>
       <c r="B68" t="n">
-        <v>57724</v>
+        <v>86823</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100049</v>
+        <v>3712</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
-      <c r="K68" t="inlineStr"/>
-      <c r="L68" t="inlineStr"/>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>712303</v>
+        <v>712157</v>
       </c>
       <c r="R68" t="n">
-        <v>6358650</v>
+        <v>6358456</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7769,7 +7769,7 @@
         <v>128947645</v>
       </c>
       <c r="B69" t="n">
-        <v>87040</v>
+        <v>87043</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>128947670</v>
       </c>
       <c r="B70" t="n">
-        <v>86820</v>
+        <v>86823</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>128947644</v>
       </c>
       <c r="B71" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>128947672</v>
       </c>
       <c r="B72" t="n">
-        <v>86820</v>
+        <v>86823</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>128947646</v>
       </c>
       <c r="B73" t="n">
-        <v>86982</v>
+        <v>86985</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>129004213</v>
       </c>
       <c r="B74" t="n">
-        <v>86842</v>
+        <v>86845</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>129004190</v>
       </c>
       <c r="B75" t="n">
-        <v>87018</v>
+        <v>87021</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>129004186</v>
       </c>
       <c r="B76" t="n">
-        <v>86938</v>
+        <v>86941</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>129004199</v>
       </c>
       <c r="B77" t="n">
-        <v>86995</v>
+        <v>86998</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>129004203</v>
       </c>
       <c r="B78" t="n">
-        <v>86911</v>
+        <v>86914</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8788,32 +8788,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129004215</v>
+        <v>129004194</v>
       </c>
       <c r="B79" t="n">
-        <v>86842</v>
+        <v>86823</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>712139</v>
+        <v>712133</v>
       </c>
       <c r="R79" t="n">
-        <v>6358436</v>
+        <v>6358398</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8895,32 +8895,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129004194</v>
+        <v>129004215</v>
       </c>
       <c r="B80" t="n">
-        <v>86820</v>
+        <v>86845</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>712133</v>
+        <v>712139</v>
       </c>
       <c r="R80" t="n">
-        <v>6358398</v>
+        <v>6358436</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9005,7 +9005,7 @@
         <v>129004211</v>
       </c>
       <c r="B81" t="n">
-        <v>87017</v>
+        <v>87020</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>129004195</v>
       </c>
       <c r="B82" t="n">
-        <v>86972</v>
+        <v>86975</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>129004208</v>
       </c>
       <c r="B83" t="n">
-        <v>87017</v>
+        <v>87020</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>129004212</v>
       </c>
       <c r="B84" t="n">
-        <v>87017</v>
+        <v>87020</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>129004207</v>
       </c>
       <c r="B85" t="n">
-        <v>87017</v>
+        <v>87020</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>129004210</v>
       </c>
       <c r="B86" t="n">
-        <v>87017</v>
+        <v>87020</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>129004192</v>
       </c>
       <c r="B87" t="n">
-        <v>110835</v>
+        <v>110839</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>129004202</v>
       </c>
       <c r="B88" t="n">
-        <v>90956</v>
+        <v>90959</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>129004200</v>
       </c>
       <c r="B89" t="n">
-        <v>86995</v>
+        <v>86998</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9974,10 +9974,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129004204</v>
+        <v>129004206</v>
       </c>
       <c r="B90" t="n">
-        <v>86911</v>
+        <v>87020</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9985,21 +9985,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10009,10 +10009,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>712180</v>
+        <v>712178</v>
       </c>
       <c r="R90" t="n">
-        <v>6358430</v>
+        <v>6358418</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10081,10 +10081,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129004206</v>
+        <v>129004204</v>
       </c>
       <c r="B91" t="n">
-        <v>87017</v>
+        <v>86914</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10092,21 +10092,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10116,10 +10116,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>712178</v>
+        <v>712180</v>
       </c>
       <c r="R91" t="n">
-        <v>6358418</v>
+        <v>6358430</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10188,32 +10188,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129004209</v>
+        <v>129004193</v>
       </c>
       <c r="B92" t="n">
-        <v>87017</v>
+        <v>90341</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>449</v>
+        <v>2072</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>712185</v>
+        <v>712067</v>
       </c>
       <c r="R92" t="n">
-        <v>6358414</v>
+        <v>6358371</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10277,6 +10277,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10295,32 +10296,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129004193</v>
+        <v>129004209</v>
       </c>
       <c r="B93" t="n">
-        <v>90338</v>
+        <v>87020</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2072</v>
+        <v>449</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10330,10 +10331,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>712067</v>
+        <v>712185</v>
       </c>
       <c r="R93" t="n">
-        <v>6358371</v>
+        <v>6358414</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10365,7 +10366,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10375,7 +10376,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10384,7 +10385,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10403,32 +10403,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129004191</v>
+        <v>129004188</v>
       </c>
       <c r="B94" t="n">
-        <v>87018</v>
+        <v>87043</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>248947</v>
+        <v>3767</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10438,10 +10438,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>712118</v>
+        <v>712181</v>
       </c>
       <c r="R94" t="n">
-        <v>6358397</v>
+        <v>6358403</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10510,32 +10510,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129004188</v>
+        <v>129004191</v>
       </c>
       <c r="B95" t="n">
-        <v>87040</v>
+        <v>87021</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>3767</v>
+        <v>248947</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10545,10 +10545,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>712181</v>
+        <v>712118</v>
       </c>
       <c r="R95" t="n">
-        <v>6358403</v>
+        <v>6358397</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10617,32 +10617,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129004205</v>
+        <v>129004214</v>
       </c>
       <c r="B96" t="n">
-        <v>87017</v>
+        <v>86961</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10652,10 +10652,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>712139</v>
+        <v>712132</v>
       </c>
       <c r="R96" t="n">
-        <v>6358437</v>
+        <v>6358416</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10724,10 +10724,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129004201</v>
+        <v>129004187</v>
       </c>
       <c r="B97" t="n">
-        <v>86887</v>
+        <v>87043</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10735,16 +10735,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>445</v>
+        <v>3767</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10759,10 +10759,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>712185</v>
+        <v>712224</v>
       </c>
       <c r="R97" t="n">
-        <v>6358418</v>
+        <v>6358420</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10831,32 +10831,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129004214</v>
+        <v>129004205</v>
       </c>
       <c r="B98" t="n">
-        <v>86958</v>
+        <v>87020</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10866,10 +10866,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>712132</v>
+        <v>712139</v>
       </c>
       <c r="R98" t="n">
-        <v>6358416</v>
+        <v>6358437</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10938,10 +10938,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129004187</v>
+        <v>129004201</v>
       </c>
       <c r="B99" t="n">
-        <v>87040</v>
+        <v>86890</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10949,16 +10949,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3767</v>
+        <v>445</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10973,10 +10973,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>712224</v>
+        <v>712185</v>
       </c>
       <c r="R99" t="n">
-        <v>6358420</v>
+        <v>6358418</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD99" t="b">

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -5899,10 +5899,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128947675</v>
+        <v>128947664</v>
       </c>
       <c r="B50" t="n">
-        <v>86961</v>
+        <v>91975</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5910,21 +5910,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3674</v>
+        <v>5420</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>712229</v>
+        <v>712272</v>
       </c>
       <c r="R50" t="n">
-        <v>6358510</v>
+        <v>6358461</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5996,10 +5996,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128947674</v>
+        <v>128947675</v>
       </c>
       <c r="B51" t="n">
-        <v>86823</v>
+        <v>86961</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6007,21 +6007,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712125</v>
+        <v>712229</v>
       </c>
       <c r="R51" t="n">
-        <v>6358399</v>
+        <v>6358510</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6093,10 +6093,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128947664</v>
+        <v>128947674</v>
       </c>
       <c r="B52" t="n">
-        <v>91975</v>
+        <v>86823</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6104,21 +6104,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5420</v>
+        <v>3712</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6128,10 +6128,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712272</v>
+        <v>712125</v>
       </c>
       <c r="R52" t="n">
-        <v>6358461</v>
+        <v>6358399</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -7271,10 +7271,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128947666</v>
+        <v>128947663</v>
       </c>
       <c r="B64" t="n">
-        <v>87020</v>
+        <v>86914</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7282,21 +7282,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712159</v>
+        <v>712176</v>
       </c>
       <c r="R64" t="n">
-        <v>6358410</v>
+        <v>6358409</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7350,6 +7350,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7368,10 +7369,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128947663</v>
+        <v>128947666</v>
       </c>
       <c r="B65" t="n">
-        <v>86914</v>
+        <v>87020</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7379,21 +7380,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7403,10 +7404,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>712176</v>
+        <v>712159</v>
       </c>
       <c r="R65" t="n">
-        <v>6358409</v>
+        <v>6358410</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7447,7 +7448,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -5512,7 +5512,7 @@
         <v>128947652</v>
       </c>
       <c r="B46" t="n">
-        <v>86845</v>
+        <v>86847</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>128947671</v>
       </c>
       <c r="B47" t="n">
-        <v>86823</v>
+        <v>86825</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>128947656</v>
       </c>
       <c r="B48" t="n">
-        <v>86998</v>
+        <v>87000</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>128947660</v>
       </c>
       <c r="B49" t="n">
-        <v>86998</v>
+        <v>87000</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5899,10 +5899,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128947664</v>
+        <v>128947674</v>
       </c>
       <c r="B50" t="n">
-        <v>91975</v>
+        <v>86825</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5910,21 +5910,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5420</v>
+        <v>3712</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>712272</v>
+        <v>712125</v>
       </c>
       <c r="R50" t="n">
-        <v>6358461</v>
+        <v>6358399</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5999,7 +5999,7 @@
         <v>128947675</v>
       </c>
       <c r="B51" t="n">
-        <v>86961</v>
+        <v>86963</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6093,10 +6093,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128947674</v>
+        <v>128947664</v>
       </c>
       <c r="B52" t="n">
-        <v>86823</v>
+        <v>91977</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6104,21 +6104,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3712</v>
+        <v>5420</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6128,10 +6128,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712125</v>
+        <v>712272</v>
       </c>
       <c r="R52" t="n">
-        <v>6358399</v>
+        <v>6358461</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6193,7 +6193,7 @@
         <v>128947659</v>
       </c>
       <c r="B53" t="n">
-        <v>86998</v>
+        <v>87000</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>128947677</v>
       </c>
       <c r="B54" t="n">
-        <v>86961</v>
+        <v>86963</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>128947676</v>
       </c>
       <c r="B55" t="n">
-        <v>86961</v>
+        <v>86963</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6482,10 +6482,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128947667</v>
+        <v>128947669</v>
       </c>
       <c r="B56" t="n">
-        <v>92861</v>
+        <v>86825</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6493,37 +6493,34 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>5964</v>
+        <v>3712</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
-      <c r="J56" t="inlineStr"/>
-      <c r="K56" t="inlineStr"/>
-      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>712163</v>
+        <v>712363</v>
       </c>
       <c r="R56" t="n">
-        <v>6358380</v>
+        <v>6358457</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6564,7 +6561,6 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
-      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6583,10 +6579,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128947669</v>
+        <v>128947667</v>
       </c>
       <c r="B57" t="n">
-        <v>86823</v>
+        <v>92863</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6594,34 +6590,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>3712</v>
+        <v>5964</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
+      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712363</v>
+        <v>712163</v>
       </c>
       <c r="R57" t="n">
-        <v>6358457</v>
+        <v>6358380</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6662,6 +6661,7 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
+      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6683,7 +6683,7 @@
         <v>128947647</v>
       </c>
       <c r="B58" t="n">
-        <v>87021</v>
+        <v>87023</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6780,7 +6780,7 @@
         <v>128947655</v>
       </c>
       <c r="B59" t="n">
-        <v>86799</v>
+        <v>86801</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6982,7 +6982,7 @@
         <v>128947648</v>
       </c>
       <c r="B61" t="n">
-        <v>87021</v>
+        <v>87023</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>128947649</v>
       </c>
       <c r="B62" t="n">
-        <v>87021</v>
+        <v>87023</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>128947643</v>
       </c>
       <c r="B63" t="n">
-        <v>86941</v>
+        <v>86943</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7271,10 +7271,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128947663</v>
+        <v>128947666</v>
       </c>
       <c r="B64" t="n">
-        <v>86914</v>
+        <v>87022</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7282,21 +7282,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712176</v>
+        <v>712159</v>
       </c>
       <c r="R64" t="n">
-        <v>6358409</v>
+        <v>6358410</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7350,7 +7350,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7369,10 +7368,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128947666</v>
+        <v>128947663</v>
       </c>
       <c r="B65" t="n">
-        <v>87020</v>
+        <v>86916</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7380,21 +7379,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7404,10 +7403,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>712159</v>
+        <v>712176</v>
       </c>
       <c r="R65" t="n">
-        <v>6358410</v>
+        <v>6358409</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7448,6 +7447,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7469,7 +7469,7 @@
         <v>128947657</v>
       </c>
       <c r="B66" t="n">
-        <v>86998</v>
+        <v>87000</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7672,7 +7672,7 @@
         <v>128947673</v>
       </c>
       <c r="B68" t="n">
-        <v>86823</v>
+        <v>86825</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7766,32 +7766,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128947645</v>
+        <v>128947670</v>
       </c>
       <c r="B69" t="n">
-        <v>87043</v>
+        <v>86825</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7801,10 +7801,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>712060</v>
+        <v>712289</v>
       </c>
       <c r="R69" t="n">
-        <v>6358285</v>
+        <v>6358623</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7863,32 +7863,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128947670</v>
+        <v>128947645</v>
       </c>
       <c r="B70" t="n">
-        <v>86823</v>
+        <v>87045</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7898,10 +7898,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>712289</v>
+        <v>712060</v>
       </c>
       <c r="R70" t="n">
-        <v>6358623</v>
+        <v>6358285</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7963,7 +7963,7 @@
         <v>128947644</v>
       </c>
       <c r="B71" t="n">
-        <v>86941</v>
+        <v>86943</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>128947672</v>
       </c>
       <c r="B72" t="n">
-        <v>86823</v>
+        <v>86825</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>128947646</v>
       </c>
       <c r="B73" t="n">
-        <v>86985</v>
+        <v>86987</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8255,7 +8255,7 @@
         <v>129004213</v>
       </c>
       <c r="B74" t="n">
-        <v>86845</v>
+        <v>86847</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8362,7 +8362,7 @@
         <v>129004190</v>
       </c>
       <c r="B75" t="n">
-        <v>87021</v>
+        <v>87023</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8469,7 +8469,7 @@
         <v>129004186</v>
       </c>
       <c r="B76" t="n">
-        <v>86941</v>
+        <v>86943</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>129004199</v>
       </c>
       <c r="B77" t="n">
-        <v>86998</v>
+        <v>87000</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>129004203</v>
       </c>
       <c r="B78" t="n">
-        <v>86914</v>
+        <v>86916</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>129004194</v>
       </c>
       <c r="B79" t="n">
-        <v>86823</v>
+        <v>86825</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>129004215</v>
       </c>
       <c r="B80" t="n">
-        <v>86845</v>
+        <v>86847</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>129004211</v>
       </c>
       <c r="B81" t="n">
-        <v>87020</v>
+        <v>87022</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>129004195</v>
       </c>
       <c r="B82" t="n">
-        <v>86975</v>
+        <v>86977</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>129004208</v>
       </c>
       <c r="B83" t="n">
-        <v>87020</v>
+        <v>87022</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>129004212</v>
       </c>
       <c r="B84" t="n">
-        <v>87020</v>
+        <v>87022</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>129004207</v>
       </c>
       <c r="B85" t="n">
-        <v>87020</v>
+        <v>87022</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>129004210</v>
       </c>
       <c r="B86" t="n">
-        <v>87020</v>
+        <v>87022</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>129004192</v>
       </c>
       <c r="B87" t="n">
-        <v>110839</v>
+        <v>110841</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>129004202</v>
       </c>
       <c r="B88" t="n">
-        <v>90959</v>
+        <v>90961</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>129004200</v>
       </c>
       <c r="B89" t="n">
-        <v>86998</v>
+        <v>87000</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>129004206</v>
       </c>
       <c r="B90" t="n">
-        <v>87020</v>
+        <v>87022</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>129004204</v>
       </c>
       <c r="B91" t="n">
-        <v>86914</v>
+        <v>86916</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10191,7 +10191,7 @@
         <v>129004193</v>
       </c>
       <c r="B92" t="n">
-        <v>90341</v>
+        <v>90343</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -10299,7 +10299,7 @@
         <v>129004209</v>
       </c>
       <c r="B93" t="n">
-        <v>87020</v>
+        <v>87022</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -10406,7 +10406,7 @@
         <v>129004188</v>
       </c>
       <c r="B94" t="n">
-        <v>87043</v>
+        <v>87045</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>129004191</v>
       </c>
       <c r="B95" t="n">
-        <v>87021</v>
+        <v>87023</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10617,32 +10617,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129004214</v>
+        <v>129004205</v>
       </c>
       <c r="B96" t="n">
-        <v>86961</v>
+        <v>87022</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10652,10 +10652,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>712132</v>
+        <v>712139</v>
       </c>
       <c r="R96" t="n">
-        <v>6358416</v>
+        <v>6358437</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10727,7 +10727,7 @@
         <v>129004187</v>
       </c>
       <c r="B97" t="n">
-        <v>87043</v>
+        <v>87045</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10831,32 +10831,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129004205</v>
+        <v>129004214</v>
       </c>
       <c r="B98" t="n">
-        <v>87020</v>
+        <v>86963</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10866,10 +10866,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>712139</v>
+        <v>712132</v>
       </c>
       <c r="R98" t="n">
-        <v>6358437</v>
+        <v>6358416</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10941,7 +10941,7 @@
         <v>129004201</v>
       </c>
       <c r="B99" t="n">
-        <v>86890</v>
+        <v>86892</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -5512,7 +5512,7 @@
         <v>128947652</v>
       </c>
       <c r="B46" t="n">
-        <v>86847</v>
+        <v>86851</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>128947671</v>
       </c>
       <c r="B47" t="n">
-        <v>86825</v>
+        <v>86829</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>128947656</v>
       </c>
       <c r="B48" t="n">
-        <v>87000</v>
+        <v>87004</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>128947660</v>
       </c>
       <c r="B49" t="n">
-        <v>87000</v>
+        <v>87004</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5899,10 +5899,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>128947674</v>
+        <v>128947664</v>
       </c>
       <c r="B50" t="n">
-        <v>86825</v>
+        <v>91981</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5910,21 +5910,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>3712</v>
+        <v>5420</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5934,10 +5934,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>712125</v>
+        <v>712272</v>
       </c>
       <c r="R50" t="n">
-        <v>6358399</v>
+        <v>6358461</v>
       </c>
       <c r="S50" t="n">
         <v>10</v>
@@ -5996,10 +5996,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128947675</v>
+        <v>128947674</v>
       </c>
       <c r="B51" t="n">
-        <v>86963</v>
+        <v>86829</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6007,21 +6007,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712229</v>
+        <v>712125</v>
       </c>
       <c r="R51" t="n">
-        <v>6358510</v>
+        <v>6358399</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6093,10 +6093,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128947664</v>
+        <v>128947675</v>
       </c>
       <c r="B52" t="n">
-        <v>91977</v>
+        <v>86967</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6104,21 +6104,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>5420</v>
+        <v>3674</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6128,10 +6128,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712272</v>
+        <v>712229</v>
       </c>
       <c r="R52" t="n">
-        <v>6358461</v>
+        <v>6358510</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6193,7 +6193,7 @@
         <v>128947659</v>
       </c>
       <c r="B53" t="n">
-        <v>87000</v>
+        <v>87004</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>128947677</v>
       </c>
       <c r="B54" t="n">
-        <v>86963</v>
+        <v>86967</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>128947676</v>
       </c>
       <c r="B55" t="n">
-        <v>86963</v>
+        <v>86967</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6482,10 +6482,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>128947669</v>
+        <v>128947667</v>
       </c>
       <c r="B56" t="n">
-        <v>86825</v>
+        <v>92867</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6493,34 +6493,37 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>3712</v>
+        <v>5964</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Fjällig taggsvamp s.str.</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Sarcodon imbricatus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(L.) P.Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
+      <c r="J56" t="inlineStr"/>
+      <c r="K56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>712363</v>
+        <v>712163</v>
       </c>
       <c r="R56" t="n">
-        <v>6358457</v>
+        <v>6358380</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6561,6 +6564,7 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
@@ -6579,10 +6583,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>128947667</v>
+        <v>128947669</v>
       </c>
       <c r="B57" t="n">
-        <v>92863</v>
+        <v>86829</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6590,37 +6594,34 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5964</v>
+        <v>3712</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Fjällig taggsvamp s.str.</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Sarcodon imbricatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) P.Karst.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
-      <c r="J57" t="inlineStr"/>
-      <c r="K57" t="inlineStr"/>
-      <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712163</v>
+        <v>712363</v>
       </c>
       <c r="R57" t="n">
-        <v>6358380</v>
+        <v>6358457</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6661,7 +6662,6 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
@@ -6683,7 +6683,7 @@
         <v>128947647</v>
       </c>
       <c r="B58" t="n">
-        <v>87023</v>
+        <v>87027</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6777,45 +6777,53 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128947655</v>
+        <v>128947654</v>
       </c>
       <c r="B59" t="n">
-        <v>86801</v>
+        <v>57724</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>3762</v>
+        <v>100049</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="K59" t="inlineStr"/>
+      <c r="L59" t="inlineStr"/>
+      <c r="M59" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712080</v>
+        <v>712106</v>
       </c>
       <c r="R59" t="n">
-        <v>6358365</v>
+        <v>6358348</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6874,53 +6882,45 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128947654</v>
+        <v>128947655</v>
       </c>
       <c r="B60" t="n">
-        <v>57724</v>
+        <v>86805</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100049</v>
+        <v>3762</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712106</v>
+        <v>712080</v>
       </c>
       <c r="R60" t="n">
-        <v>6358348</v>
+        <v>6358365</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6982,7 +6982,7 @@
         <v>128947648</v>
       </c>
       <c r="B61" t="n">
-        <v>87023</v>
+        <v>87027</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -7079,7 +7079,7 @@
         <v>128947649</v>
       </c>
       <c r="B62" t="n">
-        <v>87023</v>
+        <v>87027</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -7176,7 +7176,7 @@
         <v>128947643</v>
       </c>
       <c r="B63" t="n">
-        <v>86943</v>
+        <v>86947</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7271,10 +7271,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128947666</v>
+        <v>128947663</v>
       </c>
       <c r="B64" t="n">
-        <v>87022</v>
+        <v>86920</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7282,21 +7282,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712159</v>
+        <v>712176</v>
       </c>
       <c r="R64" t="n">
-        <v>6358410</v>
+        <v>6358409</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7350,6 +7350,7 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
+      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7368,10 +7369,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128947663</v>
+        <v>128947666</v>
       </c>
       <c r="B65" t="n">
-        <v>86916</v>
+        <v>87026</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7379,21 +7380,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7403,10 +7404,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>712176</v>
+        <v>712159</v>
       </c>
       <c r="R65" t="n">
-        <v>6358409</v>
+        <v>6358410</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7447,7 +7448,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7469,7 +7469,7 @@
         <v>128947657</v>
       </c>
       <c r="B66" t="n">
-        <v>87000</v>
+        <v>87004</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7564,53 +7564,45 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>128947653</v>
+        <v>128947673</v>
       </c>
       <c r="B67" t="n">
-        <v>57724</v>
+        <v>86829</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100049</v>
+        <v>3712</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
-      <c r="K67" t="inlineStr"/>
-      <c r="L67" t="inlineStr"/>
-      <c r="M67" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>712303</v>
+        <v>712157</v>
       </c>
       <c r="R67" t="n">
-        <v>6358650</v>
+        <v>6358456</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7669,45 +7661,53 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>128947673</v>
+        <v>128947653</v>
       </c>
       <c r="B68" t="n">
-        <v>86825</v>
+        <v>57724</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>3712</v>
+        <v>100049</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
+      <c r="K68" t="inlineStr"/>
+      <c r="L68" t="inlineStr"/>
+      <c r="M68" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>712157</v>
+        <v>712303</v>
       </c>
       <c r="R68" t="n">
-        <v>6358456</v>
+        <v>6358650</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7769,7 +7769,7 @@
         <v>128947670</v>
       </c>
       <c r="B69" t="n">
-        <v>86825</v>
+        <v>86829</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -7866,7 +7866,7 @@
         <v>128947645</v>
       </c>
       <c r="B70" t="n">
-        <v>87045</v>
+        <v>87049</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7963,7 +7963,7 @@
         <v>128947644</v>
       </c>
       <c r="B71" t="n">
-        <v>86943</v>
+        <v>86947</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>128947672</v>
       </c>
       <c r="B72" t="n">
-        <v>86825</v>
+        <v>86829</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>128947646</v>
       </c>
       <c r="B73" t="n">
-        <v>86987</v>
+        <v>86991</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8252,32 +8252,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129004213</v>
+        <v>129004190</v>
       </c>
       <c r="B74" t="n">
-        <v>86847</v>
+        <v>87027</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>424</v>
+        <v>248947</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>712140</v>
+        <v>712178</v>
       </c>
       <c r="R74" t="n">
-        <v>6358430</v>
+        <v>6358421</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8359,32 +8359,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129004190</v>
+        <v>129004213</v>
       </c>
       <c r="B75" t="n">
-        <v>87023</v>
+        <v>86851</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>248947</v>
+        <v>424</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8394,10 +8394,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>712178</v>
+        <v>712140</v>
       </c>
       <c r="R75" t="n">
-        <v>6358421</v>
+        <v>6358430</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8469,7 +8469,7 @@
         <v>129004186</v>
       </c>
       <c r="B76" t="n">
-        <v>86943</v>
+        <v>86947</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>129004199</v>
       </c>
       <c r="B77" t="n">
-        <v>87000</v>
+        <v>87004</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>129004203</v>
       </c>
       <c r="B78" t="n">
-        <v>86916</v>
+        <v>86920</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8788,32 +8788,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129004194</v>
+        <v>129004215</v>
       </c>
       <c r="B79" t="n">
-        <v>86825</v>
+        <v>86851</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>712133</v>
+        <v>712139</v>
       </c>
       <c r="R79" t="n">
-        <v>6358398</v>
+        <v>6358436</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8895,32 +8895,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129004215</v>
+        <v>129004194</v>
       </c>
       <c r="B80" t="n">
-        <v>86847</v>
+        <v>86829</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>712139</v>
+        <v>712133</v>
       </c>
       <c r="R80" t="n">
-        <v>6358436</v>
+        <v>6358398</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9005,7 +9005,7 @@
         <v>129004211</v>
       </c>
       <c r="B81" t="n">
-        <v>87022</v>
+        <v>87026</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>129004195</v>
       </c>
       <c r="B82" t="n">
-        <v>86977</v>
+        <v>86981</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>129004208</v>
       </c>
       <c r="B83" t="n">
-        <v>87022</v>
+        <v>87026</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>129004212</v>
       </c>
       <c r="B84" t="n">
-        <v>87022</v>
+        <v>87026</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>129004207</v>
       </c>
       <c r="B85" t="n">
-        <v>87022</v>
+        <v>87026</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9549,32 +9549,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129004210</v>
+        <v>129004192</v>
       </c>
       <c r="B86" t="n">
-        <v>87022</v>
+        <v>110845</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>449</v>
+        <v>219711</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9584,10 +9584,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>712140</v>
+        <v>712118</v>
       </c>
       <c r="R86" t="n">
-        <v>6358434</v>
+        <v>6358398</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9656,32 +9656,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129004192</v>
+        <v>129004210</v>
       </c>
       <c r="B87" t="n">
-        <v>110841</v>
+        <v>87026</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>219711</v>
+        <v>449</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9691,10 +9691,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>712118</v>
+        <v>712140</v>
       </c>
       <c r="R87" t="n">
-        <v>6358398</v>
+        <v>6358434</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9766,7 +9766,7 @@
         <v>129004202</v>
       </c>
       <c r="B88" t="n">
-        <v>90961</v>
+        <v>90965</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>129004200</v>
       </c>
       <c r="B89" t="n">
-        <v>87000</v>
+        <v>87004</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>129004206</v>
       </c>
       <c r="B90" t="n">
-        <v>87022</v>
+        <v>87026</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>129004204</v>
       </c>
       <c r="B91" t="n">
-        <v>86916</v>
+        <v>86920</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10188,32 +10188,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129004193</v>
+        <v>129004209</v>
       </c>
       <c r="B92" t="n">
-        <v>90343</v>
+        <v>87026</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2072</v>
+        <v>449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>712067</v>
+        <v>712185</v>
       </c>
       <c r="R92" t="n">
-        <v>6358371</v>
+        <v>6358414</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10277,7 +10277,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10296,32 +10295,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129004209</v>
+        <v>129004193</v>
       </c>
       <c r="B93" t="n">
-        <v>87022</v>
+        <v>90347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>449</v>
+        <v>2072</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10331,10 +10330,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>712185</v>
+        <v>712067</v>
       </c>
       <c r="R93" t="n">
-        <v>6358414</v>
+        <v>6358371</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10366,7 +10365,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10376,7 +10375,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10385,6 +10384,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10406,7 +10406,7 @@
         <v>129004188</v>
       </c>
       <c r="B94" t="n">
-        <v>87045</v>
+        <v>87049</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10513,7 +10513,7 @@
         <v>129004191</v>
       </c>
       <c r="B95" t="n">
-        <v>87023</v>
+        <v>87027</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -10620,7 +10620,7 @@
         <v>129004205</v>
       </c>
       <c r="B96" t="n">
-        <v>87022</v>
+        <v>87026</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10724,10 +10724,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129004187</v>
+        <v>129004201</v>
       </c>
       <c r="B97" t="n">
-        <v>87045</v>
+        <v>86896</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10735,16 +10735,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>3767</v>
+        <v>445</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10759,10 +10759,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>712224</v>
+        <v>712185</v>
       </c>
       <c r="R97" t="n">
-        <v>6358420</v>
+        <v>6358418</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10834,7 +10834,7 @@
         <v>129004214</v>
       </c>
       <c r="B98" t="n">
-        <v>86963</v>
+        <v>86967</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10938,10 +10938,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129004201</v>
+        <v>129004187</v>
       </c>
       <c r="B99" t="n">
-        <v>86892</v>
+        <v>87049</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10949,16 +10949,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>445</v>
+        <v>3767</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10973,10 +10973,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>712185</v>
+        <v>712224</v>
       </c>
       <c r="R99" t="n">
-        <v>6358418</v>
+        <v>6358420</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD99" t="b">

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -5512,7 +5512,7 @@
         <v>128947652</v>
       </c>
       <c r="B46" t="n">
-        <v>86851</v>
+        <v>86852</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5609,7 +5609,7 @@
         <v>128947671</v>
       </c>
       <c r="B47" t="n">
-        <v>86829</v>
+        <v>86830</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5706,7 +5706,7 @@
         <v>128947656</v>
       </c>
       <c r="B48" t="n">
-        <v>87004</v>
+        <v>87005</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5804,7 +5804,7 @@
         <v>128947660</v>
       </c>
       <c r="B49" t="n">
-        <v>87004</v>
+        <v>87005</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5902,7 +5902,7 @@
         <v>128947664</v>
       </c>
       <c r="B50" t="n">
-        <v>91981</v>
+        <v>91982</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5996,10 +5996,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>128947674</v>
+        <v>128947675</v>
       </c>
       <c r="B51" t="n">
-        <v>86829</v>
+        <v>86968</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6007,21 +6007,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>3712</v>
+        <v>3674</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -6031,10 +6031,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712125</v>
+        <v>712229</v>
       </c>
       <c r="R51" t="n">
-        <v>6358399</v>
+        <v>6358510</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -6093,10 +6093,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>128947675</v>
+        <v>128947674</v>
       </c>
       <c r="B52" t="n">
-        <v>86967</v>
+        <v>86830</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6104,21 +6104,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>3674</v>
+        <v>3712</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6128,10 +6128,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712229</v>
+        <v>712125</v>
       </c>
       <c r="R52" t="n">
-        <v>6358510</v>
+        <v>6358399</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6193,7 +6193,7 @@
         <v>128947659</v>
       </c>
       <c r="B53" t="n">
-        <v>87004</v>
+        <v>87005</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -6291,7 +6291,7 @@
         <v>128947677</v>
       </c>
       <c r="B54" t="n">
-        <v>86967</v>
+        <v>86968</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -6388,7 +6388,7 @@
         <v>128947676</v>
       </c>
       <c r="B55" t="n">
-        <v>86967</v>
+        <v>86968</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6485,7 +6485,7 @@
         <v>128947667</v>
       </c>
       <c r="B56" t="n">
-        <v>92867</v>
+        <v>92868</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6586,7 +6586,7 @@
         <v>128947669</v>
       </c>
       <c r="B57" t="n">
-        <v>86829</v>
+        <v>86830</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6683,7 +6683,7 @@
         <v>128947647</v>
       </c>
       <c r="B58" t="n">
-        <v>87027</v>
+        <v>87028</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6777,53 +6777,45 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>128947654</v>
+        <v>128947648</v>
       </c>
       <c r="B59" t="n">
-        <v>57724</v>
+        <v>87028</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100049</v>
+        <v>248947</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
-      <c r="K59" t="inlineStr"/>
-      <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712106</v>
+        <v>712168</v>
       </c>
       <c r="R59" t="n">
-        <v>6358348</v>
+        <v>6358403</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6882,32 +6874,32 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>128947655</v>
+        <v>128947649</v>
       </c>
       <c r="B60" t="n">
-        <v>86805</v>
+        <v>87028</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>3762</v>
+        <v>248947</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Olivspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cortinarius venetus</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) Fr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6917,10 +6909,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712080</v>
+        <v>712051</v>
       </c>
       <c r="R60" t="n">
-        <v>6358365</v>
+        <v>6358299</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6979,45 +6971,53 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>128947648</v>
+        <v>128947654</v>
       </c>
       <c r="B61" t="n">
-        <v>87027</v>
+        <v>57724</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>248947</v>
+        <v>100049</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712168</v>
+        <v>712106</v>
       </c>
       <c r="R61" t="n">
-        <v>6358403</v>
+        <v>6358348</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7076,32 +7076,32 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>128947649</v>
+        <v>128947655</v>
       </c>
       <c r="B62" t="n">
-        <v>87027</v>
+        <v>86806</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>248947</v>
+        <v>3762</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Olivspindling</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius venetus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Fr.:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7111,10 +7111,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712051</v>
+        <v>712080</v>
       </c>
       <c r="R62" t="n">
-        <v>6358299</v>
+        <v>6358365</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7176,7 +7176,7 @@
         <v>128947643</v>
       </c>
       <c r="B63" t="n">
-        <v>86947</v>
+        <v>86948</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -7271,10 +7271,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>128947663</v>
+        <v>128947666</v>
       </c>
       <c r="B64" t="n">
-        <v>86920</v>
+        <v>87027</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -7282,21 +7282,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7306,10 +7306,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712176</v>
+        <v>712159</v>
       </c>
       <c r="R64" t="n">
-        <v>6358409</v>
+        <v>6358410</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7350,7 +7350,6 @@
       <c r="AE64" t="b">
         <v>0</v>
       </c>
-      <c r="AF64" t="inlineStr"/>
       <c r="AG64" t="b">
         <v>0</v>
       </c>
@@ -7369,10 +7368,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>128947666</v>
+        <v>128947663</v>
       </c>
       <c r="B65" t="n">
-        <v>87026</v>
+        <v>86921</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -7380,21 +7379,21 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7404,10 +7403,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>712159</v>
+        <v>712176</v>
       </c>
       <c r="R65" t="n">
-        <v>6358410</v>
+        <v>6358409</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7448,6 +7447,7 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
+      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -7469,7 +7469,7 @@
         <v>128947657</v>
       </c>
       <c r="B66" t="n">
-        <v>87004</v>
+        <v>87005</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -7567,7 +7567,7 @@
         <v>128947673</v>
       </c>
       <c r="B67" t="n">
-        <v>86829</v>
+        <v>86830</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -7766,32 +7766,32 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>128947670</v>
+        <v>128947645</v>
       </c>
       <c r="B69" t="n">
-        <v>86829</v>
+        <v>87050</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>3712</v>
+        <v>3767</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7801,10 +7801,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>712289</v>
+        <v>712060</v>
       </c>
       <c r="R69" t="n">
-        <v>6358623</v>
+        <v>6358285</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7863,32 +7863,32 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128947645</v>
+        <v>128947670</v>
       </c>
       <c r="B70" t="n">
-        <v>87049</v>
+        <v>86830</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>3767</v>
+        <v>3712</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7898,10 +7898,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>712060</v>
+        <v>712289</v>
       </c>
       <c r="R70" t="n">
-        <v>6358285</v>
+        <v>6358623</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7963,7 +7963,7 @@
         <v>128947644</v>
       </c>
       <c r="B71" t="n">
-        <v>86947</v>
+        <v>86948</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -8060,7 +8060,7 @@
         <v>128947672</v>
       </c>
       <c r="B72" t="n">
-        <v>86829</v>
+        <v>86830</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8157,7 +8157,7 @@
         <v>128947646</v>
       </c>
       <c r="B73" t="n">
-        <v>86991</v>
+        <v>86992</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8252,32 +8252,32 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129004190</v>
+        <v>129004213</v>
       </c>
       <c r="B74" t="n">
-        <v>87027</v>
+        <v>86852</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E74" t="n">
-        <v>248947</v>
+        <v>424</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8287,10 +8287,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>712178</v>
+        <v>712140</v>
       </c>
       <c r="R74" t="n">
-        <v>6358421</v>
+        <v>6358430</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8322,7 +8322,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -8332,7 +8332,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>13:08</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8359,32 +8359,32 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129004213</v>
+        <v>129004190</v>
       </c>
       <c r="B75" t="n">
-        <v>86851</v>
+        <v>87028</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>424</v>
+        <v>248947</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8394,10 +8394,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>712140</v>
+        <v>712178</v>
       </c>
       <c r="R75" t="n">
-        <v>6358430</v>
+        <v>6358421</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8429,7 +8429,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8439,7 +8439,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8469,7 +8469,7 @@
         <v>129004186</v>
       </c>
       <c r="B76" t="n">
-        <v>86947</v>
+        <v>86948</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -8576,7 +8576,7 @@
         <v>129004199</v>
       </c>
       <c r="B77" t="n">
-        <v>87004</v>
+        <v>87005</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -8684,7 +8684,7 @@
         <v>129004203</v>
       </c>
       <c r="B78" t="n">
-        <v>86920</v>
+        <v>86921</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -8791,7 +8791,7 @@
         <v>129004215</v>
       </c>
       <c r="B79" t="n">
-        <v>86851</v>
+        <v>86852</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -8898,7 +8898,7 @@
         <v>129004194</v>
       </c>
       <c r="B80" t="n">
-        <v>86829</v>
+        <v>86830</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -9005,7 +9005,7 @@
         <v>129004211</v>
       </c>
       <c r="B81" t="n">
-        <v>87026</v>
+        <v>87027</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9117,7 +9117,7 @@
         <v>129004195</v>
       </c>
       <c r="B82" t="n">
-        <v>86981</v>
+        <v>86982</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -9225,7 +9225,7 @@
         <v>129004208</v>
       </c>
       <c r="B83" t="n">
-        <v>87026</v>
+        <v>87027</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -9332,7 +9332,7 @@
         <v>129004212</v>
       </c>
       <c r="B84" t="n">
-        <v>87026</v>
+        <v>87027</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9445,7 +9445,7 @@
         <v>129004207</v>
       </c>
       <c r="B85" t="n">
-        <v>87026</v>
+        <v>87027</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9552,7 +9552,7 @@
         <v>129004192</v>
       </c>
       <c r="B86" t="n">
-        <v>110845</v>
+        <v>110855</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9659,7 +9659,7 @@
         <v>129004210</v>
       </c>
       <c r="B87" t="n">
-        <v>87026</v>
+        <v>87027</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>129004202</v>
       </c>
       <c r="B88" t="n">
-        <v>90965</v>
+        <v>90966</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9869,7 +9869,7 @@
         <v>129004200</v>
       </c>
       <c r="B89" t="n">
-        <v>87004</v>
+        <v>87005</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -9977,7 +9977,7 @@
         <v>129004206</v>
       </c>
       <c r="B90" t="n">
-        <v>87026</v>
+        <v>87027</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -10084,7 +10084,7 @@
         <v>129004204</v>
       </c>
       <c r="B91" t="n">
-        <v>86920</v>
+        <v>86921</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10188,32 +10188,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129004209</v>
+        <v>129004193</v>
       </c>
       <c r="B92" t="n">
-        <v>87026</v>
+        <v>90348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>449</v>
+        <v>2072</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>712185</v>
+        <v>712067</v>
       </c>
       <c r="R92" t="n">
-        <v>6358414</v>
+        <v>6358371</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10277,6 +10277,7 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
+      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10295,32 +10296,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129004193</v>
+        <v>129004209</v>
       </c>
       <c r="B93" t="n">
-        <v>90347</v>
+        <v>87027</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>2072</v>
+        <v>449</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10330,10 +10331,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>712067</v>
+        <v>712185</v>
       </c>
       <c r="R93" t="n">
-        <v>6358371</v>
+        <v>6358414</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10365,7 +10366,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10375,7 +10376,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10384,7 +10385,6 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
-      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
@@ -10403,32 +10403,32 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129004188</v>
+        <v>129004191</v>
       </c>
       <c r="B94" t="n">
-        <v>87049</v>
+        <v>87028</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>DD</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>3767</v>
+        <v>248947</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Brandrud</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10438,10 +10438,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>712181</v>
+        <v>712118</v>
       </c>
       <c r="R94" t="n">
-        <v>6358403</v>
+        <v>6358397</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10473,7 +10473,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10483,7 +10483,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>13:31</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10510,32 +10510,32 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129004191</v>
+        <v>129004188</v>
       </c>
       <c r="B95" t="n">
-        <v>87027</v>
+        <v>87050</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>DD</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>248947</v>
+        <v>3767</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>Brandrud</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10545,10 +10545,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>712118</v>
+        <v>712181</v>
       </c>
       <c r="R95" t="n">
-        <v>6358397</v>
+        <v>6358403</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10580,7 +10580,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10590,7 +10590,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>13:31</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10620,7 +10620,7 @@
         <v>129004205</v>
       </c>
       <c r="B96" t="n">
-        <v>87026</v>
+        <v>87027</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -10727,7 +10727,7 @@
         <v>129004201</v>
       </c>
       <c r="B97" t="n">
-        <v>86896</v>
+        <v>86897</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10834,7 +10834,7 @@
         <v>129004214</v>
       </c>
       <c r="B98" t="n">
-        <v>86967</v>
+        <v>86968</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -10941,7 +10941,7 @@
         <v>129004187</v>
       </c>
       <c r="B99" t="n">
-        <v>87049</v>
+        <v>87050</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -9549,32 +9549,32 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>129004192</v>
+        <v>129004210</v>
       </c>
       <c r="B86" t="n">
-        <v>110855</v>
+        <v>87027</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>219711</v>
+        <v>449</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9584,10 +9584,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>712118</v>
+        <v>712140</v>
       </c>
       <c r="R86" t="n">
-        <v>6358398</v>
+        <v>6358434</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9619,7 +9619,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -9629,7 +9629,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>12:07</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9656,32 +9656,32 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>129004210</v>
+        <v>129004192</v>
       </c>
       <c r="B87" t="n">
-        <v>87027</v>
+        <v>110855</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>449</v>
+        <v>219711</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9691,10 +9691,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>712140</v>
+        <v>712118</v>
       </c>
       <c r="R87" t="n">
-        <v>6358434</v>
+        <v>6358398</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9726,7 +9726,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9736,7 +9736,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>12:07</t>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9974,10 +9974,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129004206</v>
+        <v>129004204</v>
       </c>
       <c r="B90" t="n">
-        <v>87027</v>
+        <v>86921</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9985,21 +9985,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10009,10 +10009,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>712178</v>
+        <v>712180</v>
       </c>
       <c r="R90" t="n">
-        <v>6358418</v>
+        <v>6358430</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10081,10 +10081,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129004204</v>
+        <v>129004206</v>
       </c>
       <c r="B91" t="n">
-        <v>86921</v>
+        <v>87027</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10092,21 +10092,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10116,10 +10116,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>712180</v>
+        <v>712178</v>
       </c>
       <c r="R91" t="n">
-        <v>6358430</v>
+        <v>6358418</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10617,32 +10617,32 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129004205</v>
+        <v>129004214</v>
       </c>
       <c r="B96" t="n">
-        <v>87027</v>
+        <v>86968</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>449</v>
+        <v>3674</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Anisspindling</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius odorifer</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Britzelm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10652,10 +10652,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>712139</v>
+        <v>712132</v>
       </c>
       <c r="R96" t="n">
-        <v>6358437</v>
+        <v>6358416</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10687,7 +10687,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10697,7 +10697,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>11:33</t>
+          <t>11:29</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10724,10 +10724,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129004201</v>
+        <v>129004187</v>
       </c>
       <c r="B97" t="n">
-        <v>86897</v>
+        <v>87050</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -10735,16 +10735,16 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>445</v>
+        <v>3767</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Kopparspindling</t>
+          <t>Violettfläckig spindling</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius cupreorufus</t>
+          <t>Cortinarius violaceomaculatus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -10759,10 +10759,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>712185</v>
+        <v>712224</v>
       </c>
       <c r="R97" t="n">
-        <v>6358418</v>
+        <v>6358420</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10794,7 +10794,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10804,7 +10804,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>13:22</t>
+          <t>13:37</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10831,32 +10831,32 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>129004214</v>
+        <v>129004205</v>
       </c>
       <c r="B98" t="n">
-        <v>86968</v>
+        <v>87027</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>3674</v>
+        <v>449</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Anisspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius odorifer</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Britzelm.</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10866,10 +10866,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>712132</v>
+        <v>712139</v>
       </c>
       <c r="R98" t="n">
-        <v>6358416</v>
+        <v>6358437</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10901,7 +10901,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10911,7 +10911,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>11:29</t>
+          <t>11:33</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10938,10 +10938,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129004187</v>
+        <v>129004201</v>
       </c>
       <c r="B99" t="n">
-        <v>87050</v>
+        <v>86897</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -10949,16 +10949,16 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>3767</v>
+        <v>445</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Violettfläckig spindling</t>
+          <t>Kopparspindling</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius violaceomaculatus</t>
+          <t>Cortinarius cupreorufus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -10973,10 +10973,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>712224</v>
+        <v>712185</v>
       </c>
       <c r="R99" t="n">
-        <v>6358420</v>
+        <v>6358418</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11008,7 +11008,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11018,7 +11018,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>13:37</t>
+          <t>13:22</t>
         </is>
       </c>
       <c r="AD99" t="b">

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -9974,10 +9974,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129004204</v>
+        <v>129004206</v>
       </c>
       <c r="B90" t="n">
-        <v>86921</v>
+        <v>87027</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -9985,21 +9985,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>248956</v>
+        <v>449</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10009,10 +10009,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>712180</v>
+        <v>712178</v>
       </c>
       <c r="R90" t="n">
-        <v>6358430</v>
+        <v>6358418</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10044,7 +10044,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10081,10 +10081,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129004206</v>
+        <v>129004204</v>
       </c>
       <c r="B91" t="n">
-        <v>87027</v>
+        <v>86921</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -10092,21 +10092,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>449</v>
+        <v>248956</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10116,10 +10116,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>712178</v>
+        <v>712180</v>
       </c>
       <c r="R91" t="n">
-        <v>6358418</v>
+        <v>6358430</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10151,7 +10151,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10161,7 +10161,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>13:00</t>
+          <t>13:02</t>
         </is>
       </c>
       <c r="AD91" t="b">

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -8788,32 +8788,32 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129004215</v>
+        <v>129004194</v>
       </c>
       <c r="B79" t="n">
-        <v>86852</v>
+        <v>86830</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>424</v>
+        <v>3712</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Svartgrön spindling</t>
+          <t>Blå slemspindling</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Cortinarius atrovirens</t>
+          <t>Cortinarius salor</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>Kalchbr.</t>
+          <t>Fr.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8823,10 +8823,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>712139</v>
+        <v>712133</v>
       </c>
       <c r="R79" t="n">
-        <v>6358436</v>
+        <v>6358398</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8858,7 +8858,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -8868,7 +8868,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>12:22</t>
+          <t>11:24</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8895,32 +8895,32 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>129004194</v>
+        <v>129004215</v>
       </c>
       <c r="B80" t="n">
-        <v>86830</v>
+        <v>86852</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>3712</v>
+        <v>424</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blå slemspindling</t>
+          <t>Svartgrön spindling</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Cortinarius salor</t>
+          <t>Cortinarius atrovirens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>Fr.</t>
+          <t>Kalchbr.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8930,10 +8930,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>712133</v>
+        <v>712139</v>
       </c>
       <c r="R80" t="n">
-        <v>6358398</v>
+        <v>6358436</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8965,7 +8965,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -8975,7 +8975,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>11:24</t>
+          <t>12:22</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9659,7 +9659,7 @@
         <v>129004192</v>
       </c>
       <c r="B87" t="n">
-        <v>110855</v>
+        <v>110858</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9766,7 +9766,7 @@
         <v>129004202</v>
       </c>
       <c r="B88" t="n">
-        <v>90966</v>
+        <v>90969</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10188,32 +10188,32 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129004193</v>
+        <v>129004209</v>
       </c>
       <c r="B92" t="n">
-        <v>90348</v>
+        <v>87027</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>2072</v>
+        <v>449</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Sienamusseron</t>
+          <t>Granrotspindling</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Tricholoma joachimii</t>
+          <t>Cortinarius subfraudulosus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>Bon &amp; A.Riva</t>
+          <t>Kytöv. &amp; al.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10223,10 +10223,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>712067</v>
+        <v>712185</v>
       </c>
       <c r="R92" t="n">
-        <v>6358371</v>
+        <v>6358414</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10258,7 +10258,7 @@
       </c>
       <c r="Z92" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
@@ -10268,7 +10268,7 @@
       </c>
       <c r="AB92" t="inlineStr">
         <is>
-          <t>10:47</t>
+          <t>13:17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10277,7 +10277,6 @@
       <c r="AE92" t="b">
         <v>0</v>
       </c>
-      <c r="AF92" t="inlineStr"/>
       <c r="AG92" t="b">
         <v>0</v>
       </c>
@@ -10296,32 +10295,32 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129004209</v>
+        <v>129004193</v>
       </c>
       <c r="B93" t="n">
-        <v>87027</v>
+        <v>90351</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>449</v>
+        <v>2072</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Granrotspindling</t>
+          <t>Sienamusseron</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius subfraudulosus</t>
+          <t>Tricholoma joachimii</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; al.</t>
+          <t>Bon &amp; A.Riva</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10331,10 +10330,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>712185</v>
+        <v>712067</v>
       </c>
       <c r="R93" t="n">
-        <v>6358414</v>
+        <v>6358371</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10366,7 +10365,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10376,7 +10375,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>13:17</t>
+          <t>10:47</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10385,6 +10384,7 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -1277,10 +1277,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>126583702</v>
+        <v>126583718</v>
       </c>
       <c r="B7" t="n">
-        <v>109266</v>
+        <v>107318</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1288,37 +1288,46 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>712372</v>
+        <v>712205</v>
       </c>
       <c r="R7" t="n">
-        <v>6358494</v>
+        <v>6358507</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1350,11 +1359,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD7" t="b">
         <v>0</v>
       </c>
@@ -1366,7 +1370,7 @@
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
+          <t>Kalkbarrskog, lite äldre skog.</t>
         </is>
       </c>
       <c r="AT7" t="inlineStr"/>
@@ -1384,10 +1388,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>126583718</v>
+        <v>126583702</v>
       </c>
       <c r="B8" t="n">
-        <v>107324</v>
+        <v>109260</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1395,46 +1399,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>220079</v>
+        <v>220299</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>712205</v>
+        <v>712372</v>
       </c>
       <c r="R8" t="n">
-        <v>6358507</v>
+        <v>6358494</v>
       </c>
       <c r="S8" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1466,6 +1461,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC8" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD8" t="b">
         <v>0</v>
       </c>
@@ -1477,7 +1477,7 @@
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, lite äldre skog.</t>
+          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
         </is>
       </c>
       <c r="AT8" t="inlineStr"/>
@@ -1498,7 +1498,7 @@
         <v>126583676</v>
       </c>
       <c r="B9" t="n">
-        <v>98465</v>
+        <v>98459</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1609,7 +1609,7 @@
         <v>126583700</v>
       </c>
       <c r="B10" t="n">
-        <v>98420</v>
+        <v>98414</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>126583720</v>
       </c>
       <c r="B11" t="n">
-        <v>109266</v>
+        <v>109260</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1836,7 +1836,7 @@
         <v>126583687</v>
       </c>
       <c r="B12" t="n">
-        <v>98360</v>
+        <v>98354</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1944,45 +1944,54 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>126583688</v>
+        <v>126583708</v>
       </c>
       <c r="B13" t="n">
-        <v>106037</v>
+        <v>107318</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>220785</v>
+        <v>220079</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>712386</v>
+        <v>712342</v>
       </c>
       <c r="R13" t="n">
-        <v>6358485</v>
+        <v>6358478</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2028,7 +2037,7 @@
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>Sumpskog runt dike; träd på socklar.</t>
+          <t>Kalkbarrskog; fuktigare skog mot O-NO.</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr"/>
@@ -2046,54 +2055,45 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>126583701</v>
+        <v>126583688</v>
       </c>
       <c r="B14" t="n">
-        <v>98360</v>
+        <v>106031</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>712372</v>
+        <v>712386</v>
       </c>
       <c r="R14" t="n">
-        <v>6358494</v>
+        <v>6358485</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2128,11 +2128,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC14" t="inlineStr">
-        <is>
-          <t>Varav 10 mot NO.</t>
-        </is>
-      </c>
       <c r="AD14" t="b">
         <v>0</v>
       </c>
@@ -2144,7 +2139,7 @@
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
+          <t>Sumpskog runt dike; träd på socklar.</t>
         </is>
       </c>
       <c r="AT14" t="inlineStr"/>
@@ -2162,37 +2157,37 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>126583708</v>
+        <v>126583701</v>
       </c>
       <c r="B15" t="n">
-        <v>107324</v>
+        <v>98354</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>220079</v>
+        <v>223591</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>75</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -2206,10 +2201,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>712342</v>
+        <v>712372</v>
       </c>
       <c r="R15" t="n">
-        <v>6358478</v>
+        <v>6358494</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2244,6 +2239,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC15" t="inlineStr">
+        <is>
+          <t>Varav 10 mot NO.</t>
+        </is>
+      </c>
       <c r="AD15" t="b">
         <v>0</v>
       </c>
@@ -2255,7 +2255,7 @@
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktigare skog mot O-NO.</t>
+          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
         </is>
       </c>
       <c r="AT15" t="inlineStr"/>
@@ -2273,10 +2273,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>126583723</v>
+        <v>126583642</v>
       </c>
       <c r="B16" t="n">
-        <v>106037</v>
+        <v>106031</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2308,13 +2308,13 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>712196</v>
+        <v>712130</v>
       </c>
       <c r="R16" t="n">
-        <v>6358593</v>
+        <v>6358376</v>
       </c>
       <c r="S16" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2357,7 +2357,7 @@
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>Alvarskog med gläntor.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT16" t="inlineStr"/>
@@ -2375,10 +2375,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>126583642</v>
+        <v>126583723</v>
       </c>
       <c r="B17" t="n">
-        <v>106037</v>
+        <v>106031</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2410,13 +2410,13 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>712130</v>
+        <v>712196</v>
       </c>
       <c r="R17" t="n">
-        <v>6358376</v>
+        <v>6358593</v>
       </c>
       <c r="S17" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T17" t="inlineStr">
         <is>
@@ -2459,7 +2459,7 @@
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvarskog med gläntor.</t>
         </is>
       </c>
       <c r="AT17" t="inlineStr"/>
@@ -2480,7 +2480,7 @@
         <v>126583639</v>
       </c>
       <c r="B18" t="n">
-        <v>106037</v>
+        <v>106031</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2582,7 +2582,7 @@
         <v>126583698</v>
       </c>
       <c r="B19" t="n">
-        <v>106037</v>
+        <v>106031</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2684,7 +2684,7 @@
         <v>126583726</v>
       </c>
       <c r="B20" t="n">
-        <v>103895</v>
+        <v>103889</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2786,7 +2786,7 @@
         <v>126583703</v>
       </c>
       <c r="B21" t="n">
-        <v>109266</v>
+        <v>109260</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2888,7 +2888,7 @@
         <v>126583672</v>
       </c>
       <c r="B22" t="n">
-        <v>109266</v>
+        <v>109260</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2995,7 +2995,7 @@
         <v>126583699</v>
       </c>
       <c r="B23" t="n">
-        <v>98465</v>
+        <v>98459</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3103,42 +3103,42 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>126583862</v>
+        <v>126583741</v>
       </c>
       <c r="B24" t="n">
-        <v>96045</v>
+        <v>99111</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>2180</v>
+        <v>222322</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>DC.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>11</t>
         </is>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>dm²</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -3147,10 +3147,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>712369</v>
+        <v>712209</v>
       </c>
       <c r="R24" t="n">
-        <v>6358414</v>
+        <v>6358656</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3185,6 +3185,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC24" t="inlineStr">
+        <is>
+          <t>Märklig kombination av arter med ängsstarr, darrgräs, blåtåtel, ängshavre, blodnäva, färgmåra.</t>
+        </is>
+      </c>
       <c r="AD24" t="b">
         <v>0</v>
       </c>
@@ -3193,6 +3198,11 @@
       </c>
       <c r="AG24" t="b">
         <v>0</v>
+      </c>
+      <c r="AI24" t="inlineStr">
+        <is>
+          <t>Fuktmark vid stig, f.d. odlingsområde?</t>
+        </is>
       </c>
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
@@ -3212,7 +3222,7 @@
         <v>126583644</v>
       </c>
       <c r="B25" t="n">
-        <v>106037</v>
+        <v>106031</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3311,42 +3321,42 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>126583741</v>
+        <v>126583862</v>
       </c>
       <c r="B26" t="n">
-        <v>99117</v>
+        <v>96039</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>222322</v>
+        <v>2180</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>dm²</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
@@ -3355,10 +3365,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>712209</v>
+        <v>712369</v>
       </c>
       <c r="R26" t="n">
-        <v>6358656</v>
+        <v>6358414</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3393,11 +3403,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC26" t="inlineStr">
-        <is>
-          <t>Märklig kombination av arter med ängsstarr, darrgräs, blåtåtel, ängshavre, blodnäva, färgmåra.</t>
-        </is>
-      </c>
       <c r="AD26" t="b">
         <v>0</v>
       </c>
@@ -3406,11 +3411,6 @@
       </c>
       <c r="AG26" t="b">
         <v>0</v>
-      </c>
-      <c r="AI26" t="inlineStr">
-        <is>
-          <t>Fuktmark vid stig, f.d. odlingsområde?</t>
-        </is>
       </c>
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
@@ -3430,7 +3430,7 @@
         <v>126583707</v>
       </c>
       <c r="B27" t="n">
-        <v>109266</v>
+        <v>109260</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3541,7 +3541,7 @@
         <v>126583694</v>
       </c>
       <c r="B28" t="n">
-        <v>98360</v>
+        <v>98354</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3640,54 +3640,45 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>126583743</v>
+        <v>126583646</v>
       </c>
       <c r="B29" t="n">
-        <v>98465</v>
+        <v>106031</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>219847</v>
+        <v>220785</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J29" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>712224</v>
+        <v>712194</v>
       </c>
       <c r="R29" t="n">
-        <v>6358688</v>
+        <v>6358413</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3751,10 +3742,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>126583675</v>
+        <v>126583808</v>
       </c>
       <c r="B30" t="n">
-        <v>109266</v>
+        <v>43228</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3762,37 +3753,56 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220299</v>
+        <v>101242</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>712351</v>
+        <v>712218</v>
       </c>
       <c r="R30" t="n">
-        <v>6358459</v>
+        <v>6358694</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3824,11 +3834,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD30" t="b">
         <v>0</v>
       </c>
@@ -3840,7 +3845,7 @@
       </c>
       <c r="AI30" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig.</t>
+          <t>Kalkbarrskog, glänta.</t>
         </is>
       </c>
       <c r="AT30" t="inlineStr"/>
@@ -3858,45 +3863,54 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>126583646</v>
+        <v>126583743</v>
       </c>
       <c r="B31" t="n">
-        <v>106037</v>
+        <v>98459</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220785</v>
+        <v>219847</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>712194</v>
+        <v>712224</v>
       </c>
       <c r="R31" t="n">
-        <v>6358413</v>
+        <v>6358688</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -3960,10 +3974,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>126583808</v>
+        <v>126583675</v>
       </c>
       <c r="B32" t="n">
-        <v>43228</v>
+        <v>109260</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3971,56 +3985,37 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>101242</v>
+        <v>220299</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dårgräsfjäril</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Lopinga achine</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Scopoli, 1763)</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J32" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K32" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M32" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>712218</v>
+        <v>712351</v>
       </c>
       <c r="R32" t="n">
-        <v>6358694</v>
+        <v>6358459</v>
       </c>
       <c r="S32" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4052,6 +4047,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -4063,7 +4063,7 @@
       </c>
       <c r="AI32" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, glänta.</t>
+          <t>Kalkbarrskog; fuktig.</t>
         </is>
       </c>
       <c r="AT32" t="inlineStr"/>
@@ -4084,7 +4084,7 @@
         <v>126583677</v>
       </c>
       <c r="B33" t="n">
-        <v>98360</v>
+        <v>98354</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -4195,7 +4195,7 @@
         <v>126583650</v>
       </c>
       <c r="B34" t="n">
-        <v>107324</v>
+        <v>107318</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -4306,7 +4306,7 @@
         <v>126583673</v>
       </c>
       <c r="B35" t="n">
-        <v>98465</v>
+        <v>98459</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -4414,10 +4414,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>126583641</v>
+        <v>126583648</v>
       </c>
       <c r="B36" t="n">
-        <v>109266</v>
+        <v>107318</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -4425,34 +4425,43 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I36" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I36" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P36" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>712130</v>
+        <v>712194</v>
       </c>
       <c r="R36" t="n">
-        <v>6358376</v>
+        <v>6358413</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4516,10 +4525,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>126583734</v>
+        <v>126583641</v>
       </c>
       <c r="B37" t="n">
-        <v>106735</v>
+        <v>109260</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4527,16 +4536,16 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -4551,10 +4560,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>712187</v>
+        <v>712130</v>
       </c>
       <c r="R37" t="n">
-        <v>6358620</v>
+        <v>6358376</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4600,7 +4609,7 @@
       </c>
       <c r="AI37" t="inlineStr">
         <is>
-          <t>Alvartallskog, gles, med flera döda tallar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT37" t="inlineStr"/>
@@ -4618,10 +4627,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>126583648</v>
+        <v>126583734</v>
       </c>
       <c r="B38" t="n">
-        <v>107324</v>
+        <v>106729</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4629,43 +4638,34 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>220079</v>
+        <v>221849</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I38" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J38" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I38" t="inlineStr"/>
       <c r="P38" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>712194</v>
+        <v>712187</v>
       </c>
       <c r="R38" t="n">
-        <v>6358413</v>
+        <v>6358620</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="AI38" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvartallskog, gles, med flera döda tallar.</t>
         </is>
       </c>
       <c r="AT38" t="inlineStr"/>
@@ -4732,7 +4732,7 @@
         <v>126583695</v>
       </c>
       <c r="B39" t="n">
-        <v>106037</v>
+        <v>106031</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4960,7 +4960,7 @@
         <v>126583670</v>
       </c>
       <c r="B41" t="n">
-        <v>98465</v>
+        <v>98459</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5192,7 +5192,7 @@
         <v>126583714</v>
       </c>
       <c r="B43" t="n">
-        <v>109266</v>
+        <v>109260</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -5303,7 +5303,7 @@
         <v>126583678</v>
       </c>
       <c r="B44" t="n">
-        <v>109266</v>
+        <v>109260</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -5410,7 +5410,7 @@
         <v>126583728</v>
       </c>
       <c r="B45" t="n">
-        <v>106735</v>
+        <v>106729</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY109"/>
+  <dimension ref="A1:AY124"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -5305,10 +5305,10 @@
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>69286493</v>
+        <v>134682619</v>
       </c>
       <c r="B46" t="n">
-        <v>43518</v>
+        <v>43472</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -5316,61 +5316,37 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>101509</v>
+        <v>101242</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Apollofjäril</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Parnassius apollo</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J46" t="inlineStr">
-        <is>
-          <t>ex.</t>
-        </is>
-      </c>
-      <c r="K46" t="inlineStr">
-        <is>
-          <t>imago/adult</t>
-        </is>
-      </c>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>friflygande</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I46" t="inlineStr"/>
       <c r="P46" t="inlineStr">
         <is>
-          <t>Etelhem, Brännkulle, kalkugnsruinen 193 m NO, Gtl</t>
+          <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>712184</v>
+        <v>712097</v>
       </c>
       <c r="R46" t="n">
-        <v>6358780</v>
+        <v>6358400</v>
       </c>
       <c r="S46" t="n">
-        <v>25</v>
+        <v>8</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5389,17 +5365,27 @@
       </c>
       <c r="W46" t="inlineStr">
         <is>
-          <t>Etelhem</t>
+          <t>Lye</t>
         </is>
       </c>
       <c r="Y46" t="inlineStr">
         <is>
-          <t>2017-07-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z46" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA46" t="inlineStr">
         <is>
-          <t>2017-07-27</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB46" t="inlineStr">
+        <is>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5414,22 +5400,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>129004192</v>
+        <v>134682620</v>
       </c>
       <c r="B47" t="n">
-        <v>111389</v>
+        <v>43472</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -5437,21 +5423,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>219711</v>
+        <v>101242</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Sårläka</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Sanicula europaea</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5461,13 +5447,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>712118</v>
+        <v>712107</v>
       </c>
       <c r="R47" t="n">
-        <v>6358398</v>
+        <v>6358388</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5491,22 +5477,27 @@
       </c>
       <c r="Y47" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:03</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-06-26</t>
         </is>
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>11:22</t>
+          <t>15:03</t>
+        </is>
+      </c>
+      <c r="AC47" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5521,60 +5512,60 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>69379905</v>
+        <v>134682622</v>
       </c>
       <c r="B48" t="n">
-        <v>99096</v>
+        <v>43472</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
       <c r="P48" t="inlineStr">
         <is>
-          <t>Lye, Brännkulle, kalkugnsruinen 187 m ONO (Bjärges 1:20), Gtl</t>
+          <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>712239</v>
+        <v>712120</v>
       </c>
       <c r="R48" t="n">
-        <v>6358697</v>
+        <v>6358397</v>
       </c>
       <c r="S48" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5598,12 +5589,22 @@
       </c>
       <c r="Y48" t="inlineStr">
         <is>
-          <t>2017-07-20</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AA48" t="inlineStr">
         <is>
-          <t>2017-07-20</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>15:04</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5614,78 +5615,64 @@
       </c>
       <c r="AG48" t="b">
         <v>0</v>
-      </c>
-      <c r="AI48" t="inlineStr">
-        <is>
-          <t>Torpruin, lada?, vid stig i glänta.</t>
-        </is>
       </c>
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>126583700</v>
+        <v>134682623</v>
       </c>
       <c r="B49" t="n">
-        <v>99096</v>
+        <v>43472</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>219798</v>
+        <v>101242</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Skogsknipprot</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Epipactis helleborine</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Crantz</t>
-        </is>
-      </c>
-      <c r="I49" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J49" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I49" t="inlineStr"/>
       <c r="P49" t="inlineStr">
         <is>
-          <t>Bjärges 1:20 (3), Gtl</t>
+          <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>712372</v>
+        <v>712181</v>
       </c>
       <c r="R49" t="n">
-        <v>6358494</v>
+        <v>6358439</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5709,12 +5696,27 @@
       </c>
       <c r="Y49" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:09</t>
         </is>
       </c>
       <c r="AA49" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:09</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5725,78 +5727,64 @@
       </c>
       <c r="AG49" t="b">
         <v>0</v>
-      </c>
-      <c r="AI49" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
-        </is>
       </c>
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>69379901</v>
+        <v>134682626</v>
       </c>
       <c r="B50" t="n">
-        <v>99120</v>
+        <v>43472</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>219811</v>
+        <v>101242</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>21</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Etelhem, Brännkulle, kalkugnsruinen 193 m NO, Gtl</t>
+          <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>712184</v>
+        <v>712195</v>
       </c>
       <c r="R50" t="n">
-        <v>6358780</v>
+        <v>6358449</v>
       </c>
       <c r="S50" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5815,17 +5803,32 @@
       </c>
       <c r="W50" t="inlineStr">
         <is>
-          <t>Etelhem</t>
+          <t>Lye</t>
         </is>
       </c>
       <c r="Y50" t="inlineStr">
         <is>
-          <t>2017-07-20</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>15:12</t>
         </is>
       </c>
       <c r="AA50" t="inlineStr">
         <is>
-          <t>2017-07-20</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>15:12</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5840,69 +5843,60 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>69379907</v>
+        <v>134682628</v>
       </c>
       <c r="B51" t="n">
-        <v>99120</v>
+        <v>43472</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>219811</v>
+        <v>101242</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Brudsporre</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Gymnadenia conopsea</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J51" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Lye, Brännkulle, kalkugnsruinen 187 m ONO (Bjärges 1:20), Gtl</t>
+          <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>712239</v>
+        <v>712241</v>
       </c>
       <c r="R51" t="n">
-        <v>6358697</v>
+        <v>6358511</v>
       </c>
       <c r="S51" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5926,12 +5920,22 @@
       </c>
       <c r="Y51" t="inlineStr">
         <is>
-          <t>2017-07-20</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
         <is>
-          <t>2017-07-20</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>15:17</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5942,69 +5946,64 @@
       </c>
       <c r="AG51" t="b">
         <v>0</v>
-      </c>
-      <c r="AI51" t="inlineStr">
-        <is>
-          <t>Torpruin, lada?, vid stig i glänta.</t>
-        </is>
       </c>
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>69908560</v>
+        <v>134682630</v>
       </c>
       <c r="B52" t="n">
-        <v>99142</v>
+        <v>43472</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>219847</v>
+        <v>101242</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
+          <t>(Scopoli, 1763)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Lye, Brännkulle, kalkugnsruinen 187 m ONO (Bjärges 1:20), Gtl</t>
+          <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>712239</v>
+        <v>712265</v>
       </c>
       <c r="R52" t="n">
-        <v>6358697</v>
+        <v>6358551</v>
       </c>
       <c r="S52" t="n">
-        <v>25</v>
+        <v>9</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6028,12 +6027,22 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2017-07-20</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2017-07-20</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:31</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6044,78 +6053,64 @@
       </c>
       <c r="AG52" t="b">
         <v>0</v>
-      </c>
-      <c r="AI52" t="inlineStr">
-        <is>
-          <t>Torpruin, lada?, vid stig i glänta.</t>
-        </is>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>126583670</v>
+        <v>134682632</v>
       </c>
       <c r="B53" t="n">
-        <v>99142</v>
+        <v>43472</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>219847</v>
+        <v>101242</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I53" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J53" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Bjärges 1:20 (3), Gtl</t>
+          <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>712360</v>
+        <v>712267</v>
       </c>
       <c r="R53" t="n">
-        <v>6358451</v>
+        <v>6358562</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6139,12 +6134,22 @@
       </c>
       <c r="Y53" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6155,78 +6160,64 @@
       </c>
       <c r="AG53" t="b">
         <v>0</v>
-      </c>
-      <c r="AI53" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; fuktig.</t>
-        </is>
       </c>
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126583673</v>
+        <v>134682633</v>
       </c>
       <c r="B54" t="n">
-        <v>99142</v>
+        <v>43472</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>219847</v>
+        <v>101242</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="J54" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>Bjärges 1:20 (3), Gtl</t>
+          <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>712351</v>
+        <v>712247</v>
       </c>
       <c r="R54" t="n">
-        <v>6358459</v>
+        <v>6358587</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6250,12 +6241,27 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:33</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:33</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>2 st</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6266,78 +6272,64 @@
       </c>
       <c r="AG54" t="b">
         <v>0</v>
-      </c>
-      <c r="AI54" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; fuktig.</t>
-        </is>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>126583676</v>
+        <v>134686402</v>
       </c>
       <c r="B55" t="n">
-        <v>99142</v>
+        <v>43472</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>219847</v>
+        <v>101242</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I55" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J55" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr"/>
       <c r="P55" t="inlineStr">
         <is>
-          <t>Bjärges 1:20 (3), Gtl</t>
+          <t>Lye Bärges, Gtl</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>712373</v>
+        <v>712141</v>
       </c>
       <c r="R55" t="n">
-        <v>6358470</v>
+        <v>6358342</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6361,12 +6353,22 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:00</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6377,78 +6379,64 @@
       </c>
       <c r="AG55" t="b">
         <v>0</v>
-      </c>
-      <c r="AI55" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
-        </is>
       </c>
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>126583699</v>
+        <v>134686405</v>
       </c>
       <c r="B56" t="n">
-        <v>99142</v>
+        <v>43472</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>219847</v>
+        <v>101242</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J56" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Bjärges 1:20 (3), Gtl</t>
+          <t>Lye Bärges, Gtl</t>
         </is>
       </c>
       <c r="Q56" t="n">
         <v>712372</v>
       </c>
       <c r="R56" t="n">
-        <v>6358494</v>
+        <v>6358372</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6472,12 +6460,22 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6488,78 +6486,64 @@
       </c>
       <c r="AG56" t="b">
         <v>0</v>
-      </c>
-      <c r="AI56" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
-        </is>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126583743</v>
+        <v>134686409</v>
       </c>
       <c r="B57" t="n">
-        <v>99142</v>
+        <v>43472</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E57" t="n">
-        <v>219847</v>
+        <v>101242</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tvåblad</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia ovata</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Buff. &amp; Fingerh.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Bjärges 1:20 (3), Gtl</t>
+          <t>Lye Bärges, Gtl</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>712224</v>
+        <v>712403</v>
       </c>
       <c r="R57" t="n">
-        <v>6358688</v>
+        <v>6358381</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6583,12 +6567,27 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>15:24</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>15:24</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>3</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6599,31 +6598,26 @@
       </c>
       <c r="AG57" t="b">
         <v>0</v>
-      </c>
-      <c r="AI57" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>126583648</v>
+        <v>134686414</v>
       </c>
       <c r="B58" t="n">
-        <v>108116</v>
+        <v>43472</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6631,46 +6625,37 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220079</v>
+        <v>101242</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J58" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Bjärges 1:20 (3), Gtl</t>
+          <t>Lye Bärges, Gtl</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>712194</v>
+        <v>712361</v>
       </c>
       <c r="R58" t="n">
-        <v>6358413</v>
+        <v>6358367</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6694,12 +6679,22 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>15:43</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6710,31 +6705,26 @@
       </c>
       <c r="AG58" t="b">
         <v>0</v>
-      </c>
-      <c r="AI58" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>126583650</v>
+        <v>134686416</v>
       </c>
       <c r="B59" t="n">
-        <v>108116</v>
+        <v>43472</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6742,46 +6732,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220079</v>
+        <v>101242</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Dårgräsfjäril</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Lopinga achine</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="J59" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Scopoli, 1763)</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Bjärges 1:20 (3), Gtl</t>
+          <t>Lye Bärges, Gtl</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>712214</v>
+        <v>712362</v>
       </c>
       <c r="R59" t="n">
-        <v>6358424</v>
+        <v>6358353</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6805,12 +6786,22 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>15:44</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6821,31 +6812,26 @@
       </c>
       <c r="AG59" t="b">
         <v>0</v>
-      </c>
-      <c r="AI59" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>126583659</v>
+        <v>69286493</v>
       </c>
       <c r="B60" t="n">
-        <v>108116</v>
+        <v>43518</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6853,46 +6839,61 @@
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220079</v>
+        <v>101509</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Apollofjäril</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Parnassius apollo</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J60" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K60" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
+      <c r="N60" t="inlineStr">
+        <is>
+          <t>observerad</t>
         </is>
       </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Bjärges 1:20 (3), Gtl</t>
+          <t>Etelhem, Brännkulle, kalkugnsruinen 193 m NO, Gtl</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>712322</v>
+        <v>712184</v>
       </c>
       <c r="R60" t="n">
-        <v>6358407</v>
+        <v>6358780</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6911,17 +6912,17 @@
       </c>
       <c r="W60" t="inlineStr">
         <is>
-          <t>Lye</t>
+          <t>Etelhem</t>
         </is>
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2017-07-27</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2017-07-27</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6932,11 +6933,6 @@
       </c>
       <c r="AG60" t="b">
         <v>0</v>
-      </c>
-      <c r="AI60" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog.</t>
-        </is>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
@@ -6953,10 +6949,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>126583708</v>
+        <v>129004192</v>
       </c>
       <c r="B61" t="n">
-        <v>108116</v>
+        <v>111389</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6964,43 +6960,34 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220079</v>
+        <v>219711</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Sårläka</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Sanicula europaea</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J61" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Bjärges 1:20 (3), Gtl</t>
+          <t>Lye Bjärges, Gtl</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>712342</v>
+        <v>712118</v>
       </c>
       <c r="R61" t="n">
-        <v>6358478</v>
+        <v>6358398</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -7027,12 +7014,22 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>11:22</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7043,78 +7040,64 @@
       </c>
       <c r="AG61" t="b">
         <v>0</v>
-      </c>
-      <c r="AI61" t="inlineStr">
-        <is>
-          <t>Kalkbarrskog; fuktigare skog mot O-NO.</t>
-        </is>
       </c>
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Jörgen Petersson</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>126583718</v>
+        <v>69379905</v>
       </c>
       <c r="B62" t="n">
-        <v>108116</v>
+        <v>99096</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="J62" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) Crantz</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Bjärges 1:20 (3), Gtl</t>
+          <t>Lye, Brännkulle, kalkugnsruinen 187 m ONO (Bjärges 1:20), Gtl</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>712205</v>
+        <v>712239</v>
       </c>
       <c r="R62" t="n">
-        <v>6358507</v>
+        <v>6358697</v>
       </c>
       <c r="S62" t="n">
-        <v>3</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7138,12 +7121,12 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2017-07-20</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2017-07-20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7157,7 +7140,7 @@
       </c>
       <c r="AI62" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, lite äldre skog.</t>
+          <t>Torpruin, lada?, vid stig i glänta.</t>
         </is>
       </c>
       <c r="AT62" t="inlineStr"/>
@@ -7175,37 +7158,37 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>126583754</v>
+        <v>126583700</v>
       </c>
       <c r="B63" t="n">
-        <v>108116</v>
+        <v>99096</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220079</v>
+        <v>219798</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Jordtistel</t>
+          <t>Skogsknipprot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Cirsium acaule</t>
+          <t>Epipactis helleborine</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Scop.</t>
+          <t>(L.) Crantz</t>
         </is>
       </c>
       <c r="I63" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J63" t="inlineStr">
@@ -7219,13 +7202,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>712234</v>
+        <v>712372</v>
       </c>
       <c r="R63" t="n">
-        <v>6358749</v>
+        <v>6358494</v>
       </c>
       <c r="S63" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7244,7 +7227,7 @@
       </c>
       <c r="W63" t="inlineStr">
         <is>
-          <t>Etelhem</t>
+          <t>Lye</t>
         </is>
       </c>
       <c r="Y63" t="inlineStr">
@@ -7268,7 +7251,7 @@
       </c>
       <c r="AI63" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
         </is>
       </c>
       <c r="AT63" t="inlineStr"/>
@@ -7286,48 +7269,57 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>126583726</v>
+        <v>69379901</v>
       </c>
       <c r="B64" t="n">
-        <v>104640</v>
+        <v>99120</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>220164</v>
+        <v>219811</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Solvända</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Helianthemum nummularium</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Mill.</t>
-        </is>
-      </c>
-      <c r="I64" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I64" t="inlineStr">
+        <is>
+          <t>21</t>
+        </is>
+      </c>
+      <c r="J64" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Bjärges 1:20 (3), Gtl</t>
+          <t>Etelhem, Brännkulle, kalkugnsruinen 193 m NO, Gtl</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>712183</v>
+        <v>712184</v>
       </c>
       <c r="R64" t="n">
-        <v>6358595</v>
+        <v>6358780</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7346,17 +7338,17 @@
       </c>
       <c r="W64" t="inlineStr">
         <is>
-          <t>Lye</t>
+          <t>Etelhem</t>
         </is>
       </c>
       <c r="Y64" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2017-07-20</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2017-07-20</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7367,11 +7359,6 @@
       </c>
       <c r="AG64" t="b">
         <v>0</v>
-      </c>
-      <c r="AI64" t="inlineStr">
-        <is>
-          <t>Alvarglänta.</t>
-        </is>
       </c>
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
@@ -7388,48 +7375,57 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>126583618</v>
+        <v>69379907</v>
       </c>
       <c r="B65" t="n">
-        <v>110078</v>
+        <v>99120</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220299</v>
+        <v>219811</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Brudsporre</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Gymnadenia conopsea</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I65" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J65" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Tänglings 1:47 (2), Gtl</t>
+          <t>Lye, Brännkulle, kalkugnsruinen 187 m ONO (Bjärges 1:20), Gtl</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>712182</v>
+        <v>712239</v>
       </c>
       <c r="R65" t="n">
-        <v>6358762</v>
+        <v>6358697</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7448,17 +7444,17 @@
       </c>
       <c r="W65" t="inlineStr">
         <is>
-          <t>Etelhem</t>
+          <t>Lye</t>
         </is>
       </c>
       <c r="Y65" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2017-07-20</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2017-07-20</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7472,7 +7468,7 @@
       </c>
       <c r="AI65" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Torpruin, lada?, vid stig i glänta.</t>
         </is>
       </c>
       <c r="AT65" t="inlineStr"/>
@@ -7490,48 +7486,48 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>126583633</v>
+        <v>69908560</v>
       </c>
       <c r="B66" t="n">
-        <v>110078</v>
+        <v>99142</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Buff. &amp; Fingerh.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Bjärges 1:20 (3), Gtl</t>
+          <t>Lye, Brännkulle, kalkugnsruinen 187 m ONO (Bjärges 1:20), Gtl</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>712092</v>
+        <v>712239</v>
       </c>
       <c r="R66" t="n">
-        <v>6358436</v>
+        <v>6358697</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7555,12 +7551,12 @@
       </c>
       <c r="Y66" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2017-07-20</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2017-07-20</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7574,7 +7570,7 @@
       </c>
       <c r="AI66" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Torpruin, lada?, vid stig i glänta.</t>
         </is>
       </c>
       <c r="AT66" t="inlineStr"/>
@@ -7592,45 +7588,54 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>126583641</v>
+        <v>126583670</v>
       </c>
       <c r="B67" t="n">
-        <v>110078</v>
+        <v>99142</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J67" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>712130</v>
+        <v>712360</v>
       </c>
       <c r="R67" t="n">
-        <v>6358376</v>
+        <v>6358451</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7676,7 +7681,7 @@
       </c>
       <c r="AI67" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog; fuktig.</t>
         </is>
       </c>
       <c r="AT67" t="inlineStr"/>
@@ -7694,45 +7699,54 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>126583672</v>
+        <v>126583673</v>
       </c>
       <c r="B68" t="n">
-        <v>110078</v>
+        <v>99142</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>712360</v>
+        <v>712351</v>
       </c>
       <c r="R68" t="n">
-        <v>6358451</v>
+        <v>6358459</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7765,11 +7779,6 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2025-06-26</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7801,45 +7810,54 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>126583675</v>
+        <v>126583676</v>
       </c>
       <c r="B69" t="n">
-        <v>110078</v>
+        <v>99142</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J69" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>712351</v>
+        <v>712373</v>
       </c>
       <c r="R69" t="n">
-        <v>6358459</v>
+        <v>6358470</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7874,11 +7892,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD69" t="b">
         <v>0</v>
       </c>
@@ -7890,7 +7903,7 @@
       </c>
       <c r="AI69" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig.</t>
+          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
         </is>
       </c>
       <c r="AT69" t="inlineStr"/>
@@ -7908,45 +7921,54 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>126583678</v>
+        <v>126583699</v>
       </c>
       <c r="B70" t="n">
-        <v>110078</v>
+        <v>99142</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J70" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>712373</v>
+        <v>712372</v>
       </c>
       <c r="R70" t="n">
-        <v>6358470</v>
+        <v>6358494</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7981,11 +8003,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD70" t="b">
         <v>0</v>
       </c>
@@ -7997,7 +8014,7 @@
       </c>
       <c r="AI70" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
+          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
         </is>
       </c>
       <c r="AT70" t="inlineStr"/>
@@ -8015,45 +8032,54 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>126583702</v>
+        <v>126583743</v>
       </c>
       <c r="B71" t="n">
-        <v>110078</v>
+        <v>99142</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220299</v>
+        <v>219847</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Tvåblad</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Neottia ovata</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) Buff. &amp; Fingerh.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J71" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>712372</v>
+        <v>712224</v>
       </c>
       <c r="R71" t="n">
-        <v>6358494</v>
+        <v>6358688</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8088,11 +8114,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Spridd.</t>
-        </is>
-      </c>
       <c r="AD71" t="b">
         <v>0</v>
       </c>
@@ -8104,7 +8125,7 @@
       </c>
       <c r="AI71" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT71" t="inlineStr"/>
@@ -8122,10 +8143,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>126583703</v>
+        <v>126583648</v>
       </c>
       <c r="B72" t="n">
-        <v>110078</v>
+        <v>108116</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -8133,34 +8154,43 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="J72" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>712360</v>
+        <v>712194</v>
       </c>
       <c r="R72" t="n">
-        <v>6358476</v>
+        <v>6358413</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8206,7 +8236,7 @@
       </c>
       <c r="AI72" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktigare skog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT72" t="inlineStr"/>
@@ -8224,10 +8254,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>126583707</v>
+        <v>126583650</v>
       </c>
       <c r="B73" t="n">
-        <v>110078</v>
+        <v>108116</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -8235,31 +8265,31 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>8</t>
         </is>
       </c>
       <c r="J73" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P73" t="inlineStr">
@@ -8268,10 +8298,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>712342</v>
+        <v>712214</v>
       </c>
       <c r="R73" t="n">
-        <v>6358478</v>
+        <v>6358424</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8317,7 +8347,7 @@
       </c>
       <c r="AI73" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktigare skog mot O-NO.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT73" t="inlineStr"/>
@@ -8335,10 +8365,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>126583714</v>
+        <v>126583659</v>
       </c>
       <c r="B74" t="n">
-        <v>110078</v>
+        <v>108116</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -8346,26 +8376,26 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>4</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -8379,13 +8409,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>712284</v>
+        <v>712322</v>
       </c>
       <c r="R74" t="n">
-        <v>6358477</v>
+        <v>6358407</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8428,7 +8458,7 @@
       </c>
       <c r="AI74" t="inlineStr">
         <is>
-          <t>Kalkbarrskog, lite äldre skog.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT74" t="inlineStr"/>
@@ -8446,10 +8476,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>126583720</v>
+        <v>126583708</v>
       </c>
       <c r="B75" t="n">
-        <v>110078</v>
+        <v>108116</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -8457,31 +8487,31 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>220299</v>
+        <v>220079</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Scop.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J75" t="inlineStr">
         <is>
-          <t>m²</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
@@ -8490,10 +8520,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>712215</v>
+        <v>712342</v>
       </c>
       <c r="R75" t="n">
-        <v>6358579</v>
+        <v>6358478</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8528,11 +8558,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Vid mindre sten (OL-kontroll).</t>
-        </is>
-      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -8544,7 +8569,7 @@
       </c>
       <c r="AI75" t="inlineStr">
         <is>
-          <t>Tallskog med yngre rakare tallar, enstaka grövre samt enstaka granar. Möjligen på f.d. odlingsområde (jfr Fornsök).</t>
+          <t>Kalkbarrskog; fuktigare skog mot O-NO.</t>
         </is>
       </c>
       <c r="AT75" t="inlineStr"/>
@@ -8562,48 +8587,57 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>126583639</v>
+        <v>126583718</v>
       </c>
       <c r="B76" t="n">
-        <v>106813</v>
+        <v>108116</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220785</v>
+        <v>220079</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J76" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>712121</v>
+        <v>712205</v>
       </c>
       <c r="R76" t="n">
-        <v>6358401</v>
+        <v>6358507</v>
       </c>
       <c r="S76" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8646,7 +8680,7 @@
       </c>
       <c r="AI76" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkbarrskog, lite äldre skog.</t>
         </is>
       </c>
       <c r="AT76" t="inlineStr"/>
@@ -8664,48 +8698,57 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>126583642</v>
+        <v>126583754</v>
       </c>
       <c r="B77" t="n">
-        <v>106813</v>
+        <v>108116</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220785</v>
+        <v>220079</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Jordtistel</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Cirsium acaule</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) Scop.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J77" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>712130</v>
+        <v>712234</v>
       </c>
       <c r="R77" t="n">
-        <v>6358376</v>
+        <v>6358749</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8724,7 +8767,7 @@
       </c>
       <c r="W77" t="inlineStr">
         <is>
-          <t>Lye</t>
+          <t>Etelhem</t>
         </is>
       </c>
       <c r="Y77" t="inlineStr">
@@ -8766,32 +8809,32 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>126583644</v>
+        <v>126583726</v>
       </c>
       <c r="B78" t="n">
-        <v>106813</v>
+        <v>104640</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220785</v>
+        <v>220164</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Solvända</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Helianthemum nummularium</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Mill.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8801,13 +8844,13 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>712152</v>
+        <v>712183</v>
       </c>
       <c r="R78" t="n">
-        <v>6358376</v>
+        <v>6358595</v>
       </c>
       <c r="S78" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8850,7 +8893,7 @@
       </c>
       <c r="AI78" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Alvarglänta.</t>
         </is>
       </c>
       <c r="AT78" t="inlineStr"/>
@@ -8868,27 +8911,27 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>126583646</v>
+        <v>126583618</v>
       </c>
       <c r="B79" t="n">
-        <v>106813</v>
+        <v>110078</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -8899,14 +8942,14 @@
       <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Bjärges 1:20 (3), Gtl</t>
+          <t>Tänglings 1:47 (2), Gtl</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>712194</v>
+        <v>712182</v>
       </c>
       <c r="R79" t="n">
-        <v>6358413</v>
+        <v>6358762</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -8928,7 +8971,7 @@
       </c>
       <c r="W79" t="inlineStr">
         <is>
-          <t>Lye</t>
+          <t>Etelhem</t>
         </is>
       </c>
       <c r="Y79" t="inlineStr">
@@ -8952,7 +8995,7 @@
       </c>
       <c r="AI79" t="inlineStr">
         <is>
-          <t>Kalkbarrskog.</t>
+          <t>Kalkhäll i kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT79" t="inlineStr"/>
@@ -8970,27 +9013,27 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>126583688</v>
+        <v>126583633</v>
       </c>
       <c r="B80" t="n">
-        <v>106813</v>
+        <v>110078</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
@@ -9005,10 +9048,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>712386</v>
+        <v>712092</v>
       </c>
       <c r="R80" t="n">
-        <v>6358485</v>
+        <v>6358436</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9054,7 +9097,7 @@
       </c>
       <c r="AI80" t="inlineStr">
         <is>
-          <t>Sumpskog runt dike; träd på socklar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT80" t="inlineStr"/>
@@ -9072,27 +9115,27 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>126583695</v>
+        <v>126583641</v>
       </c>
       <c r="B81" t="n">
-        <v>106813</v>
+        <v>110078</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -9107,10 +9150,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>712382</v>
+        <v>712130</v>
       </c>
       <c r="R81" t="n">
-        <v>6358499</v>
+        <v>6358376</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9156,7 +9199,7 @@
       </c>
       <c r="AI81" t="inlineStr">
         <is>
-          <t>Sumpskog runt dike; träd på socklar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT81" t="inlineStr"/>
@@ -9174,27 +9217,27 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>126583698</v>
+        <v>126583672</v>
       </c>
       <c r="B82" t="n">
-        <v>106813</v>
+        <v>110078</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -9209,10 +9252,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>712372</v>
+        <v>712360</v>
       </c>
       <c r="R82" t="n">
-        <v>6358494</v>
+        <v>6358451</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9247,6 +9290,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC82" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD82" t="b">
         <v>0</v>
       </c>
@@ -9258,7 +9306,7 @@
       </c>
       <c r="AI82" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
+          <t>Kalkbarrskog; fuktig.</t>
         </is>
       </c>
       <c r="AT82" t="inlineStr"/>
@@ -9276,27 +9324,27 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>126583723</v>
+        <v>126583675</v>
       </c>
       <c r="B83" t="n">
-        <v>106813</v>
+        <v>110078</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>220785</v>
+        <v>220299</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Ask</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fraxinus excelsior</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -9311,13 +9359,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>712196</v>
+        <v>712351</v>
       </c>
       <c r="R83" t="n">
-        <v>6358593</v>
+        <v>6358459</v>
       </c>
       <c r="S83" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9349,6 +9397,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC83" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD83" t="b">
         <v>0</v>
       </c>
@@ -9360,7 +9413,7 @@
       </c>
       <c r="AI83" t="inlineStr">
         <is>
-          <t>Alvarskog med gläntor.</t>
+          <t>Kalkbarrskog; fuktig.</t>
         </is>
       </c>
       <c r="AT83" t="inlineStr"/>
@@ -9378,10 +9431,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>126583620</v>
+        <v>126583678</v>
       </c>
       <c r="B84" t="n">
-        <v>107517</v>
+        <v>110078</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -9389,16 +9442,16 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
@@ -9409,17 +9462,17 @@
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Tänglings 1:47 (2), Gtl</t>
+          <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>712156</v>
+        <v>712373</v>
       </c>
       <c r="R84" t="n">
-        <v>6358682</v>
+        <v>6358470</v>
       </c>
       <c r="S84" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9438,7 +9491,7 @@
       </c>
       <c r="W84" t="inlineStr">
         <is>
-          <t>Etelhem</t>
+          <t>Lye</t>
         </is>
       </c>
       <c r="Y84" t="inlineStr">
@@ -9451,6 +9504,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD84" t="b">
         <v>0</v>
       </c>
@@ -9462,7 +9520,7 @@
       </c>
       <c r="AI84" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
         </is>
       </c>
       <c r="AT84" t="inlineStr"/>
@@ -9480,10 +9538,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>126583728</v>
+        <v>126583702</v>
       </c>
       <c r="B85" t="n">
-        <v>107517</v>
+        <v>110078</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -9491,16 +9549,16 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -9515,10 +9573,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>712183</v>
+        <v>712372</v>
       </c>
       <c r="R85" t="n">
-        <v>6358595</v>
+        <v>6358494</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9553,6 +9611,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Spridd.</t>
+        </is>
+      </c>
       <c r="AD85" t="b">
         <v>0</v>
       </c>
@@ -9564,7 +9627,7 @@
       </c>
       <c r="AI85" t="inlineStr">
         <is>
-          <t>Alvarglänta.</t>
+          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
         </is>
       </c>
       <c r="AT85" t="inlineStr"/>
@@ -9582,10 +9645,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>126583734</v>
+        <v>126583703</v>
       </c>
       <c r="B86" t="n">
-        <v>107517</v>
+        <v>110078</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -9593,16 +9656,16 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>221849</v>
+        <v>220299</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Backtimjan</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Thymus serpyllum</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
@@ -9617,10 +9680,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>712187</v>
+        <v>712360</v>
       </c>
       <c r="R86" t="n">
-        <v>6358620</v>
+        <v>6358476</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9666,7 +9729,7 @@
       </c>
       <c r="AI86" t="inlineStr">
         <is>
-          <t>Alvartallskog, gles, med flera döda tallar.</t>
+          <t>Kalkbarrskog; fuktigare skog.</t>
         </is>
       </c>
       <c r="AT86" t="inlineStr"/>
@@ -9684,10 +9747,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>126583622</v>
+        <v>126583707</v>
       </c>
       <c r="B87" t="n">
-        <v>107061</v>
+        <v>110078</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -9695,16 +9758,16 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>221903</v>
+        <v>220299</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Axveronika</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Veronica spicata</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -9712,17 +9775,26 @@
           <t>L.</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr"/>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J87" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Tänglings 1:47 (2), Gtl</t>
+          <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>712156</v>
+        <v>712342</v>
       </c>
       <c r="R87" t="n">
-        <v>6358682</v>
+        <v>6358478</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9744,7 +9816,7 @@
       </c>
       <c r="W87" t="inlineStr">
         <is>
-          <t>Etelhem</t>
+          <t>Lye</t>
         </is>
       </c>
       <c r="Y87" t="inlineStr">
@@ -9768,7 +9840,7 @@
       </c>
       <c r="AI87" t="inlineStr">
         <is>
-          <t>Kalkhäll i kalkbarrskog.</t>
+          <t>Kalkbarrskog; fuktigare skog mot O-NO.</t>
         </is>
       </c>
       <c r="AT87" t="inlineStr"/>
@@ -9786,10 +9858,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>126583741</v>
+        <v>126583714</v>
       </c>
       <c r="B88" t="n">
-        <v>99803</v>
+        <v>110078</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -9797,31 +9869,31 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>222322</v>
+        <v>220299</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Ängsstarr</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carex hostiana</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>DC.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>10</t>
         </is>
       </c>
       <c r="J88" t="inlineStr">
         <is>
-          <t>stjälkar/strån/skott</t>
+          <t>plantor/tuvor</t>
         </is>
       </c>
       <c r="P88" t="inlineStr">
@@ -9830,10 +9902,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>712209</v>
+        <v>712284</v>
       </c>
       <c r="R88" t="n">
-        <v>6358656</v>
+        <v>6358477</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9868,11 +9940,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>Märklig kombination av arter med ängsstarr, darrgräs, blåtåtel, ängshavre, blodnäva, färgmåra.</t>
-        </is>
-      </c>
       <c r="AD88" t="b">
         <v>0</v>
       </c>
@@ -9884,7 +9951,7 @@
       </c>
       <c r="AI88" t="inlineStr">
         <is>
-          <t>Fuktmark vid stig, f.d. odlingsområde?</t>
+          <t>Kalkbarrskog, lite äldre skog.</t>
         </is>
       </c>
       <c r="AT88" t="inlineStr"/>
@@ -9902,42 +9969,42 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>126583677</v>
+        <v>126583720</v>
       </c>
       <c r="B89" t="n">
-        <v>99036</v>
+        <v>110078</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>223591</v>
+        <v>220299</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Svinrot</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Scorzonera humilis</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr">
         <is>
-          <t>66</t>
+          <t>1</t>
         </is>
       </c>
       <c r="J89" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>m²</t>
         </is>
       </c>
       <c r="P89" t="inlineStr">
@@ -9946,10 +10013,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>712373</v>
+        <v>712215</v>
       </c>
       <c r="R89" t="n">
-        <v>6358470</v>
+        <v>6358579</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9984,6 +10051,11 @@
           <t>2025-06-26</t>
         </is>
       </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Vid mindre sten (OL-kontroll).</t>
+        </is>
+      </c>
       <c r="AD89" t="b">
         <v>0</v>
       </c>
@@ -9995,7 +10067,7 @@
       </c>
       <c r="AI89" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
+          <t>Tallskog med yngre rakare tallar, enstaka grövre samt enstaka granar. Möjligen på f.d. odlingsområde (jfr Fornsök).</t>
         </is>
       </c>
       <c r="AT89" t="inlineStr"/>
@@ -10013,57 +10085,48 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>126583687</v>
+        <v>126583639</v>
       </c>
       <c r="B90" t="n">
-        <v>99036</v>
+        <v>106813</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>25</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>712386</v>
+        <v>712121</v>
       </c>
       <c r="R90" t="n">
-        <v>6358485</v>
+        <v>6358401</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10106,7 +10169,7 @@
       </c>
       <c r="AI90" t="inlineStr">
         <is>
-          <t>Sumpskog runt dike; träd på socklar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT90" t="inlineStr"/>
@@ -10124,32 +10187,32 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>126583694</v>
+        <v>126583642</v>
       </c>
       <c r="B91" t="n">
-        <v>99036</v>
+        <v>106813</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10159,10 +10222,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>712382</v>
+        <v>712130</v>
       </c>
       <c r="R91" t="n">
-        <v>6358499</v>
+        <v>6358376</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10208,7 +10271,7 @@
       </c>
       <c r="AI91" t="inlineStr">
         <is>
-          <t>Sumpskog runt dike; träd på socklar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT91" t="inlineStr"/>
@@ -10226,57 +10289,48 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>126583701</v>
+        <v>126583644</v>
       </c>
       <c r="B92" t="n">
-        <v>99036</v>
+        <v>106813</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>223591</v>
+        <v>220785</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Skogsnycklar</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. fuchsii</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Druce) Hyl.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>75</t>
-        </is>
-      </c>
-      <c r="J92" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>712372</v>
+        <v>712152</v>
       </c>
       <c r="R92" t="n">
-        <v>6358494</v>
+        <v>6358376</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10308,11 +10362,6 @@
           <t>2025-06-26</t>
         </is>
       </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Varav 10 mot NO.</t>
-        </is>
-      </c>
       <c r="AD92" t="b">
         <v>0</v>
       </c>
@@ -10324,7 +10373,7 @@
       </c>
       <c r="AI92" t="inlineStr">
         <is>
-          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
+          <t>Kalkbarrskog.</t>
         </is>
       </c>
       <c r="AT92" t="inlineStr"/>
@@ -10342,42 +10391,42 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>128947647</v>
+        <v>126583646</v>
       </c>
       <c r="B93" t="n">
-        <v>87369</v>
+        <v>106813</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>248947</v>
+        <v>220785</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Lye Bjärges, Gtl</t>
+          <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>712175</v>
+        <v>712194</v>
       </c>
       <c r="R93" t="n">
         <v>6358413</v>
@@ -10407,12 +10456,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10423,61 +10472,66 @@
       </c>
       <c r="AG93" t="b">
         <v>0</v>
+      </c>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>128947648</v>
+        <v>126583688</v>
       </c>
       <c r="B94" t="n">
-        <v>87369</v>
+        <v>106813</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>248947</v>
+        <v>220785</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Lye Bjärges, Gtl</t>
+          <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>712168</v>
+        <v>712386</v>
       </c>
       <c r="R94" t="n">
-        <v>6358403</v>
+        <v>6358485</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10504,12 +10558,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10520,61 +10574,66 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AI94" t="inlineStr">
+        <is>
+          <t>Sumpskog runt dike; träd på socklar.</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>128947649</v>
+        <v>126583695</v>
       </c>
       <c r="B95" t="n">
-        <v>87369</v>
+        <v>106813</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>248947</v>
+        <v>220785</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Lye Bjärges, Gtl</t>
+          <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>712051</v>
+        <v>712382</v>
       </c>
       <c r="R95" t="n">
-        <v>6358299</v>
+        <v>6358499</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10601,12 +10660,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10617,61 +10676,66 @@
       </c>
       <c r="AG95" t="b">
         <v>0</v>
+      </c>
+      <c r="AI95" t="inlineStr">
+        <is>
+          <t>Sumpskog runt dike; träd på socklar.</t>
+        </is>
       </c>
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>129004190</v>
+        <v>126583698</v>
       </c>
       <c r="B96" t="n">
-        <v>87369</v>
+        <v>106813</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>248947</v>
+        <v>220785</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Lye Bjärges, Gtl</t>
+          <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>712178</v>
+        <v>712372</v>
       </c>
       <c r="R96" t="n">
-        <v>6358421</v>
+        <v>6358494</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10698,22 +10762,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>13:08</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10724,64 +10778,69 @@
       </c>
       <c r="AG96" t="b">
         <v>0</v>
+      </c>
+      <c r="AI96" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
+        </is>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>129004191</v>
+        <v>126583723</v>
       </c>
       <c r="B97" t="n">
-        <v>87369</v>
+        <v>106813</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>248947</v>
+        <v>220785</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Lye Bjärges, Gtl</t>
+          <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>712118</v>
+        <v>712196</v>
       </c>
       <c r="R97" t="n">
-        <v>6358397</v>
+        <v>6358593</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10805,22 +10864,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10831,64 +10880,69 @@
       </c>
       <c r="AG97" t="b">
         <v>0</v>
+      </c>
+      <c r="AI97" t="inlineStr">
+        <is>
+          <t>Alvarskog med gläntor.</t>
+        </is>
       </c>
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128947663</v>
+        <v>126583620</v>
       </c>
       <c r="B98" t="n">
-        <v>87262</v>
+        <v>107517</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>248956</v>
+        <v>221849</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Lye Bjärges, Gtl</t>
+          <t>Tänglings 1:47 (2), Gtl</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>712176</v>
+        <v>712156</v>
       </c>
       <c r="R98" t="n">
-        <v>6358409</v>
+        <v>6358682</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10907,17 +10961,17 @@
       </c>
       <c r="W98" t="inlineStr">
         <is>
-          <t>Lye</t>
+          <t>Etelhem</t>
         </is>
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10926,64 +10980,68 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
-      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
+      </c>
+      <c r="AI98" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>129004203</v>
+        <v>126583728</v>
       </c>
       <c r="B99" t="n">
-        <v>87262</v>
+        <v>107517</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>248956</v>
+        <v>221849</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Lye Bjärges, Gtl</t>
+          <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>712263</v>
+        <v>712183</v>
       </c>
       <c r="R99" t="n">
-        <v>6358461</v>
+        <v>6358595</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11010,22 +11068,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>13:47</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11036,61 +11084,66 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AI99" t="inlineStr">
+        <is>
+          <t>Alvarglänta.</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>129004204</v>
+        <v>126583734</v>
       </c>
       <c r="B100" t="n">
-        <v>87262</v>
+        <v>107517</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>248956</v>
+        <v>221849</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Backtimjan</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Thymus serpyllum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Lye Bjärges, Gtl</t>
+          <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>712180</v>
+        <v>712187</v>
       </c>
       <c r="R100" t="n">
-        <v>6358430</v>
+        <v>6358620</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11117,22 +11170,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>13:02</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11143,26 +11186,31 @@
       </c>
       <c r="AG100" t="b">
         <v>0</v>
+      </c>
+      <c r="AI100" t="inlineStr">
+        <is>
+          <t>Alvartallskog, gles, med flera döda tallar.</t>
+        </is>
       </c>
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129004195</v>
+        <v>126583622</v>
       </c>
       <c r="B101" t="n">
-        <v>87323</v>
+        <v>107061</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -11170,34 +11218,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>249228</v>
+        <v>221903</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Axveronika</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Veronica spicata</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Lye Bjärges, Gtl</t>
+          <t>Tänglings 1:47 (2), Gtl</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>712179</v>
+        <v>712156</v>
       </c>
       <c r="R101" t="n">
-        <v>6358417</v>
+        <v>6358682</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11219,93 +11267,96 @@
       </c>
       <c r="W101" t="inlineStr">
         <is>
-          <t>Lye</t>
+          <t>Etelhem</t>
         </is>
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>13:15</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD101" t="b">
         <v>0</v>
       </c>
       <c r="AE101" t="b">
-        <v>1</v>
-      </c>
-      <c r="AF101" t="inlineStr"/>
+        <v>0</v>
+      </c>
       <c r="AG101" t="b">
         <v>0</v>
+      </c>
+      <c r="AI101" t="inlineStr">
+        <is>
+          <t>Kalkhäll i kalkbarrskog.</t>
+        </is>
       </c>
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129004202</v>
+        <v>126583741</v>
       </c>
       <c r="B102" t="n">
-        <v>91316</v>
+        <v>99803</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>1000938</v>
+        <v>222322</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Jordstjärnesläktet</t>
+          <t>Ängsstarr</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Geastrum</t>
+          <t>Carex hostiana</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>DC.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J102" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Lye Bjärges, Gtl</t>
+          <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>712196</v>
+        <v>712209</v>
       </c>
       <c r="R102" t="n">
-        <v>6358401</v>
+        <v>6358656</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11332,22 +11383,17 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>13:25</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Märklig kombination av arter med ängsstarr, darrgräs, blåtåtel, ängshavre, blodnäva, färgmåra.</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11356,51 +11402,55 @@
       <c r="AE102" t="b">
         <v>0</v>
       </c>
-      <c r="AF102" t="inlineStr"/>
       <c r="AG102" t="b">
         <v>0</v>
+      </c>
+      <c r="AI102" t="inlineStr">
+        <is>
+          <t>Fuktmark vid stig, f.d. odlingsområde?</t>
+        </is>
       </c>
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128947656</v>
+        <v>134682629</v>
       </c>
       <c r="B103" t="n">
-        <v>87346</v>
+        <v>99001</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6003295</v>
+        <v>223049</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Ormbär</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Paris quadrifolia</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11410,13 +11460,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>712239</v>
+        <v>712242</v>
       </c>
       <c r="R103" t="n">
-        <v>6358515</v>
+        <v>6358510</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11440,12 +11490,22 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11454,7 +11514,6 @@
       <c r="AE103" t="b">
         <v>0</v>
       </c>
-      <c r="AF103" t="inlineStr"/>
       <c r="AG103" t="b">
         <v>0</v>
       </c>
@@ -11473,45 +11532,54 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>128947657</v>
+        <v>126583677</v>
       </c>
       <c r="B104" t="n">
-        <v>87346</v>
+        <v>99036</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6003295</v>
+        <v>223591</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr">
+        <is>
+          <t>66</t>
+        </is>
+      </c>
+      <c r="J104" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Lye Bjärges, Gtl</t>
+          <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>712164</v>
+        <v>712373</v>
       </c>
       <c r="R104" t="n">
-        <v>6358415</v>
+        <v>6358470</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11538,12 +11606,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11552,64 +11620,77 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
+      </c>
+      <c r="AI104" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; fuktig, träd på socklar.</t>
+        </is>
       </c>
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>128947659</v>
+        <v>126583687</v>
       </c>
       <c r="B105" t="n">
-        <v>87346</v>
+        <v>99036</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6003295</v>
+        <v>223591</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>25</t>
+        </is>
+      </c>
+      <c r="J105" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Lye Bjärges, Gtl</t>
+          <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>712053</v>
+        <v>712386</v>
       </c>
       <c r="R105" t="n">
-        <v>6358298</v>
+        <v>6358485</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11636,12 +11717,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11650,64 +11731,68 @@
       <c r="AE105" t="b">
         <v>0</v>
       </c>
-      <c r="AF105" t="inlineStr"/>
       <c r="AG105" t="b">
         <v>0</v>
+      </c>
+      <c r="AI105" t="inlineStr">
+        <is>
+          <t>Sumpskog runt dike; träd på socklar.</t>
+        </is>
       </c>
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>128947660</v>
+        <v>126583694</v>
       </c>
       <c r="B106" t="n">
-        <v>87346</v>
+        <v>99036</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6003295</v>
+        <v>223591</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Lye Bjärges, Gtl</t>
+          <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>712054</v>
+        <v>712382</v>
       </c>
       <c r="R106" t="n">
-        <v>6358300</v>
+        <v>6358499</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11734,12 +11819,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11748,64 +11833,77 @@
       <c r="AE106" t="b">
         <v>0</v>
       </c>
-      <c r="AF106" t="inlineStr"/>
       <c r="AG106" t="b">
         <v>0</v>
+      </c>
+      <c r="AI106" t="inlineStr">
+        <is>
+          <t>Sumpskog runt dike; träd på socklar.</t>
+        </is>
       </c>
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>129004198</v>
+        <v>126583701</v>
       </c>
       <c r="B107" t="n">
-        <v>87346</v>
+        <v>99036</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6003295</v>
+        <v>223591</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(Druce) Hyl.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="J107" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Lye Bjärges, Gtl</t>
+          <t>Bjärges 1:20 (3), Gtl</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>712260</v>
+        <v>712372</v>
       </c>
       <c r="R107" t="n">
-        <v>6358398</v>
+        <v>6358494</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11832,22 +11930,17 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>13:55</t>
+          <t>2025-06-26</t>
+        </is>
+      </c>
+      <c r="AC107" t="inlineStr">
+        <is>
+          <t>Varav 10 mot NO.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11856,51 +11949,55 @@
       <c r="AE107" t="b">
         <v>0</v>
       </c>
-      <c r="AF107" t="inlineStr"/>
       <c r="AG107" t="b">
         <v>0</v>
+      </c>
+      <c r="AI107" t="inlineStr">
+        <is>
+          <t>Kalkbarrskog; fuktig med blåtåtel; träd på socklar.</t>
+        </is>
       </c>
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Jörgen Petersson</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129004199</v>
+        <v>128947647</v>
       </c>
       <c r="B108" t="n">
-        <v>87346</v>
+        <v>87369</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6003295</v>
+        <v>248947</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -11910,10 +12007,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>712133</v>
+        <v>712175</v>
       </c>
       <c r="R108" t="n">
-        <v>6358416</v>
+        <v>6358413</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -11943,72 +12040,61 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AD108" t="b">
         <v>0</v>
       </c>
       <c r="AE108" t="b">
         <v>0</v>
       </c>
-      <c r="AF108" t="inlineStr"/>
       <c r="AG108" t="b">
         <v>0</v>
       </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>129004200</v>
+        <v>128947648</v>
       </c>
       <c r="B109" t="n">
-        <v>87346</v>
+        <v>87369</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6003295</v>
+        <v>248947</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12018,10 +12104,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>712116</v>
+        <v>712168</v>
       </c>
       <c r="R109" t="n">
-        <v>6358338</v>
+        <v>6358403</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12051,43 +12137,1587 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AD109" t="b">
         <v>0</v>
       </c>
       <c r="AE109" t="b">
         <v>0</v>
       </c>
-      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX109" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY109" t="inlineStr"/>
+    </row>
+    <row r="110">
+      <c r="A110" t="n">
+        <v>128947649</v>
+      </c>
+      <c r="B110" t="n">
+        <v>87369</v>
+      </c>
+      <c r="D110" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E110" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F110" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G110" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
+      <c r="P110" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q110" t="n">
+        <v>712051</v>
+      </c>
+      <c r="R110" t="n">
+        <v>6358299</v>
+      </c>
+      <c r="S110" t="n">
+        <v>10</v>
+      </c>
+      <c r="T110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V110" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W110" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y110" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA110" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG110" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT110" t="inlineStr"/>
+      <c r="AW110" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX110" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY110" t="inlineStr"/>
+    </row>
+    <row r="111">
+      <c r="A111" t="n">
+        <v>129004190</v>
+      </c>
+      <c r="B111" t="n">
+        <v>87369</v>
+      </c>
+      <c r="D111" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E111" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F111" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G111" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="P111" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q111" t="n">
+        <v>712178</v>
+      </c>
+      <c r="R111" t="n">
+        <v>6358421</v>
+      </c>
+      <c r="S111" t="n">
+        <v>10</v>
+      </c>
+      <c r="T111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V111" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W111" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y111" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AA111" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>13:08</t>
+        </is>
+      </c>
+      <c r="AD111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG111" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT111" t="inlineStr"/>
+      <c r="AW111" t="inlineStr">
+        <is>
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AX109" t="inlineStr">
+      <c r="AX111" t="inlineStr">
         <is>
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY109" t="inlineStr"/>
+      <c r="AY111" t="inlineStr"/>
+    </row>
+    <row r="112">
+      <c r="A112" t="n">
+        <v>129004191</v>
+      </c>
+      <c r="B112" t="n">
+        <v>87369</v>
+      </c>
+      <c r="D112" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E112" t="n">
+        <v>248947</v>
+      </c>
+      <c r="F112" t="inlineStr">
+        <is>
+          <t>Trollspindling</t>
+        </is>
+      </c>
+      <c r="G112" t="inlineStr">
+        <is>
+          <t>Cortinarius subgracilis</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr">
+        <is>
+          <t>Moënne-Locc.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
+      <c r="P112" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q112" t="n">
+        <v>712118</v>
+      </c>
+      <c r="R112" t="n">
+        <v>6358397</v>
+      </c>
+      <c r="S112" t="n">
+        <v>10</v>
+      </c>
+      <c r="T112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V112" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W112" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y112" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA112" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG112" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT112" t="inlineStr"/>
+      <c r="AW112" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX112" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
+    </row>
+    <row r="113">
+      <c r="A113" t="n">
+        <v>128947663</v>
+      </c>
+      <c r="B113" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D113" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E113" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F113" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G113" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
+      <c r="P113" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q113" t="n">
+        <v>712176</v>
+      </c>
+      <c r="R113" t="n">
+        <v>6358409</v>
+      </c>
+      <c r="S113" t="n">
+        <v>10</v>
+      </c>
+      <c r="T113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V113" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W113" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y113" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA113" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF113" t="inlineStr"/>
+      <c r="AG113" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT113" t="inlineStr"/>
+      <c r="AW113" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX113" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr"/>
+    </row>
+    <row r="114">
+      <c r="A114" t="n">
+        <v>129004203</v>
+      </c>
+      <c r="B114" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D114" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E114" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F114" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I114" t="inlineStr"/>
+      <c r="P114" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q114" t="n">
+        <v>712263</v>
+      </c>
+      <c r="R114" t="n">
+        <v>6358461</v>
+      </c>
+      <c r="S114" t="n">
+        <v>10</v>
+      </c>
+      <c r="T114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V114" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W114" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y114" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AA114" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>13:47</t>
+        </is>
+      </c>
+      <c r="AD114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG114" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT114" t="inlineStr"/>
+      <c r="AW114" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX114" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY114" t="inlineStr"/>
+    </row>
+    <row r="115">
+      <c r="A115" t="n">
+        <v>129004204</v>
+      </c>
+      <c r="B115" t="n">
+        <v>87262</v>
+      </c>
+      <c r="D115" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E115" t="n">
+        <v>248956</v>
+      </c>
+      <c r="F115" t="inlineStr">
+        <is>
+          <t>Gulsträngad fagerspindling</t>
+        </is>
+      </c>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>Cortinarius haasii</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr">
+        <is>
+          <t>(M.M.Moser) M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr"/>
+      <c r="P115" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q115" t="n">
+        <v>712180</v>
+      </c>
+      <c r="R115" t="n">
+        <v>6358430</v>
+      </c>
+      <c r="S115" t="n">
+        <v>10</v>
+      </c>
+      <c r="T115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V115" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W115" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y115" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AA115" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
+      <c r="AD115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG115" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT115" t="inlineStr"/>
+      <c r="AW115" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX115" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY115" t="inlineStr"/>
+    </row>
+    <row r="116">
+      <c r="A116" t="n">
+        <v>129004195</v>
+      </c>
+      <c r="B116" t="n">
+        <v>87323</v>
+      </c>
+      <c r="D116" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E116" t="n">
+        <v>249228</v>
+      </c>
+      <c r="F116" t="inlineStr">
+        <is>
+          <t>Barrfagerspindling</t>
+        </is>
+      </c>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>Cortinarius piceae</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr">
+        <is>
+          <t>Frøslev &amp; al.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
+      <c r="P116" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q116" t="n">
+        <v>712179</v>
+      </c>
+      <c r="R116" t="n">
+        <v>6358417</v>
+      </c>
+      <c r="S116" t="n">
+        <v>10</v>
+      </c>
+      <c r="T116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V116" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W116" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y116" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AA116" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
+      <c r="AD116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE116" t="b">
+        <v>1</v>
+      </c>
+      <c r="AF116" t="inlineStr"/>
+      <c r="AG116" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT116" t="inlineStr"/>
+      <c r="AW116" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX116" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY116" t="inlineStr"/>
+    </row>
+    <row r="117">
+      <c r="A117" t="n">
+        <v>129004202</v>
+      </c>
+      <c r="B117" t="n">
+        <v>91316</v>
+      </c>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E117" t="n">
+        <v>1000938</v>
+      </c>
+      <c r="F117" t="inlineStr">
+        <is>
+          <t>Jordstjärnesläktet</t>
+        </is>
+      </c>
+      <c r="G117" t="inlineStr">
+        <is>
+          <t>Geastrum</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>Pers., nom.sanct.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
+      <c r="P117" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q117" t="n">
+        <v>712196</v>
+      </c>
+      <c r="R117" t="n">
+        <v>6358401</v>
+      </c>
+      <c r="S117" t="n">
+        <v>10</v>
+      </c>
+      <c r="T117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V117" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W117" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y117" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AA117" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
+      <c r="AD117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF117" t="inlineStr"/>
+      <c r="AG117" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT117" t="inlineStr"/>
+      <c r="AW117" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX117" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY117" t="inlineStr"/>
+    </row>
+    <row r="118">
+      <c r="A118" t="n">
+        <v>128947656</v>
+      </c>
+      <c r="B118" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D118" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E118" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F118" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G118" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H118" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="P118" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q118" t="n">
+        <v>712239</v>
+      </c>
+      <c r="R118" t="n">
+        <v>6358515</v>
+      </c>
+      <c r="S118" t="n">
+        <v>10</v>
+      </c>
+      <c r="T118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V118" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W118" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y118" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA118" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF118" t="inlineStr"/>
+      <c r="AG118" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT118" t="inlineStr"/>
+      <c r="AW118" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX118" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY118" t="inlineStr"/>
+    </row>
+    <row r="119">
+      <c r="A119" t="n">
+        <v>128947657</v>
+      </c>
+      <c r="B119" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E119" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F119" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G119" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr"/>
+      <c r="P119" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q119" t="n">
+        <v>712164</v>
+      </c>
+      <c r="R119" t="n">
+        <v>6358415</v>
+      </c>
+      <c r="S119" t="n">
+        <v>10</v>
+      </c>
+      <c r="T119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V119" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W119" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y119" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF119" t="inlineStr"/>
+      <c r="AG119" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT119" t="inlineStr"/>
+      <c r="AW119" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX119" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY119" t="inlineStr"/>
+    </row>
+    <row r="120">
+      <c r="A120" t="n">
+        <v>128947659</v>
+      </c>
+      <c r="B120" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E120" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F120" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr"/>
+      <c r="P120" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q120" t="n">
+        <v>712053</v>
+      </c>
+      <c r="R120" t="n">
+        <v>6358298</v>
+      </c>
+      <c r="S120" t="n">
+        <v>10</v>
+      </c>
+      <c r="T120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V120" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W120" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y120" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA120" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF120" t="inlineStr"/>
+      <c r="AG120" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT120" t="inlineStr"/>
+      <c r="AW120" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX120" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY120" t="inlineStr"/>
+    </row>
+    <row r="121">
+      <c r="A121" t="n">
+        <v>128947660</v>
+      </c>
+      <c r="B121" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D121" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E121" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F121" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
+      <c r="P121" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q121" t="n">
+        <v>712054</v>
+      </c>
+      <c r="R121" t="n">
+        <v>6358300</v>
+      </c>
+      <c r="S121" t="n">
+        <v>10</v>
+      </c>
+      <c r="T121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V121" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W121" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y121" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AA121" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AD121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF121" t="inlineStr"/>
+      <c r="AG121" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT121" t="inlineStr"/>
+      <c r="AW121" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX121" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY121" t="inlineStr"/>
+    </row>
+    <row r="122">
+      <c r="A122" t="n">
+        <v>129004198</v>
+      </c>
+      <c r="B122" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D122" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E122" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G122" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H122" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
+      <c r="P122" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q122" t="n">
+        <v>712260</v>
+      </c>
+      <c r="R122" t="n">
+        <v>6358398</v>
+      </c>
+      <c r="S122" t="n">
+        <v>10</v>
+      </c>
+      <c r="T122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V122" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W122" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y122" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA122" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF122" t="inlineStr"/>
+      <c r="AG122" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT122" t="inlineStr"/>
+      <c r="AW122" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX122" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY122" t="inlineStr"/>
+    </row>
+    <row r="123">
+      <c r="A123" t="n">
+        <v>129004199</v>
+      </c>
+      <c r="B123" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D123" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E123" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
+      <c r="P123" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q123" t="n">
+        <v>712133</v>
+      </c>
+      <c r="R123" t="n">
+        <v>6358416</v>
+      </c>
+      <c r="S123" t="n">
+        <v>10</v>
+      </c>
+      <c r="T123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V123" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W123" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y123" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA123" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF123" t="inlineStr"/>
+      <c r="AG123" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT123" t="inlineStr"/>
+      <c r="AW123" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX123" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY123" t="inlineStr"/>
+    </row>
+    <row r="124">
+      <c r="A124" t="n">
+        <v>129004200</v>
+      </c>
+      <c r="B124" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D124" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E124" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
+      <c r="P124" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q124" t="n">
+        <v>712116</v>
+      </c>
+      <c r="R124" t="n">
+        <v>6358338</v>
+      </c>
+      <c r="S124" t="n">
+        <v>10</v>
+      </c>
+      <c r="T124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V124" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W124" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y124" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA124" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF124" t="inlineStr"/>
+      <c r="AG124" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT124" t="inlineStr"/>
+      <c r="AW124" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY124"/>
+  <dimension ref="A1:AY127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11972,48 +11972,48 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>128947647</v>
+        <v>134690189</v>
       </c>
       <c r="B108" t="n">
-        <v>87369</v>
+        <v>99113</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>248947</v>
+        <v>223591</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Lye Bjärges, Gtl</t>
+          <t>Lye Bärges, Gtl</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>712175</v>
+        <v>712377</v>
       </c>
       <c r="R108" t="n">
-        <v>6358413</v>
+        <v>6358365</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12037,12 +12037,27 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>15:19</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>15:19</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>9</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12057,60 +12072,60 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>128947648</v>
+        <v>134690193</v>
       </c>
       <c r="B109" t="n">
-        <v>87369</v>
+        <v>99113</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>248947</v>
+        <v>223591</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Lye Bjärges, Gtl</t>
+          <t>Lye Bärges, Gtl</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>712168</v>
+        <v>712396</v>
       </c>
       <c r="R109" t="n">
-        <v>6358403</v>
+        <v>6358391</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12134,12 +12149,27 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>15:29</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>15:29</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>27</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12154,60 +12184,60 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>128947649</v>
+        <v>134690194</v>
       </c>
       <c r="B110" t="n">
-        <v>87369</v>
+        <v>99113</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>248947</v>
+        <v>223591</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Trollspindling</t>
+          <t>Skogsnycklar</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Cortinarius subgracilis</t>
+          <t>Dactylorhiza maculata subsp. fuchsii</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>Moënne-Locc.</t>
+          <t>(Druce) Hyl.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Lye Bjärges, Gtl</t>
+          <t>Lye Bärges, Gtl</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>712051</v>
+        <v>712410</v>
       </c>
       <c r="R110" t="n">
-        <v>6358299</v>
+        <v>6358429</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12231,12 +12261,27 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>15:36</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-10-06</t>
+          <t>2026-06-26</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>15:36</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>10</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12251,19 +12296,19 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Margaret Rainey</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>129004190</v>
+        <v>128947647</v>
       </c>
       <c r="B111" t="n">
         <v>87369</v>
@@ -12298,10 +12343,10 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>712178</v>
+        <v>712175</v>
       </c>
       <c r="R111" t="n">
-        <v>6358421</v>
+        <v>6358413</v>
       </c>
       <c r="S111" t="n">
         <v>10</v>
@@ -12331,19 +12376,9 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>13:08</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>13:08</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12358,19 +12393,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>129004191</v>
+        <v>128947648</v>
       </c>
       <c r="B112" t="n">
         <v>87369</v>
@@ -12405,10 +12440,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>712118</v>
+        <v>712168</v>
       </c>
       <c r="R112" t="n">
-        <v>6358397</v>
+        <v>6358403</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12438,19 +12473,9 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>11:01</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>11:01</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12465,22 +12490,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>128947663</v>
+        <v>128947649</v>
       </c>
       <c r="B113" t="n">
-        <v>87262</v>
+        <v>87369</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12488,21 +12513,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>248956</v>
+        <v>248947</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12512,10 +12537,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>712176</v>
+        <v>712051</v>
       </c>
       <c r="R113" t="n">
-        <v>6358409</v>
+        <v>6358299</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12556,7 +12581,6 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
       </c>
@@ -12575,10 +12599,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>129004203</v>
+        <v>129004190</v>
       </c>
       <c r="B114" t="n">
-        <v>87262</v>
+        <v>87369</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -12586,21 +12610,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>248956</v>
+        <v>248947</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12610,10 +12634,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>712263</v>
+        <v>712178</v>
       </c>
       <c r="R114" t="n">
-        <v>6358461</v>
+        <v>6358421</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12645,7 +12669,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12655,7 +12679,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>13:47</t>
+          <t>13:08</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12682,10 +12706,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129004204</v>
+        <v>129004191</v>
       </c>
       <c r="B115" t="n">
-        <v>87262</v>
+        <v>87369</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -12693,21 +12717,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>248956</v>
+        <v>248947</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Gulsträngad fagerspindling</t>
+          <t>Trollspindling</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Cortinarius haasii</t>
+          <t>Cortinarius subgracilis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(M.M.Moser) M.M.Moser</t>
+          <t>Moënne-Locc.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12717,10 +12741,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>712180</v>
+        <v>712118</v>
       </c>
       <c r="R115" t="n">
-        <v>6358430</v>
+        <v>6358397</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -12752,7 +12776,7 @@
       </c>
       <c r="Z115" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
@@ -12762,7 +12786,7 @@
       </c>
       <c r="AB115" t="inlineStr">
         <is>
-          <t>13:02</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12789,32 +12813,32 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129004195</v>
+        <v>128947663</v>
       </c>
       <c r="B116" t="n">
-        <v>87323</v>
+        <v>87262</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>249228</v>
+        <v>248956</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Barrfagerspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cortinarius piceae</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>Frøslev &amp; al.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12824,10 +12848,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>712179</v>
+        <v>712176</v>
       </c>
       <c r="R116" t="n">
-        <v>6358417</v>
+        <v>6358409</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12857,26 +12881,16 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>13:15</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
       <c r="AE116" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
@@ -12885,44 +12899,44 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129004202</v>
+        <v>129004203</v>
       </c>
       <c r="B117" t="n">
-        <v>91316</v>
+        <v>87262</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1000938</v>
+        <v>248956</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Jordstjärnesläktet</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Geastrum</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct.</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12932,10 +12946,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>712196</v>
+        <v>712263</v>
       </c>
       <c r="R117" t="n">
-        <v>6358401</v>
+        <v>6358461</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12967,7 +12981,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12977,7 +12991,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>13:25</t>
+          <t>13:47</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -12986,7 +13000,6 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
-      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13005,32 +13018,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128947656</v>
+        <v>129004204</v>
       </c>
       <c r="B118" t="n">
-        <v>87346</v>
+        <v>87262</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6003295</v>
+        <v>248956</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Gulsträngad fagerspindling</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius haasii</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>(M.M.Moser) M.M.Moser</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13040,10 +13053,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>712239</v>
+        <v>712180</v>
       </c>
       <c r="R118" t="n">
-        <v>6358515</v>
+        <v>6358430</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13073,40 +13086,49 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>13:02</t>
+        </is>
+      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
       <c r="AE118" t="b">
         <v>0</v>
       </c>
-      <c r="AF118" t="inlineStr"/>
       <c r="AG118" t="b">
         <v>0</v>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128947657</v>
+        <v>129004195</v>
       </c>
       <c r="B119" t="n">
-        <v>87346</v>
+        <v>87323</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13114,21 +13136,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6003295</v>
+        <v>249228</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Barrfagerspindling</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Cortinarius piceae</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Frøslev &amp; al.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13138,10 +13160,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>712164</v>
+        <v>712179</v>
       </c>
       <c r="R119" t="n">
-        <v>6358415</v>
+        <v>6358417</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13171,16 +13193,26 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>13:15</t>
+        </is>
+      </c>
       <c r="AD119" t="b">
         <v>0</v>
       </c>
       <c r="AE119" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF119" t="inlineStr"/>
       <c r="AG119" t="b">
@@ -13189,44 +13221,44 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128947659</v>
+        <v>129004202</v>
       </c>
       <c r="B120" t="n">
-        <v>87346</v>
+        <v>91316</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6003295</v>
+        <v>1000938</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Odörspindling</t>
+          <t>Jordstjärnesläktet</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Cortinarius russeoides</t>
+          <t>Geastrum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>M.M.Moser</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13236,10 +13268,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>712053</v>
+        <v>712196</v>
       </c>
       <c r="R120" t="n">
-        <v>6358298</v>
+        <v>6358401</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13269,9 +13301,19 @@
           <t>2025-10-06</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>13:25</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>13:25</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13287,19 +13329,19 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Ulla Sebestyen</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128947660</v>
+        <v>128947656</v>
       </c>
       <c r="B121" t="n">
         <v>87346</v>
@@ -13334,10 +13376,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>712054</v>
+        <v>712239</v>
       </c>
       <c r="R121" t="n">
-        <v>6358300</v>
+        <v>6358515</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13397,7 +13439,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>129004198</v>
+        <v>128947657</v>
       </c>
       <c r="B122" t="n">
         <v>87346</v>
@@ -13432,10 +13474,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>712260</v>
+        <v>712164</v>
       </c>
       <c r="R122" t="n">
-        <v>6358398</v>
+        <v>6358415</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13465,19 +13507,9 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>13:55</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>13:55</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13493,19 +13525,19 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>129004199</v>
+        <v>128947659</v>
       </c>
       <c r="B123" t="n">
         <v>87346</v>
@@ -13540,10 +13572,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>712133</v>
+        <v>712053</v>
       </c>
       <c r="R123" t="n">
-        <v>6358416</v>
+        <v>6358298</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13573,19 +13605,9 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>11:29</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>11:29</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13601,19 +13623,19 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Ulla Sebestyen</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>129004200</v>
+        <v>128947660</v>
       </c>
       <c r="B124" t="n">
         <v>87346</v>
@@ -13648,10 +13670,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>712116</v>
+        <v>712054</v>
       </c>
       <c r="R124" t="n">
-        <v>6358338</v>
+        <v>6358300</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13681,19 +13703,9 @@
           <t>2025-10-06</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>10:24</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2025-10-06</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>10:24</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13709,15 +13721,339 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AX124" t="inlineStr">
+        <is>
+          <t>Ulla Sebestyen</t>
+        </is>
+      </c>
+      <c r="AY124" t="inlineStr"/>
+    </row>
+    <row r="125">
+      <c r="A125" t="n">
+        <v>129004198</v>
+      </c>
+      <c r="B125" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D125" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E125" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G125" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H125" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I125" t="inlineStr"/>
+      <c r="P125" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q125" t="n">
+        <v>712260</v>
+      </c>
+      <c r="R125" t="n">
+        <v>6358398</v>
+      </c>
+      <c r="S125" t="n">
+        <v>10</v>
+      </c>
+      <c r="T125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V125" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W125" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y125" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z125" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AA125" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB125" t="inlineStr">
+        <is>
+          <t>13:55</t>
+        </is>
+      </c>
+      <c r="AD125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF125" t="inlineStr"/>
+      <c r="AG125" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT125" t="inlineStr"/>
+      <c r="AW125" t="inlineStr">
+        <is>
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AX124" t="inlineStr">
+      <c r="AX125" t="inlineStr">
         <is>
           <t>Martin Axegård</t>
         </is>
       </c>
-      <c r="AY124" t="inlineStr"/>
+      <c r="AY125" t="inlineStr"/>
+    </row>
+    <row r="126">
+      <c r="A126" t="n">
+        <v>129004199</v>
+      </c>
+      <c r="B126" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D126" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E126" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G126" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H126" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="P126" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q126" t="n">
+        <v>712133</v>
+      </c>
+      <c r="R126" t="n">
+        <v>6358416</v>
+      </c>
+      <c r="S126" t="n">
+        <v>10</v>
+      </c>
+      <c r="T126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V126" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W126" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y126" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z126" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AA126" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB126" t="inlineStr">
+        <is>
+          <t>11:29</t>
+        </is>
+      </c>
+      <c r="AD126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF126" t="inlineStr"/>
+      <c r="AG126" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT126" t="inlineStr"/>
+      <c r="AW126" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX126" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY126" t="inlineStr"/>
+    </row>
+    <row r="127">
+      <c r="A127" t="n">
+        <v>129004200</v>
+      </c>
+      <c r="B127" t="n">
+        <v>87346</v>
+      </c>
+      <c r="D127" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E127" t="n">
+        <v>6003295</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>Odörspindling</t>
+        </is>
+      </c>
+      <c r="G127" t="inlineStr">
+        <is>
+          <t>Cortinarius russeoides</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr">
+        <is>
+          <t>M.M.Moser</t>
+        </is>
+      </c>
+      <c r="I127" t="inlineStr"/>
+      <c r="P127" t="inlineStr">
+        <is>
+          <t>Lye Bjärges, Gtl</t>
+        </is>
+      </c>
+      <c r="Q127" t="n">
+        <v>712116</v>
+      </c>
+      <c r="R127" t="n">
+        <v>6358338</v>
+      </c>
+      <c r="S127" t="n">
+        <v>10</v>
+      </c>
+      <c r="T127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="U127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="V127" t="inlineStr">
+        <is>
+          <t>Gotland</t>
+        </is>
+      </c>
+      <c r="W127" t="inlineStr">
+        <is>
+          <t>Lye</t>
+        </is>
+      </c>
+      <c r="Y127" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="Z127" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AA127" t="inlineStr">
+        <is>
+          <t>2025-10-06</t>
+        </is>
+      </c>
+      <c r="AB127" t="inlineStr">
+        <is>
+          <t>10:24</t>
+        </is>
+      </c>
+      <c r="AD127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF127" t="inlineStr"/>
+      <c r="AG127" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT127" t="inlineStr"/>
+      <c r="AW127" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AX127" t="inlineStr">
+        <is>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY127" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30542-2025 artfynd.xlsx
+++ b/artfynd/A 30542-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY127"/>
+  <dimension ref="A1:AZ127"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947677</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947645</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947649</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1061,6 +1081,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947659</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1159,6 +1184,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947660</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1256,6 +1286,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947652</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1363,6 +1398,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004213</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1470,6 +1510,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004215</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1577,6 +1622,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004201</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1674,6 +1724,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947666</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1781,6 +1836,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004205</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1888,6 +1948,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004206</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1995,6 +2060,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004207</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2102,6 +2172,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004208</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2209,6 +2284,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004209</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2316,6 +2396,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004210</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2428,6 +2513,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004211</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2541,6 +2631,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004212</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2639,6 +2734,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947643</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2736,6 +2836,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947644</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2843,6 +2948,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004186</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2951,6 +3061,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004193</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3057,6 +3172,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583862</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3155,6 +3275,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947646</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3252,6 +3377,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947675</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3349,6 +3479,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947676</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3456,6 +3591,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004214</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3553,6 +3693,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947669</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3650,6 +3795,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947670</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3747,6 +3897,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947671</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3844,6 +3999,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947672</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3941,6 +4101,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947673</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4038,6 +4203,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947674</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4145,6 +4315,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004194</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4242,6 +4417,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947655</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4349,6 +4529,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004187</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4456,6 +4641,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004188</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4553,6 +4743,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947664</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4654,6 +4849,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947667</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4759,6 +4959,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947653</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4864,6 +5069,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947654</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -4985,6 +5195,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583805</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5111,6 +5326,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583806</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5232,6 +5452,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583807</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5353,6 +5578,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583808</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5474,6 +5704,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583809</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5595,6 +5830,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583810</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5702,6 +5942,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682619</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5814,6 +6059,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682620</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5921,6 +6171,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682622</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -6033,6 +6288,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682623</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6145,6 +6405,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682626</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6252,6 +6517,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682628</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6359,6 +6629,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682630</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6466,6 +6741,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682632</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6578,6 +6858,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682633</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6685,6 +6970,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134686402</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6792,6 +7082,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134686405</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6904,6 +7199,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134686409</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -7011,6 +7311,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134686414</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7118,6 +7423,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134686416</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7239,6 +7549,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69286493</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7346,6 +7661,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004192</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7448,6 +7768,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69379905</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7559,6 +7884,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583700</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7665,6 +7995,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69379901</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7776,6 +8111,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69379907</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7878,6 +8218,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/69908560</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7989,6 +8334,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583670</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8100,6 +8450,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583673</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8211,6 +8566,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583676</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8322,6 +8682,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583699</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8433,6 +8798,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583743</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8544,6 +8914,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583648</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8655,6 +9030,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583650</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8766,6 +9146,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583659</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8877,6 +9262,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583708</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8988,6 +9378,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583718</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -9099,6 +9494,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583754</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9201,6 +9601,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583726</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9303,6 +9708,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583618</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9405,6 +9815,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583633</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9507,6 +9922,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583641</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9614,6 +10034,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583672</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9721,6 +10146,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583675</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9828,6 +10258,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583678</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9935,6 +10370,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583702</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -10037,6 +10477,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583703</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -10148,6 +10593,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583707</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10259,6 +10709,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583714</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10375,6 +10830,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583720</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10477,6 +10937,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583639</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10579,6 +11044,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583642</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10681,6 +11151,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583644</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10783,6 +11258,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583646</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10885,6 +11365,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583688</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10987,6 +11472,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583695</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11089,6 +11579,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583698</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11191,6 +11686,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583723</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11293,6 +11793,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583620</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11395,6 +11900,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583728</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11497,6 +12007,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583734</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11599,6 +12114,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583622</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11715,6 +12235,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583741</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11822,6 +12347,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134682629</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11933,6 +12463,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583677</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -12044,6 +12579,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583687</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12146,6 +12686,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583694</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12262,6 +12807,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126583701</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12374,6 +12924,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134690189</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12486,6 +13041,11 @@
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134690193</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12598,6 +13158,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134690194</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12695,6 +13260,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947647</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12792,6 +13362,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947648</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12899,6 +13474,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004190</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -13006,6 +13586,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004191</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13104,6 +13689,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947663</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13211,6 +13801,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004203</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13318,6 +13913,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004204</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13426,6 +14026,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004195</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13534,6 +14139,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004202</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13632,6 +14242,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947656</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13730,6 +14345,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128947657</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13838,6 +14458,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004198</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13946,6 +14571,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004199</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14054,8 +14684,141 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129004200</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>